--- a/Timesheet_Reconciliation_Jonathan_Hendratno.xlsx
+++ b/Timesheet_Reconciliation_Jonathan_Hendratno.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -53,12 +53,12 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font/>
     <font>
       <b val="1"/>
       <color rgb="001F3864"/>
@@ -75,14 +75,19 @@
       <sz val="11"/>
     </font>
     <font>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
-      <color rgb="00404040"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +121,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -156,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,56 +201,69 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -652,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T73"/>
+  <dimension ref="A1:T90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="17" min="1" max="1"/>
@@ -665,7 +698,7 @@
     <col width="11" customWidth="1" style="12" min="8" max="8"/>
     <col width="10" customWidth="1" style="12" min="9" max="9"/>
     <col width="10" customWidth="1" style="12" min="10" max="10"/>
-    <col width="12" customWidth="1" style="12" min="11" max="11"/>
+    <col width="14" customWidth="1" style="12" min="11" max="11"/>
     <col width="11" customWidth="1" style="12" min="12" max="12"/>
     <col width="12" customWidth="1" style="12" min="13" max="13"/>
     <col width="16" customWidth="1" style="12" min="14" max="14"/>
@@ -701,7 +734,7 @@
     <row r="2" ht="28" customHeight="1" s="12">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Timesheet hours transcribed from the timesheet screenshots (4 fortnights ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026). Paid hours are pulled live by formula from the pay-run tabs in this workbook, matched on work date AND location. Prepared 22/09/2026.</t>
+          <t>Timesheet hours transcribed from the timesheet screenshots (fortnights ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026). Paid hours are pulled live by formula from the pay-run tabs in this workbook, matched on work date AND location. Prepared 22/09/2026.</t>
         </is>
       </c>
       <c r="P2" s="24" t="n"/>
@@ -735,7 +768,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>A.  FORTNIGHT SUMMARY  -  timesheet hours vs hours actually paid</t>
+          <t>A.  QUERY RESPONSE  -  the 16 hours claimed missing WERE paid.  Nothing is owing.</t>
         </is>
       </c>
       <c r="B4" s="26" t="n"/>
@@ -761,52 +794,66 @@
     <row r="5" ht="30" customHeight="1" s="12">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>Fortnight Ending</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>Timesheets
-(count)</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>Timesheet
-Hours</t>
+          <t>Location / Client</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>Paid
-Hours</t>
+          <t>Hours
+Claimed Missing</t>
         </is>
       </c>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>Variance
+          <t>Hours
+Actually Paid</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>Shortfall
 (Hrs)</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
-        <is>
-          <t>Variance
-($ @ $37.50)</t>
-        </is>
-      </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Paid in
+Pay Run</t>
         </is>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>Paid in Pay Run(s)</t>
-        </is>
-      </c>
-      <c r="I5" s="24" t="n"/>
-      <c r="J5" s="24" t="n"/>
-      <c r="K5" s="24" t="n"/>
+          <t>Where to find it
+on that tab</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t>Rate
+$/hr</t>
+        </is>
+      </c>
+      <c r="J5" s="27" t="inlineStr">
+        <is>
+          <t>Gross Paid
+$</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
       <c r="L5" s="24" t="n"/>
       <c r="M5" s="24" t="n"/>
       <c r="N5" s="24" t="n"/>
@@ -819,40 +866,50 @@
     </row>
     <row r="6">
       <c r="A6" s="28" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B6" s="29">
-        <f>COUNTIFS($C$14:$C$29,$A6)</f>
-        <v/>
-      </c>
-      <c r="C6" s="30">
-        <f>SUMIFS($H$14:$H$29,$C$14:$C$29,$A6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="30">
-        <f>SUMIFS($I$14:$I$29,$C$14:$C$29,$A6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="30">
-        <f>C6-D6</f>
+        <v>46258</v>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>DTTL Mel Tech FT 1 [ONS]</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="31">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6)</f>
         <v/>
       </c>
       <c r="F6" s="31">
-        <f>E6*37.5</f>
-        <v/>
-      </c>
-      <c r="G6" s="32">
-        <f>IF(ROUND(E6,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <f>D6-E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="29">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
       <c r="H6" s="32" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
-        </is>
-      </c>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="24" t="n"/>
-      <c r="K6" s="24" t="n"/>
+          <t>'20 Sept 2026 ' rows 3 and 4  (3.5 hrs 08:30-12:00  +  4.5 hrs 12:30-17:00)</t>
+        </is>
+      </c>
+      <c r="I6" s="33">
+        <f>IFERROR(J6/E6,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="33">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="29">
+        <f>IF(ROUND(F6,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
+        <v/>
+      </c>
       <c r="L6" s="24" t="n"/>
       <c r="M6" s="24" t="n"/>
       <c r="N6" s="24" t="n"/>
@@ -865,40 +922,50 @@
     </row>
     <row r="7">
       <c r="A7" s="28" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B7" s="29">
-        <f>COUNTIFS($C$14:$C$29,$A7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="30">
-        <f>SUMIFS($H$14:$H$29,$C$14:$C$29,$A7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="30">
-        <f>SUMIFS($I$14:$I$29,$C$14:$C$29,$A7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="30">
-        <f>C7-D7</f>
+        <v>46262</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>DTTL Mel Tech FT 1 [ONS]</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="31">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7)</f>
         <v/>
       </c>
       <c r="F7" s="31">
-        <f>E7*37.5</f>
-        <v/>
-      </c>
-      <c r="G7" s="32">
-        <f>IF(ROUND(E7,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <f>D7-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="29">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
       <c r="H7" s="32" t="inlineStr">
         <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="24" t="n"/>
+          <t>'20 Sept 2026 ' rows 5 and 6  (3.5 hrs 08:30-12:00  +  4.5 hrs 12:30-17:00)</t>
+        </is>
+      </c>
+      <c r="I7" s="33">
+        <f>IFERROR(J7/E7,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="33">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="29">
+        <f>IF(ROUND(F7,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
+        <v/>
+      </c>
       <c r="L7" s="24" t="n"/>
       <c r="M7" s="24" t="n"/>
       <c r="N7" s="24" t="n"/>
@@ -910,41 +977,36 @@
       <c r="T7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B8" s="29">
-        <f>COUNTIFS($C$14:$C$29,$A8)</f>
-        <v/>
-      </c>
-      <c r="C8" s="30">
-        <f>SUMIFS($H$14:$H$29,$C$14:$C$29,$A8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="30">
-        <f>SUMIFS($I$14:$I$29,$C$14:$C$29,$A8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="30">
-        <f>C8-D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="31">
-        <f>E8*37.5</f>
-        <v/>
-      </c>
-      <c r="G8" s="32">
-        <f>IF(ROUND(E8,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="H8" s="32" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 (DTTL) + 22 Sep 2026 (PwC)</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="n"/>
-      <c r="J8" s="24" t="n"/>
-      <c r="K8" s="24" t="n"/>
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>TOTAL CLAIMED</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="35">
+        <f>SUM(D6:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="35">
+        <f>SUM(E6:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="35">
+        <f>SUM(F6:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="36">
+        <f>SUM(J6:J7)</f>
+        <v/>
+      </c>
+      <c r="K8" s="34">
+        <f>IF(ROUND(F8,2)=0,"NIL OWING - all "&amp;TEXT(D8,"0")&amp;" hrs paid ($"&amp;TEXT(J8,"#,##0.00")&amp;" gross)","AMOUNT OWING - investigate")</f>
+        <v/>
+      </c>
       <c r="L8" s="24" t="n"/>
       <c r="M8" s="24" t="n"/>
       <c r="N8" s="24" t="n"/>
@@ -955,46 +1017,12 @@
       <c r="S8" s="24" t="n"/>
       <c r="T8" s="24" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="28" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B9" s="29">
-        <f>COUNTIFS($C$14:$C$29,$A9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="30">
-        <f>SUMIFS($H$14:$H$29,$C$14:$C$29,$A9)</f>
-        <v/>
-      </c>
-      <c r="D9" s="30">
-        <f>SUMIFS($I$14:$I$29,$C$14:$C$29,$A9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="30">
-        <f>C9-D9</f>
-        <v/>
-      </c>
-      <c r="F9" s="31">
-        <f>E9*37.5</f>
-        <v/>
-      </c>
-      <c r="G9" s="32">
-        <f>IF(ROUND(E9,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="H9" s="32" t="inlineStr">
-        <is>
-          <t>22 Sep 2026</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="24" t="n"/>
-      <c r="K9" s="24" t="n"/>
-      <c r="L9" s="24" t="n"/>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="24" t="n"/>
-      <c r="O9" s="24" t="n"/>
+    <row r="9" ht="46" customHeight="1" s="12">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>WHY IT LOOKED MISSING:  (1) Each day is split across two pay lines, either side of the lunch break - 3.5 hrs + 4.5 hrs - so neither line ever shows as "8 hours" when you scan the payslip.  (2) Both days sit in the fortnight ending 04/09/2026, but that fortnight was paid across TWO pay runs: the 48 hrs of DTTL work went through the 20 Sep 2026 run, while the 23.5 hrs of PwC work went through the 22 Sep 2026 run. Looking at only one of those payslips shows only part of the fortnight.</t>
+        </is>
+      </c>
       <c r="P9" s="24" t="n"/>
       <c r="Q9" s="24" t="n"/>
       <c r="R9" s="24" t="n"/>
@@ -1002,36 +1030,14 @@
       <c r="T9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="34">
-        <f>SUM(B6:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="35">
-        <f>SUM(C6:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="35">
-        <f>SUM(D6:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="35">
-        <f>SUM(E6:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="36">
-        <f>SUM(F6:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="33">
-        <f>IF(ROUND(E10,2)=0,"FULLY RECONCILED","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="H10" s="33" t="n"/>
+      <c r="A10" s="24" t="n"/>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
+      <c r="H10" s="24" t="n"/>
       <c r="I10" s="24" t="n"/>
       <c r="J10" s="24" t="n"/>
       <c r="K10" s="24" t="n"/>
@@ -1046,137 +1052,130 @@
       <c r="T10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n"/>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="24" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="24" t="n"/>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="24" t="n"/>
-      <c r="O11" s="24" t="n"/>
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>B.  FORTNIGHT SUMMARY  -  timesheet hours vs hours actually paid</t>
+        </is>
+      </c>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="38" t="n"/>
+      <c r="J11" s="38" t="n"/>
+      <c r="K11" s="38" t="n"/>
+      <c r="L11" s="38" t="n"/>
+      <c r="M11" s="38" t="n"/>
+      <c r="N11" s="38" t="n"/>
+      <c r="O11" s="38" t="n"/>
       <c r="P11" s="24" t="n"/>
       <c r="Q11" s="24" t="n"/>
       <c r="R11" s="24" t="n"/>
       <c r="S11" s="24" t="n"/>
       <c r="T11" s="24" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>B.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay run that paid it</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="26" t="n"/>
-      <c r="O12" s="26" t="n"/>
+    <row r="12" ht="30" customHeight="1" s="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Fortnight Ending</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Timesheets
+(count)</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Timesheet
+Hours</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Paid
+Hours</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>Variance
+(Hrs)</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>Variance
+($ @ $37.50)</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
+        <is>
+          <t>Paid in Pay Run(s)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="24" t="n"/>
+      <c r="K12" s="24" t="n"/>
+      <c r="L12" s="24" t="n"/>
+      <c r="M12" s="24" t="n"/>
+      <c r="N12" s="24" t="n"/>
+      <c r="O12" s="24" t="n"/>
       <c r="P12" s="24" t="n"/>
       <c r="Q12" s="24" t="n"/>
       <c r="R12" s="24" t="n"/>
       <c r="S12" s="24" t="n"/>
       <c r="T12" s="24" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="12">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>Fortnight
-Ending</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>Location / Client (per timesheet)</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="G13" s="27" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="inlineStr">
-        <is>
-          <t>Timesheet
-Hours</t>
-        </is>
-      </c>
-      <c r="I13" s="27" t="inlineStr">
-        <is>
-          <t>Paid
-Hours</t>
-        </is>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
-        <is>
-          <t>Variance
-(Hrs)</t>
-        </is>
-      </c>
-      <c r="K13" s="27" t="inlineStr">
-        <is>
-          <t>Paid in
-Pay Run</t>
-        </is>
-      </c>
-      <c r="L13" s="27" t="inlineStr">
-        <is>
-          <t>Rate Paid
-$/hr</t>
-        </is>
-      </c>
-      <c r="M13" s="27" t="inlineStr">
-        <is>
-          <t>Gross Paid
-$</t>
-        </is>
-      </c>
-      <c r="N13" s="27" t="inlineStr">
-        <is>
-          <t>Rate
-Check</t>
-        </is>
-      </c>
-      <c r="O13" s="27" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+    <row r="13">
+      <c r="A13" s="39" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" s="40">
+        <f>COUNTIFS($C$21:$C$36,$A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="41">
+        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="41">
+        <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="41">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="42">
+        <f>E13*37.5</f>
+        <v/>
+      </c>
+      <c r="G13" s="43">
+        <f>IF(ROUND(E13,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="H13" s="43" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="24" t="n"/>
+      <c r="L13" s="24" t="n"/>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="24" t="n"/>
+      <c r="O13" s="24" t="n"/>
       <c r="P13" s="24" t="n"/>
       <c r="Q13" s="24" t="n"/>
       <c r="R13" s="24" t="n"/>
@@ -1184,69 +1183,45 @@
       <c r="T13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>CBA FT Tech MEL - 12 months [ONS]</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="inlineStr">
-        <is>
-          <t>7:00 AM</t>
-        </is>
-      </c>
-      <c r="F14" s="29" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="G14" s="29" t="inlineStr">
-        <is>
-          <t>12:30-1:30</t>
-        </is>
-      </c>
-      <c r="H14" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" s="30">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A14,'07 Aug 2026'!$K$3:$K$6,$D14)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A14,'21 Aug 2026'!$K$3:$K$7,$D14)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A14,'20 Sept 2026 '!$K$3:$K$14,$D14)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A14,'22 Sep 2026'!$K$3:$K$11,$D14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="30">
-        <f>H14-I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A14,'07 Aug 2026'!$K$3:$K$6,$D14)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A14,'21 Aug 2026'!$K$3:$K$7,$D14)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A14,'20 Sept 2026 '!$K$3:$K$14,$D14)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A14,'22 Sep 2026'!$K$3:$K$11,$D14)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L14" s="31">
-        <f>IFERROR(M14/I14,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="31">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A14,'07 Aug 2026'!$K$3:$K$6,$D14)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A14,'21 Aug 2026'!$K$3:$K$7,$D14)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A14,'20 Sept 2026 '!$K$3:$K$14,$D14)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A14,'22 Sep 2026'!$K$3:$K$11,$D14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="29">
-        <f>IF(I14=0,"",IF(ROUND(L14,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L14)*I14,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O14" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 5.5 + 2.5 hrs either side of break</t>
-        </is>
-      </c>
+      <c r="A14" s="39" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B14" s="40">
+        <f>COUNTIFS($C$21:$C$36,$A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="41">
+        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="41">
+        <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="41">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="42">
+        <f>E14*37.5</f>
+        <v/>
+      </c>
+      <c r="G14" s="43">
+        <f>IF(ROUND(E14,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
+        <is>
+          <t>21 Aug 2026</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="n"/>
+      <c r="J14" s="24" t="n"/>
+      <c r="K14" s="24" t="n"/>
+      <c r="L14" s="24" t="n"/>
+      <c r="M14" s="24" t="n"/>
+      <c r="N14" s="24" t="n"/>
+      <c r="O14" s="24" t="n"/>
       <c r="P14" s="24" t="n"/>
       <c r="Q14" s="24" t="n"/>
       <c r="R14" s="24" t="n"/>
@@ -1254,69 +1229,45 @@
       <c r="T14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n">
-        <v>46233</v>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>PWC – MEL Technician [ONS]</t>
-        </is>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
-        <is>
-          <t>8:00 AM</t>
-        </is>
-      </c>
-      <c r="F15" s="29" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="G15" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="30">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A15,'07 Aug 2026'!$K$3:$K$6,$D15)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A15,'21 Aug 2026'!$K$3:$K$7,$D15)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A15,'20 Sept 2026 '!$K$3:$K$14,$D15)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A15,'22 Sep 2026'!$K$3:$K$11,$D15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="30">
-        <f>H15-I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A15,'07 Aug 2026'!$K$3:$K$6,$D15)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A15,'21 Aug 2026'!$K$3:$K$7,$D15)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A15,'20 Sept 2026 '!$K$3:$K$14,$D15)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A15,'22 Sep 2026'!$K$3:$K$11,$D15)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L15" s="31">
-        <f>IFERROR(M15/I15,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="31">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A15,'07 Aug 2026'!$K$3:$K$6,$D15)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A15,'21 Aug 2026'!$K$3:$K$7,$D15)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A15,'20 Sept 2026 '!$K$3:$K$14,$D15)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A15,'22 Sep 2026'!$K$3:$K$11,$D15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="29">
-        <f>IF(I15=0,"",IF(ROUND(L15,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L15)*I15,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O15" s="37" t="inlineStr">
-        <is>
-          <t>Two separate timesheets this day - matched by location</t>
-        </is>
-      </c>
+      <c r="A15" s="39" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B15" s="40">
+        <f>COUNTIFS($C$21:$C$36,$A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="41">
+        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="41">
+        <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="41">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="42">
+        <f>E15*37.5</f>
+        <v/>
+      </c>
+      <c r="G15" s="43">
+        <f>IF(ROUND(E15,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 (DTTL 48 hrs) + 22 Sep 2026 (PwC 23.5 hrs)</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="n"/>
+      <c r="K15" s="24" t="n"/>
+      <c r="L15" s="24" t="n"/>
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="24" t="n"/>
+      <c r="O15" s="24" t="n"/>
       <c r="P15" s="24" t="n"/>
       <c r="Q15" s="24" t="n"/>
       <c r="R15" s="24" t="n"/>
@@ -1324,69 +1275,45 @@
       <c r="T15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="n">
-        <v>46233</v>
-      </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C16" s="28" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D16" s="32" t="inlineStr">
-        <is>
-          <t>Aware Super AV Maintenance [ONS]</t>
-        </is>
-      </c>
-      <c r="E16" s="29" t="inlineStr">
-        <is>
-          <t>2:25 PM</t>
-        </is>
-      </c>
-      <c r="F16" s="29" t="inlineStr">
-        <is>
-          <t>6:25 PM</t>
-        </is>
-      </c>
-      <c r="G16" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="30">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A16,'07 Aug 2026'!$K$3:$K$6,$D16)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A16,'21 Aug 2026'!$K$3:$K$7,$D16)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A16,'20 Sept 2026 '!$K$3:$K$14,$D16)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A16,'22 Sep 2026'!$K$3:$K$11,$D16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="30">
-        <f>H16-I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A16,'07 Aug 2026'!$K$3:$K$6,$D16)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A16,'21 Aug 2026'!$K$3:$K$7,$D16)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A16,'20 Sept 2026 '!$K$3:$K$14,$D16)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A16,'22 Sep 2026'!$K$3:$K$11,$D16)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L16" s="31">
-        <f>IFERROR(M16/I16,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="31">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A16,'07 Aug 2026'!$K$3:$K$6,$D16)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A16,'21 Aug 2026'!$K$3:$K$7,$D16)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A16,'20 Sept 2026 '!$K$3:$K$14,$D16)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A16,'22 Sep 2026'!$K$3:$K$11,$D16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="29">
-        <f>IF(I16=0,"",IF(ROUND(L16,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L16)*I16,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O16" s="37" t="inlineStr">
-        <is>
-          <t>Two separate timesheets this day - matched by location</t>
-        </is>
-      </c>
+      <c r="A16" s="39" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B16" s="40">
+        <f>COUNTIFS($C$21:$C$36,$A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="41">
+        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="41">
+        <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="41">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="42">
+        <f>E16*37.5</f>
+        <v/>
+      </c>
+      <c r="G16" s="43">
+        <f>IF(ROUND(E16,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="24" t="n"/>
+      <c r="K16" s="24" t="n"/>
+      <c r="L16" s="24" t="n"/>
+      <c r="M16" s="24" t="n"/>
+      <c r="N16" s="24" t="n"/>
+      <c r="O16" s="24" t="n"/>
       <c r="P16" s="24" t="n"/>
       <c r="Q16" s="24" t="n"/>
       <c r="R16" s="24" t="n"/>
@@ -1394,69 +1321,43 @@
       <c r="T16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B17" s="29" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="n">
-        <v>46255</v>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>CBA FT Tech MEL - 12 months [ONS]</t>
-        </is>
-      </c>
-      <c r="E17" s="29" t="inlineStr">
-        <is>
-          <t>7:00 AM</t>
-        </is>
-      </c>
-      <c r="F17" s="29" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="G17" s="29" t="inlineStr">
-        <is>
-          <t>12:00-1:00</t>
-        </is>
-      </c>
-      <c r="H17" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I17" s="30">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A17,'07 Aug 2026'!$K$3:$K$6,$D17)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A17,'21 Aug 2026'!$K$3:$K$7,$D17)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A17,'20 Sept 2026 '!$K$3:$K$14,$D17)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A17,'22 Sep 2026'!$K$3:$K$11,$D17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="30">
-        <f>H17-I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A17,'07 Aug 2026'!$K$3:$K$6,$D17)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A17,'21 Aug 2026'!$K$3:$K$7,$D17)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A17,'20 Sept 2026 '!$K$3:$K$14,$D17)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A17,'22 Sep 2026'!$K$3:$K$11,$D17)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L17" s="31">
-        <f>IFERROR(M17/I17,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="31">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A17,'07 Aug 2026'!$K$3:$K$6,$D17)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A17,'21 Aug 2026'!$K$3:$K$7,$D17)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A17,'20 Sept 2026 '!$K$3:$K$14,$D17)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A17,'22 Sep 2026'!$K$3:$K$11,$D17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="29">
-        <f>IF(I17=0,"",IF(ROUND(L17,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L17)*I17,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O17" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 5 + 3 hrs either side of break</t>
-        </is>
-      </c>
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B17" s="45">
+        <f>SUM(B13:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="46">
+        <f>SUM(C13:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="46">
+        <f>SUM(D13:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="46">
+        <f>SUM(E13:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="47">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="44">
+        <f>IF(ROUND(E17,2)=0,"FULLY RECONCILED","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="H17" s="44" t="n"/>
+      <c r="I17" s="24" t="n"/>
+      <c r="J17" s="24" t="n"/>
+      <c r="K17" s="24" t="n"/>
+      <c r="L17" s="24" t="n"/>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="24" t="n"/>
+      <c r="O17" s="24" t="n"/>
       <c r="P17" s="24" t="n"/>
       <c r="Q17" s="24" t="n"/>
       <c r="R17" s="24" t="n"/>
@@ -1464,65 +1365,21 @@
       <c r="T17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="n">
-        <v>46254</v>
-      </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="n">
-        <v>46255</v>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
-        <is>
-          <t>PWC National Pool of Hours [ONS]</t>
-        </is>
-      </c>
-      <c r="E18" s="29" t="inlineStr">
-        <is>
-          <t>1:00 PM</t>
-        </is>
-      </c>
-      <c r="F18" s="29" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="G18" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="30">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A18,'07 Aug 2026'!$K$3:$K$6,$D18)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A18,'21 Aug 2026'!$K$3:$K$7,$D18)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A18,'20 Sept 2026 '!$K$3:$K$14,$D18)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A18,'22 Sep 2026'!$K$3:$K$11,$D18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="30">
-        <f>H18-I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A18,'07 Aug 2026'!$K$3:$K$6,$D18)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A18,'21 Aug 2026'!$K$3:$K$7,$D18)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A18,'20 Sept 2026 '!$K$3:$K$14,$D18)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A18,'22 Sep 2026'!$K$3:$K$11,$D18)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L18" s="31">
-        <f>IFERROR(M18/I18,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="31">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A18,'07 Aug 2026'!$K$3:$K$6,$D18)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A18,'21 Aug 2026'!$K$3:$K$7,$D18)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A18,'20 Sept 2026 '!$K$3:$K$14,$D18)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A18,'22 Sep 2026'!$K$3:$K$11,$D18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="29">
-        <f>IF(I18=0,"",IF(ROUND(L18,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L18)*I18,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O18" s="37" t="inlineStr"/>
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="24" t="n"/>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="24" t="n"/>
+      <c r="L18" s="24" t="n"/>
+      <c r="M18" s="24" t="n"/>
+      <c r="N18" s="24" t="n"/>
+      <c r="O18" s="24" t="n"/>
       <c r="P18" s="24" t="n"/>
       <c r="Q18" s="24" t="n"/>
       <c r="R18" s="24" t="n"/>
@@ -1530,137 +1387,113 @@
       <c r="T18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D19" s="32" t="inlineStr">
-        <is>
-          <t>DTTL Mel Tech FT 1 [ONS]</t>
-        </is>
-      </c>
-      <c r="E19" s="29" t="inlineStr">
-        <is>
-          <t>8:30 AM</t>
-        </is>
-      </c>
-      <c r="F19" s="29" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="G19" s="29" t="inlineStr">
-        <is>
-          <t>12:00-12:30</t>
-        </is>
-      </c>
-      <c r="H19" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I19" s="30">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A19,'07 Aug 2026'!$K$3:$K$6,$D19)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A19,'21 Aug 2026'!$K$3:$K$7,$D19)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A19,'20 Sept 2026 '!$K$3:$K$14,$D19)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A19,'22 Sep 2026'!$K$3:$K$11,$D19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="30">
-        <f>H19-I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A19,'07 Aug 2026'!$K$3:$K$6,$D19)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A19,'21 Aug 2026'!$K$3:$K$7,$D19)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A19,'20 Sept 2026 '!$K$3:$K$14,$D19)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A19,'22 Sep 2026'!$K$3:$K$11,$D19)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L19" s="31">
-        <f>IFERROR(M19/I19,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="31">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A19,'07 Aug 2026'!$K$3:$K$6,$D19)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A19,'21 Aug 2026'!$K$3:$K$7,$D19)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A19,'20 Sept 2026 '!$K$3:$K$14,$D19)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A19,'22 Sep 2026'!$K$3:$K$11,$D19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="29">
-        <f>IF(I19=0,"",IF(ROUND(L19,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L19)*I19,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O19" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 3.5 + 4.5 hrs</t>
-        </is>
-      </c>
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay run that paid it</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="38" t="n"/>
+      <c r="M19" s="38" t="n"/>
+      <c r="N19" s="38" t="n"/>
+      <c r="O19" s="38" t="n"/>
       <c r="P19" s="24" t="n"/>
       <c r="Q19" s="24" t="n"/>
       <c r="R19" s="24" t="n"/>
       <c r="S19" s="24" t="n"/>
       <c r="T19" s="24" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="28" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B20" s="29" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C20" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D20" s="32" t="inlineStr">
-        <is>
-          <t>PWC National Pool of Hours [ONS]</t>
-        </is>
-      </c>
-      <c r="E20" s="29" t="inlineStr">
-        <is>
-          <t>8:00 AM</t>
-        </is>
-      </c>
-      <c r="F20" s="29" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="G20" s="29" t="inlineStr">
-        <is>
-          <t>12:00-1:00</t>
-        </is>
-      </c>
-      <c r="H20" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I20" s="30">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A20,'07 Aug 2026'!$K$3:$K$6,$D20)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A20,'21 Aug 2026'!$K$3:$K$7,$D20)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A20,'20 Sept 2026 '!$K$3:$K$14,$D20)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A20,'22 Sep 2026'!$K$3:$K$11,$D20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="30">
-        <f>H20-I20</f>
-        <v/>
-      </c>
-      <c r="K20" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A20,'07 Aug 2026'!$K$3:$K$6,$D20)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A20,'21 Aug 2026'!$K$3:$K$7,$D20)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A20,'20 Sept 2026 '!$K$3:$K$14,$D20)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A20,'22 Sep 2026'!$K$3:$K$11,$D20)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L20" s="31">
-        <f>IFERROR(M20/I20,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="31">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A20,'07 Aug 2026'!$K$3:$K$6,$D20)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A20,'21 Aug 2026'!$K$3:$K$7,$D20)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A20,'20 Sept 2026 '!$K$3:$K$14,$D20)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A20,'22 Sep 2026'!$K$3:$K$11,$D20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="29">
-        <f>IF(I20=0,"",IF(ROUND(L20,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L20)*I20,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O20" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 4 hrs</t>
+    <row r="20" ht="30" customHeight="1" s="12">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Fortnight
+Ending</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Location / Client (per timesheet)</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="inlineStr">
+        <is>
+          <t>Timesheet
+Hours</t>
+        </is>
+      </c>
+      <c r="I20" s="27" t="inlineStr">
+        <is>
+          <t>Paid
+Hours</t>
+        </is>
+      </c>
+      <c r="J20" s="27" t="inlineStr">
+        <is>
+          <t>Variance
+(Hrs)</t>
+        </is>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>Paid in
+Pay Run</t>
+        </is>
+      </c>
+      <c r="L20" s="27" t="inlineStr">
+        <is>
+          <t>Rate Paid
+$/hr</t>
+        </is>
+      </c>
+      <c r="M20" s="27" t="inlineStr">
+        <is>
+          <t>Gross Paid
+$</t>
+        </is>
+      </c>
+      <c r="N20" s="27" t="inlineStr">
+        <is>
+          <t>Rate
+Check</t>
+        </is>
+      </c>
+      <c r="O20" s="27" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
       <c r="P20" s="24" t="n"/>
@@ -1670,67 +1503,67 @@
       <c r="T20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="A21" s="39" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C21" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>PWC National Pool of Hours [ONS]</t>
-        </is>
-      </c>
-      <c r="E21" s="29" t="inlineStr">
-        <is>
-          <t>8:00 AM</t>
-        </is>
-      </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="C21" s="39" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>CBA FT Tech MEL - 12 months [ONS]</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>7:00 AM</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr">
-        <is>
-          <t>12:00-12:30</t>
-        </is>
-      </c>
-      <c r="H21" s="30" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I21" s="30">
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>12:30-1:30</t>
+        </is>
+      </c>
+      <c r="H21" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="41">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$D21)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$D21)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$D21)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$D21)</f>
         <v/>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="41">
         <f>H21-I21</f>
         <v/>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="40">
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$D21)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$D21)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$D21)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$D21)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="42">
         <f>IFERROR(M21/I21,"")</f>
         <v/>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="42">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$D21)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$D21)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$D21)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$D21)</f>
         <v/>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="40">
         <f>IF(I21=0,"",IF(ROUND(L21,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L21)*I21,"0.00")))</f>
         <v/>
       </c>
-      <c r="O21" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 3.5 hrs</t>
+      <c r="O21" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 5.5 + 2.5 hrs either side of break</t>
         </is>
       </c>
       <c r="P21" s="24" t="n"/>
@@ -1740,67 +1573,67 @@
       <c r="T21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="A22" s="39" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C22" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D22" s="32" t="inlineStr">
-        <is>
-          <t>PWC National Pool of Hours [ONS]</t>
-        </is>
-      </c>
-      <c r="E22" s="29" t="inlineStr">
+      <c r="C22" s="39" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>PWC – MEL Technician [ONS]</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="G22" s="29" t="inlineStr">
-        <is>
-          <t>12:00-1:00</t>
-        </is>
-      </c>
-      <c r="H22" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I22" s="30">
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="41">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$D22)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$D22)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$D22)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$D22)</f>
         <v/>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="41">
         <f>H22-I22</f>
         <v/>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="40">
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$D22)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$D22)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$D22)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$D22)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="42">
         <f>IFERROR(M22/I22,"")</f>
         <v/>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="42">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$D22)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$D22)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$D22)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$D22)</f>
         <v/>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="40">
         <f>IF(I22=0,"",IF(ROUND(L22,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L22)*I22,"0.00")))</f>
         <v/>
       </c>
-      <c r="O22" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 4 hrs</t>
+      <c r="O22" s="48" t="inlineStr">
+        <is>
+          <t>Two separate timesheets this day - matched by location</t>
         </is>
       </c>
       <c r="P22" s="24" t="n"/>
@@ -1810,67 +1643,67 @@
       <c r="T22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D23" s="32" t="inlineStr">
-        <is>
-          <t>DTTL Mel Tech FT 1 [ONS]</t>
-        </is>
-      </c>
-      <c r="E23" s="29" t="inlineStr">
-        <is>
-          <t>8:30 AM</t>
-        </is>
-      </c>
-      <c r="F23" s="29" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="G23" s="29" t="inlineStr">
-        <is>
-          <t>12:00-12:30</t>
-        </is>
-      </c>
-      <c r="H23" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I23" s="30">
+      <c r="A23" s="39" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C23" s="39" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Aware Super AV Maintenance [ONS]</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="inlineStr">
+        <is>
+          <t>2:25 PM</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>6:25 PM</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" s="41">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$D23)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$D23)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$D23)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$D23)</f>
         <v/>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="41">
         <f>H23-I23</f>
         <v/>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="40">
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$D23)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$D23)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$D23)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$D23)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="42">
         <f>IFERROR(M23/I23,"")</f>
         <v/>
       </c>
-      <c r="M23" s="31">
+      <c r="M23" s="42">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$D23)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$D23)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$D23)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$D23)</f>
         <v/>
       </c>
-      <c r="N23" s="29">
+      <c r="N23" s="40">
         <f>IF(I23=0,"",IF(ROUND(L23,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L23)*I23,"0.00")))</f>
         <v/>
       </c>
-      <c r="O23" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 3.5 + 4.5 hrs</t>
+      <c r="O23" s="48" t="inlineStr">
+        <is>
+          <t>Two separate timesheets this day - matched by location</t>
         </is>
       </c>
       <c r="P23" s="24" t="n"/>
@@ -1880,67 +1713,67 @@
       <c r="T23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B24" s="29" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D24" s="32" t="inlineStr">
-        <is>
-          <t>DTTL Mel Tech FT 1 [ONS]</t>
-        </is>
-      </c>
-      <c r="E24" s="29" t="inlineStr">
-        <is>
-          <t>8:30 AM</t>
-        </is>
-      </c>
-      <c r="F24" s="29" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="G24" s="29" t="inlineStr">
-        <is>
-          <t>12:00-12:30</t>
-        </is>
-      </c>
-      <c r="H24" s="30" t="n">
+      <c r="A24" s="39" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C24" s="39" t="n">
+        <v>46255</v>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>CBA FT Tech MEL - 12 months [ONS]</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>7:00 AM</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>12:00-1:00</t>
+        </is>
+      </c>
+      <c r="H24" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="41">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$D24)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$D24)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$D24)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$D24)</f>
         <v/>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="41">
         <f>H24-I24</f>
         <v/>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="40">
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$D24)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$D24)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$D24)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$D24)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="42">
         <f>IFERROR(M24/I24,"")</f>
         <v/>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="42">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$D24)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$D24)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$D24)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$D24)</f>
         <v/>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="40">
         <f>IF(I24=0,"",IF(ROUND(L24,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L24)*I24,"0.00")))</f>
         <v/>
       </c>
-      <c r="O24" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 3.5 + 4.5 hrs</t>
+      <c r="O24" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 5 + 3 hrs either side of break</t>
         </is>
       </c>
       <c r="P24" s="24" t="n"/>
@@ -1950,100 +1783,96 @@
       <c r="T24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D25" s="32" t="inlineStr">
-        <is>
-          <t>DTTL Mel Tech FT 1 [ONS]</t>
-        </is>
-      </c>
-      <c r="E25" s="29" t="inlineStr">
-        <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="F25" s="29" t="inlineStr">
-        <is>
-          <t>5:30 PM</t>
-        </is>
-      </c>
-      <c r="G25" s="29" t="inlineStr">
-        <is>
-          <t>12:00-12:30</t>
-        </is>
-      </c>
-      <c r="H25" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I25" s="30">
+      <c r="A25" s="39" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C25" s="39" t="n">
+        <v>46255</v>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>PWC National Pool of Hours [ONS]</t>
+        </is>
+      </c>
+      <c r="E25" s="40" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" s="41">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)</f>
         <v/>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="41">
         <f>H25-I25</f>
         <v/>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="40">
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="42">
         <f>IFERROR(M25/I25,"")</f>
         <v/>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="42">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)</f>
         <v/>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="40">
         <f>IF(I25=0,"",IF(ROUND(L25,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L25)*I25,"0.00")))</f>
         <v/>
       </c>
-      <c r="O25" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 3 + 5 hrs</t>
-        </is>
-      </c>
+      <c r="O25" s="48" t="inlineStr"/>
       <c r="P25" s="24" t="n"/>
       <c r="Q25" s="24" t="n"/>
       <c r="R25" s="24" t="n"/>
       <c r="S25" s="24" t="n"/>
       <c r="T25" s="24" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1" s="12">
       <c r="A26" s="28" t="n">
-        <v>46267</v>
+        <v>46258</v>
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C26" s="28" t="n">
         <v>46269</v>
       </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
@@ -2051,14 +1880,14 @@
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H26" s="30" t="n">
+      <c r="H26" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="31">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$D26)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$D26)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$D26)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$D26)</f>
         <v/>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="31">
         <f>H26-I26</f>
         <v/>
       </c>
@@ -2066,11 +1895,11 @@
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$D26)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$D26)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$D26)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$D26)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="33">
         <f>IFERROR(M26/I26,"")</f>
         <v/>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="33">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$D26)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$D26)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$D26)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$D26)</f>
         <v/>
       </c>
@@ -2078,9 +1907,9 @@
         <f>IF(I26=0,"",IF(ROUND(L26,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L26)*I26,"0.00")))</f>
         <v/>
       </c>
-      <c r="O26" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 3 + 5 hrs</t>
+      <c r="O26" s="49" t="inlineStr">
+        <is>
+          <t>QUERY - claimed missing. PAID IN FULL in the 20 Sep 2026 run as 3.5 + 4.5 hrs, $300.00 gross. See Section A.</t>
         </is>
       </c>
       <c r="P26" s="24" t="n"/>
@@ -2090,67 +1919,67 @@
       <c r="T26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="n">
+      <c r="A27" s="39" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C27" s="39" t="n">
         <v>46269</v>
       </c>
-      <c r="B27" s="29" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
-        <is>
-          <t>DTTL Mel Tech FT 1 [ONS]</t>
-        </is>
-      </c>
-      <c r="E27" s="29" t="inlineStr">
-        <is>
-          <t>8:30 AM</t>
-        </is>
-      </c>
-      <c r="F27" s="29" t="inlineStr">
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>PWC National Pool of Hours [ONS]</t>
+        </is>
+      </c>
+      <c r="E27" s="40" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G27" s="29" t="inlineStr">
-        <is>
-          <t>12:00-12:30</t>
-        </is>
-      </c>
-      <c r="H27" s="30" t="n">
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>12:00-1:00</t>
+        </is>
+      </c>
+      <c r="H27" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="41">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$D27)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$D27)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$D27)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$D27)</f>
         <v/>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="41">
         <f>H27-I27</f>
         <v/>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="40">
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$D27)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$D27)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$D27)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$D27)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="42">
         <f>IFERROR(M27/I27,"")</f>
         <v/>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="42">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$D27)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$D27)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$D27)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$D27)</f>
         <v/>
       </c>
-      <c r="N27" s="29">
+      <c r="N27" s="40">
         <f>IF(I27=0,"",IF(ROUND(L27,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L27)*I27,"0.00")))</f>
         <v/>
       </c>
-      <c r="O27" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 3.5 + 4.5 hrs</t>
+      <c r="O27" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 4 hrs</t>
         </is>
       </c>
       <c r="P27" s="24" t="n"/>
@@ -2160,67 +1989,67 @@
       <c r="T27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B28" s="29" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="A28" s="39" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C28" s="39" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E28" s="29" t="inlineStr">
+      <c r="E28" s="40" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F28" s="29" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="G28" s="29" t="inlineStr">
-        <is>
-          <t>12:00-1:00</t>
-        </is>
-      </c>
-      <c r="H28" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I28" s="30">
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>12:00-12:30</t>
+        </is>
+      </c>
+      <c r="H28" s="41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I28" s="41">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$D28)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$D28)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$D28)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$D28)</f>
         <v/>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="41">
         <f>H28-I28</f>
         <v/>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="40">
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$D28)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$D28)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$D28)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$D28)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="42">
         <f>IFERROR(M28/I28,"")</f>
         <v/>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="42">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$D28)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$D28)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$D28)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$D28)</f>
         <v/>
       </c>
-      <c r="N28" s="29">
+      <c r="N28" s="40">
         <f>IF(I28=0,"",IF(ROUND(L28,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L28)*I28,"0.00")))</f>
         <v/>
       </c>
-      <c r="O28" s="37" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 4 hrs</t>
+      <c r="O28" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 3.5 hrs</t>
         </is>
       </c>
       <c r="P28" s="24" t="n"/>
@@ -2230,106 +2059,139 @@
       <c r="T28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="A29" s="39" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C29" s="28" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
-        <is>
-          <t>Aware Super AV Maintenance [ONS]</t>
-        </is>
-      </c>
-      <c r="E29" s="29" t="inlineStr">
-        <is>
-          <t>11:30 AM</t>
-        </is>
-      </c>
-      <c r="F29" s="29" t="inlineStr">
-        <is>
-          <t>3:30 PM</t>
-        </is>
-      </c>
-      <c r="G29" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="I29" s="30">
+      <c r="C29" s="39" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t>PWC National Pool of Hours [ONS]</t>
+        </is>
+      </c>
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>12:00-1:00</t>
+        </is>
+      </c>
+      <c r="H29" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" s="41">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$D29)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$D29)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$D29)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$D29)</f>
         <v/>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="41">
         <f>H29-I29</f>
         <v/>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="40">
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$D29)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$D29)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$D29)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$D29)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L29" s="31">
+      <c r="L29" s="42">
         <f>IFERROR(M29/I29,"")</f>
         <v/>
       </c>
-      <c r="M29" s="31">
+      <c r="M29" s="42">
         <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$D29)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$D29)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$D29)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$D29)</f>
         <v/>
       </c>
-      <c r="N29" s="29">
+      <c r="N29" s="40">
         <f>IF(I29=0,"",IF(ROUND(L29,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L29)*I29,"0.00")))</f>
         <v/>
       </c>
-      <c r="O29" s="37" t="inlineStr"/>
+      <c r="O29" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 4 hrs</t>
+        </is>
+      </c>
       <c r="P29" s="24" t="n"/>
       <c r="Q29" s="24" t="n"/>
       <c r="R29" s="24" t="n"/>
       <c r="S29" s="24" t="n"/>
       <c r="T29" s="24" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="n"/>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="33" t="n"/>
-      <c r="E30" s="33" t="n"/>
-      <c r="F30" s="33" t="n"/>
-      <c r="G30" s="33" t="n"/>
-      <c r="H30" s="35">
-        <f>SUM(H14:H29)</f>
-        <v/>
-      </c>
-      <c r="I30" s="35">
-        <f>SUM(I14:I29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="35">
-        <f>SUM(J14:J29)</f>
-        <v/>
-      </c>
-      <c r="K30" s="33" t="n"/>
-      <c r="L30" s="33" t="n"/>
-      <c r="M30" s="36">
-        <f>SUM(M14:M29)</f>
-        <v/>
-      </c>
-      <c r="N30" s="33">
-        <f>IF(ROUND(J30,2)=0,"HOURS AGREE","VARIANCE")</f>
-        <v/>
-      </c>
-      <c r="O30" s="33" t="n"/>
+    <row r="30" ht="30" customHeight="1" s="12">
+      <c r="A30" s="28" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>DTTL Mel Tech FT 1 [ONS]</t>
+        </is>
+      </c>
+      <c r="E30" s="29" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G30" s="29" t="inlineStr">
+        <is>
+          <t>12:00-12:30</t>
+        </is>
+      </c>
+      <c r="H30" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="I30" s="31">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$D30)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$D30)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$D30)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$D30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="31">
+        <f>H30-I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="29">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$D30)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$D30)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$D30)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$D30)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+        <v/>
+      </c>
+      <c r="L30" s="33">
+        <f>IFERROR(M30/I30,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="33">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$D30)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$D30)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$D30)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$D30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="29">
+        <f>IF(I30=0,"",IF(ROUND(L30,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L30)*I30,"0.00")))</f>
+        <v/>
+      </c>
+      <c r="O30" s="49" t="inlineStr">
+        <is>
+          <t>QUERY - claimed missing. PAID IN FULL in the 20 Sep 2026 run as 3.5 + 4.5 hrs, $300.00 gross. See Section A.</t>
+        </is>
+      </c>
       <c r="P30" s="24" t="n"/>
       <c r="Q30" s="24" t="n"/>
       <c r="R30" s="24" t="n"/>
@@ -2337,21 +2199,69 @@
       <c r="T30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="n"/>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="24" t="n"/>
-      <c r="I31" s="24" t="n"/>
-      <c r="J31" s="24" t="n"/>
-      <c r="K31" s="24" t="n"/>
-      <c r="L31" s="24" t="n"/>
-      <c r="M31" s="24" t="n"/>
-      <c r="N31" s="24" t="n"/>
-      <c r="O31" s="24" t="n"/>
+      <c r="A31" s="39" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C31" s="39" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>DTTL Mel Tech FT 1 [ONS]</t>
+        </is>
+      </c>
+      <c r="E31" s="40" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>12:00-12:30</t>
+        </is>
+      </c>
+      <c r="H31" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I31" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$D31)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$D31)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$D31)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$D31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="41">
+        <f>H31-I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="40">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$D31)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$D31)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$D31)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$D31)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+        <v/>
+      </c>
+      <c r="L31" s="42">
+        <f>IFERROR(M31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="42">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$D31)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$D31)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$D31)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$D31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="40">
+        <f>IF(I31=0,"",IF(ROUND(L31,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L31)*I31,"0.00")))</f>
+        <v/>
+      </c>
+      <c r="O31" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 3.5 + 4.5 hrs</t>
+        </is>
+      </c>
       <c r="P31" s="24" t="n"/>
       <c r="Q31" s="24" t="n"/>
       <c r="R31" s="24" t="n"/>
@@ -2359,72 +2269,139 @@
       <c r="T31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>C.  PAY RATE ERROR AND CORRECTION  -  fortnight ending 07/08/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
-      <c r="H32" s="26" t="n"/>
-      <c r="I32" s="26" t="n"/>
-      <c r="J32" s="26" t="n"/>
-      <c r="K32" s="26" t="n"/>
-      <c r="L32" s="26" t="n"/>
-      <c r="M32" s="26" t="n"/>
-      <c r="N32" s="26" t="n"/>
-      <c r="O32" s="26" t="n"/>
+      <c r="A32" s="39" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C32" s="39" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t>DTTL Mel Tech FT 1 [ONS]</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>12:00-12:30</t>
+        </is>
+      </c>
+      <c r="H32" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I32" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$D32)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$D32)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$D32)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$D32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="41">
+        <f>H32-I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="40">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$D32)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$D32)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$D32)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$D32)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+        <v/>
+      </c>
+      <c r="L32" s="42">
+        <f>IFERROR(M32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="42">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$D32)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$D32)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$D32)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$D32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="40">
+        <f>IF(I32=0,"",IF(ROUND(L32,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L32)*I32,"0.00")))</f>
+        <v/>
+      </c>
+      <c r="O32" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 3 + 5 hrs</t>
+        </is>
+      </c>
       <c r="P32" s="24" t="n"/>
       <c r="Q32" s="24" t="n"/>
       <c r="R32" s="24" t="n"/>
       <c r="S32" s="24" t="n"/>
       <c r="T32" s="24" t="n"/>
     </row>
-    <row r="33" ht="30" customHeight="1" s="12">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>Pay Run</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>Hours</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="inlineStr">
-        <is>
-          <t>Rate
-$/hr</t>
-        </is>
-      </c>
-      <c r="E33" s="27" t="inlineStr">
-        <is>
-          <t>Gross $</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="G33" s="24" t="n"/>
-      <c r="H33" s="24" t="n"/>
-      <c r="I33" s="24" t="n"/>
-      <c r="J33" s="24" t="n"/>
-      <c r="K33" s="24" t="n"/>
-      <c r="L33" s="24" t="n"/>
-      <c r="M33" s="24" t="n"/>
-      <c r="N33" s="24" t="n"/>
-      <c r="O33" s="24" t="n"/>
+    <row r="33">
+      <c r="A33" s="39" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C33" s="39" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>DTTL Mel Tech FT 1 [ONS]</t>
+        </is>
+      </c>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>12:00-12:30</t>
+        </is>
+      </c>
+      <c r="H33" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$D33)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$D33)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$D33)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$D33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="41">
+        <f>H33-I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="40">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$D33)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$D33)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$D33)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$D33)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+        <v/>
+      </c>
+      <c r="L33" s="42">
+        <f>IFERROR(M33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="42">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$D33)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$D33)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$D33)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$D33)</f>
+        <v/>
+      </c>
+      <c r="N33" s="40">
+        <f>IF(I33=0,"",IF(ROUND(L33,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L33)*I33,"0.00")))</f>
+        <v/>
+      </c>
+      <c r="O33" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 3 + 5 hrs</t>
+        </is>
+      </c>
       <c r="P33" s="24" t="n"/>
       <c r="Q33" s="24" t="n"/>
       <c r="R33" s="24" t="n"/>
@@ -2432,41 +2409,69 @@
       <c r="T33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>Paid at incorrect rate</t>
-        </is>
-      </c>
-      <c r="B34" s="32" t="inlineStr">
-        <is>
-          <t>07 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C34" s="30">
-        <f>'07 Aug 2026'!G3+'07 Aug 2026'!G4+'07 Aug 2026'!G5+'07 Aug 2026'!G6</f>
-        <v/>
-      </c>
-      <c r="D34" s="31" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="E34" s="31">
-        <f>SUM('07 Aug 2026'!O3:O6)</f>
-        <v/>
-      </c>
-      <c r="F34" s="37" t="inlineStr">
-        <is>
-          <t>Original payment - rate used was $35.15/hr</t>
-        </is>
-      </c>
-      <c r="G34" s="24" t="n"/>
-      <c r="H34" s="24" t="n"/>
-      <c r="I34" s="24" t="n"/>
-      <c r="J34" s="24" t="n"/>
-      <c r="K34" s="24" t="n"/>
-      <c r="L34" s="24" t="n"/>
-      <c r="M34" s="24" t="n"/>
-      <c r="N34" s="24" t="n"/>
-      <c r="O34" s="24" t="n"/>
+      <c r="A34" s="39" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C34" s="39" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>DTTL Mel Tech FT 1 [ONS]</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>12:00-12:30</t>
+        </is>
+      </c>
+      <c r="H34" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I34" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$D34)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$D34)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$D34)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$D34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="41">
+        <f>H34-I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="40">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$D34)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$D34)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$D34)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$D34)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+        <v/>
+      </c>
+      <c r="L34" s="42">
+        <f>IFERROR(M34/I34,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="42">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$D34)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$D34)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$D34)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$D34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="40">
+        <f>IF(I34=0,"",IF(ROUND(L34,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L34)*I34,"0.00")))</f>
+        <v/>
+      </c>
+      <c r="O34" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 3.5 + 4.5 hrs</t>
+        </is>
+      </c>
       <c r="P34" s="24" t="n"/>
       <c r="Q34" s="24" t="n"/>
       <c r="R34" s="24" t="n"/>
@@ -2474,41 +2479,69 @@
       <c r="T34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>Should have been paid</t>
-        </is>
-      </c>
-      <c r="B35" s="32" t="inlineStr">
-        <is>
-          <t>07 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C35" s="30">
-        <f>C34</f>
-        <v/>
-      </c>
-      <c r="D35" s="31" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="E35" s="31">
-        <f>C35*D35</f>
-        <v/>
-      </c>
-      <c r="F35" s="37" t="inlineStr">
-        <is>
-          <t>Correct casual ordinary rate is $37.50/hr</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="n"/>
-      <c r="H35" s="24" t="n"/>
-      <c r="I35" s="24" t="n"/>
-      <c r="J35" s="24" t="n"/>
-      <c r="K35" s="24" t="n"/>
-      <c r="L35" s="24" t="n"/>
-      <c r="M35" s="24" t="n"/>
-      <c r="N35" s="24" t="n"/>
-      <c r="O35" s="24" t="n"/>
+      <c r="A35" s="39" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C35" s="39" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>PWC National Pool of Hours [ONS]</t>
+        </is>
+      </c>
+      <c r="E35" s="40" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>12:00-1:00</t>
+        </is>
+      </c>
+      <c r="H35" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$D35)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$D35)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$D35)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$D35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="41">
+        <f>H35-I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="40">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$D35)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$D35)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$D35)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$D35)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+        <v/>
+      </c>
+      <c r="L35" s="42">
+        <f>IFERROR(M35/I35,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="42">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$D35)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$D35)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$D35)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$D35)</f>
+        <v/>
+      </c>
+      <c r="N35" s="40">
+        <f>IF(I35=0,"",IF(ROUND(L35,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L35)*I35,"0.00")))</f>
+        <v/>
+      </c>
+      <c r="O35" s="48" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 4 hrs</t>
+        </is>
+      </c>
       <c r="P35" s="24" t="n"/>
       <c r="Q35" s="24" t="n"/>
       <c r="R35" s="24" t="n"/>
@@ -2516,32 +2549,65 @@
       <c r="T35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="inlineStr">
-        <is>
-          <t>Underpayment</t>
-        </is>
-      </c>
-      <c r="B36" s="38" t="inlineStr"/>
-      <c r="C36" s="39" t="inlineStr"/>
-      <c r="D36" s="40" t="inlineStr"/>
-      <c r="E36" s="40">
-        <f>E35-E34</f>
-        <v/>
-      </c>
-      <c r="F36" s="41" t="inlineStr">
-        <is>
-          <t>Shortfall on the first fortnight</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
-      <c r="I36" s="24" t="n"/>
-      <c r="J36" s="24" t="n"/>
-      <c r="K36" s="24" t="n"/>
-      <c r="L36" s="24" t="n"/>
-      <c r="M36" s="24" t="n"/>
-      <c r="N36" s="24" t="n"/>
-      <c r="O36" s="24" t="n"/>
+      <c r="A36" s="39" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D36" s="43" t="inlineStr">
+        <is>
+          <t>Aware Super AV Maintenance [ONS]</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="41">
+        <f>H36-I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="40">
+        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+        <v/>
+      </c>
+      <c r="L36" s="42">
+        <f>IFERROR(M36/I36,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="42">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)</f>
+        <v/>
+      </c>
+      <c r="N36" s="40">
+        <f>IF(I36=0,"",IF(ROUND(L36,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L36)*I36,"0.00")))</f>
+        <v/>
+      </c>
+      <c r="O36" s="48" t="inlineStr"/>
       <c r="P36" s="24" t="n"/>
       <c r="Q36" s="24" t="n"/>
       <c r="R36" s="24" t="n"/>
@@ -2549,42 +2615,40 @@
       <c r="T36" s="24" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>Reversal of incorrect rate</t>
-        </is>
-      </c>
-      <c r="B37" s="32" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C37" s="30">
-        <f>'21 Aug 2026'!G3</f>
-        <v/>
-      </c>
-      <c r="D37" s="31">
-        <f>'21 Aug 2026'!M3</f>
-        <v/>
-      </c>
-      <c r="E37" s="31">
-        <f>'21 Aug 2026'!O3</f>
-        <v/>
-      </c>
-      <c r="F37" s="37" t="inlineStr">
-        <is>
-          <t>Payroll reversed the full 16 hrs at $35.15</t>
-        </is>
-      </c>
-      <c r="G37" s="24" t="n"/>
-      <c r="H37" s="24" t="n"/>
-      <c r="I37" s="24" t="n"/>
-      <c r="J37" s="24" t="n"/>
-      <c r="K37" s="24" t="n"/>
-      <c r="L37" s="24" t="n"/>
-      <c r="M37" s="24" t="n"/>
-      <c r="N37" s="24" t="n"/>
-      <c r="O37" s="24" t="n"/>
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B37" s="44" t="n"/>
+      <c r="C37" s="44" t="n"/>
+      <c r="D37" s="44" t="n"/>
+      <c r="E37" s="44" t="n"/>
+      <c r="F37" s="44" t="n"/>
+      <c r="G37" s="44" t="n"/>
+      <c r="H37" s="46">
+        <f>SUM(H21:H36)</f>
+        <v/>
+      </c>
+      <c r="I37" s="46">
+        <f>SUM(I21:I36)</f>
+        <v/>
+      </c>
+      <c r="J37" s="46">
+        <f>SUM(J21:J36)</f>
+        <v/>
+      </c>
+      <c r="K37" s="44" t="n"/>
+      <c r="L37" s="44" t="n"/>
+      <c r="M37" s="47">
+        <f>SUM(M21:M36)</f>
+        <v/>
+      </c>
+      <c r="N37" s="44">
+        <f>IF(ROUND(J37,2)=0,"HOURS AGREE","VARIANCE")</f>
+        <v/>
+      </c>
+      <c r="O37" s="44" t="n"/>
       <c r="P37" s="24" t="n"/>
       <c r="Q37" s="24" t="n"/>
       <c r="R37" s="24" t="n"/>
@@ -2592,33 +2656,12 @@
       <c r="T37" s="24" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
-        <is>
-          <t>Re-paid at correct rate</t>
-        </is>
-      </c>
-      <c r="B38" s="32" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C38" s="30">
-        <f>'21 Aug 2026'!G4</f>
-        <v/>
-      </c>
-      <c r="D38" s="31">
-        <f>'21 Aug 2026'!M4</f>
-        <v/>
-      </c>
-      <c r="E38" s="31">
-        <f>'21 Aug 2026'!O4</f>
-        <v/>
-      </c>
-      <c r="F38" s="37" t="inlineStr">
-        <is>
-          <t>Re-paid the same 16 hrs at $37.50</t>
-        </is>
-      </c>
+      <c r="A38" s="24" t="n"/>
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="24" t="n"/>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="24" t="n"/>
       <c r="G38" s="24" t="n"/>
       <c r="H38" s="24" t="n"/>
       <c r="I38" s="24" t="n"/>
@@ -2635,61 +2678,61 @@
       <c r="T38" s="24" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
-        <is>
-          <t>Net correction received</t>
-        </is>
-      </c>
-      <c r="B39" s="32" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C39" s="30">
-        <f>C37+C38</f>
-        <v/>
-      </c>
-      <c r="D39" s="31" t="inlineStr"/>
-      <c r="E39" s="31">
-        <f>E37+E38</f>
-        <v/>
-      </c>
-      <c r="F39" s="37" t="inlineStr">
-        <is>
-          <t>Net hours effect is nil - this is a rate top-up only</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
-      <c r="I39" s="24" t="n"/>
-      <c r="J39" s="24" t="n"/>
-      <c r="K39" s="24" t="n"/>
-      <c r="L39" s="24" t="n"/>
-      <c r="M39" s="24" t="n"/>
-      <c r="N39" s="24" t="n"/>
-      <c r="O39" s="24" t="n"/>
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>D.  PAY RATE ERROR AND CORRECTION  -  fortnight ending 07/08/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="38" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="38" t="n"/>
+      <c r="H39" s="38" t="n"/>
+      <c r="I39" s="38" t="n"/>
+      <c r="J39" s="38" t="n"/>
+      <c r="K39" s="38" t="n"/>
+      <c r="L39" s="38" t="n"/>
+      <c r="M39" s="38" t="n"/>
+      <c r="N39" s="38" t="n"/>
+      <c r="O39" s="38" t="n"/>
       <c r="P39" s="24" t="n"/>
       <c r="Q39" s="24" t="n"/>
       <c r="R39" s="24" t="n"/>
       <c r="S39" s="24" t="n"/>
       <c r="T39" s="24" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="33" t="inlineStr">
-        <is>
-          <t>AMOUNT STILL OWING</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr"/>
-      <c r="C40" s="35" t="inlineStr"/>
-      <c r="D40" s="36" t="inlineStr"/>
-      <c r="E40" s="36">
-        <f>E36-E39</f>
-        <v/>
-      </c>
-      <c r="F40" s="42" t="inlineStr">
-        <is>
-          <t>Nil = the underpayment has been fully corrected</t>
+    <row r="40" ht="30" customHeight="1" s="12">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Pay Run</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>Rate
+$/hr</t>
+        </is>
+      </c>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>Gross $</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
       <c r="G40" s="24" t="n"/>
@@ -2707,368 +2750,1332 @@
       <c r="S40" s="24" t="n"/>
       <c r="T40" s="24" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Paid at incorrect rate</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C41" s="41">
+        <f>'07 Aug 2026'!G3+'07 Aug 2026'!G4+'07 Aug 2026'!G5+'07 Aug 2026'!G6</f>
+        <v/>
+      </c>
+      <c r="D41" s="42" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="E41" s="42">
+        <f>SUM('07 Aug 2026'!O3:O6)</f>
+        <v/>
+      </c>
+      <c r="F41" s="48" t="inlineStr">
+        <is>
+          <t>Original payment - rate used was $35.15/hr</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="n"/>
+      <c r="H41" s="24" t="n"/>
+      <c r="I41" s="24" t="n"/>
+      <c r="J41" s="24" t="n"/>
+      <c r="K41" s="24" t="n"/>
+      <c r="L41" s="24" t="n"/>
+      <c r="M41" s="24" t="n"/>
+      <c r="N41" s="24" t="n"/>
+      <c r="O41" s="24" t="n"/>
+      <c r="P41" s="24" t="n"/>
+      <c r="Q41" s="24" t="n"/>
+      <c r="R41" s="24" t="n"/>
+      <c r="S41" s="24" t="n"/>
+      <c r="T41" s="24" t="n"/>
+    </row>
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>D.  COMPLETENESS CHECK  -  proves nothing paid sits outside this reconciliation, on hours and on dollars</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="43" t="n"/>
-      <c r="E42" s="43" t="n"/>
-      <c r="F42" s="43" t="n"/>
-      <c r="G42" s="43" t="n"/>
-      <c r="H42" s="43" t="n"/>
-      <c r="I42" s="43" t="n"/>
-      <c r="J42" s="43" t="n"/>
-      <c r="K42" s="43" t="n"/>
-      <c r="L42" s="43" t="n"/>
-      <c r="M42" s="43" t="n"/>
-      <c r="N42" s="43" t="n"/>
-      <c r="O42" s="43" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1" s="12">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="inlineStr">
-        <is>
-          <t>Hours</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="inlineStr">
-        <is>
-          <t>Gross $</t>
-        </is>
-      </c>
-      <c r="D43" s="27" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
+          <t>Should have been paid</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C42" s="41">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="D42" s="42" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E42" s="42">
+        <f>C42*D42</f>
+        <v/>
+      </c>
+      <c r="F42" s="48" t="inlineStr">
+        <is>
+          <t>Correct casual ordinary rate is $37.50/hr</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="n"/>
+      <c r="H42" s="24" t="n"/>
+      <c r="I42" s="24" t="n"/>
+      <c r="J42" s="24" t="n"/>
+      <c r="K42" s="24" t="n"/>
+      <c r="L42" s="24" t="n"/>
+      <c r="M42" s="24" t="n"/>
+      <c r="N42" s="24" t="n"/>
+      <c r="O42" s="24" t="n"/>
+      <c r="P42" s="24" t="n"/>
+      <c r="Q42" s="24" t="n"/>
+      <c r="R42" s="24" t="n"/>
+      <c r="S42" s="24" t="n"/>
+      <c r="T42" s="24" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="50" t="inlineStr">
+        <is>
+          <t>Underpayment</t>
+        </is>
+      </c>
+      <c r="B43" s="50" t="inlineStr"/>
+      <c r="C43" s="51" t="inlineStr"/>
+      <c r="D43" s="52" t="inlineStr"/>
+      <c r="E43" s="52">
+        <f>E42-E41</f>
+        <v/>
+      </c>
+      <c r="F43" s="53" t="inlineStr">
+        <is>
+          <t>Shortfall on the first fortnight</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="n"/>
+      <c r="H43" s="24" t="n"/>
+      <c r="I43" s="24" t="n"/>
+      <c r="J43" s="24" t="n"/>
+      <c r="K43" s="24" t="n"/>
+      <c r="L43" s="24" t="n"/>
+      <c r="M43" s="24" t="n"/>
+      <c r="N43" s="24" t="n"/>
+      <c r="O43" s="24" t="n"/>
+      <c r="P43" s="24" t="n"/>
+      <c r="Q43" s="24" t="n"/>
+      <c r="R43" s="24" t="n"/>
+      <c r="S43" s="24" t="n"/>
+      <c r="T43" s="24" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="inlineStr">
-        <is>
-          <t>Total on all four pay-run tabs (including the +/-16 hr rate reversal)</t>
-        </is>
-      </c>
-      <c r="B44" s="45">
-        <f>SUM('07 Aug 2026'!$G$3:$G$6)+SUM('21 Aug 2026'!$G$3:$G$7)+SUM('20 Sept 2026 '!$G$3:$G$14)+SUM('22 Sep 2026'!$G$3:$G$11)</f>
-        <v/>
-      </c>
-      <c r="C44" s="46">
-        <f>SUM('07 Aug 2026'!$O$3:$O$6)+SUM('21 Aug 2026'!$O$3:$O$7)+SUM('20 Sept 2026 '!$O$3:$O$14)+SUM('22 Sep 2026'!$O$3:$O$11)</f>
-        <v/>
-      </c>
-      <c r="D44" s="37" t="inlineStr"/>
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Reversal of incorrect rate</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>21 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C44" s="41">
+        <f>'21 Aug 2026'!G3</f>
+        <v/>
+      </c>
+      <c r="D44" s="42">
+        <f>'21 Aug 2026'!M3</f>
+        <v/>
+      </c>
+      <c r="E44" s="42">
+        <f>'21 Aug 2026'!O3</f>
+        <v/>
+      </c>
+      <c r="F44" s="48" t="inlineStr">
+        <is>
+          <t>Payroll reversed the full 16 hrs at $35.15</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="24" t="n"/>
+      <c r="I44" s="24" t="n"/>
+      <c r="J44" s="24" t="n"/>
+      <c r="K44" s="24" t="n"/>
+      <c r="L44" s="24" t="n"/>
+      <c r="M44" s="24" t="n"/>
+      <c r="N44" s="24" t="n"/>
+      <c r="O44" s="24" t="n"/>
+      <c r="P44" s="24" t="n"/>
+      <c r="Q44" s="24" t="n"/>
+      <c r="R44" s="24" t="n"/>
+      <c r="S44" s="24" t="n"/>
+      <c r="T44" s="24" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="44" t="inlineStr">
-        <is>
-          <t>Total matched to a timesheet line in Section B</t>
-        </is>
-      </c>
-      <c r="B45" s="45">
-        <f>I30</f>
-        <v/>
-      </c>
-      <c r="C45" s="46">
-        <f>M30</f>
-        <v/>
-      </c>
-      <c r="D45" s="37" t="inlineStr"/>
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Re-paid at correct rate</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="inlineStr">
+        <is>
+          <t>21 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C45" s="41">
+        <f>'21 Aug 2026'!G4</f>
+        <v/>
+      </c>
+      <c r="D45" s="42">
+        <f>'21 Aug 2026'!M4</f>
+        <v/>
+      </c>
+      <c r="E45" s="42">
+        <f>'21 Aug 2026'!O4</f>
+        <v/>
+      </c>
+      <c r="F45" s="48" t="inlineStr">
+        <is>
+          <t>Re-paid the same 16 hrs at $37.50</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="24" t="n"/>
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="24" t="n"/>
+      <c r="K45" s="24" t="n"/>
+      <c r="L45" s="24" t="n"/>
+      <c r="M45" s="24" t="n"/>
+      <c r="N45" s="24" t="n"/>
+      <c r="O45" s="24" t="n"/>
+      <c r="P45" s="24" t="n"/>
+      <c r="Q45" s="24" t="n"/>
+      <c r="R45" s="24" t="n"/>
+      <c r="S45" s="24" t="n"/>
+      <c r="T45" s="24" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="44" t="inlineStr">
-        <is>
-          <t>Difference - rate-correction adjustment, no work date attached</t>
-        </is>
-      </c>
-      <c r="B46" s="45">
-        <f>B44-B45</f>
-        <v/>
-      </c>
-      <c r="C46" s="46">
-        <f>C44-C45</f>
-        <v/>
-      </c>
-      <c r="D46" s="37">
-        <f>IF(ROUND(B46,2)=0,"OK - nil unmatched hours; $"&amp;TEXT(C46,"0.00")&amp;" is the rate top-up per Section C","INVESTIGATE - unmatched paid hours")</f>
-        <v/>
-      </c>
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Net correction received</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>21 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="41">
+        <f>C44+C45</f>
+        <v/>
+      </c>
+      <c r="D46" s="42" t="inlineStr"/>
+      <c r="E46" s="42">
+        <f>E44+E45</f>
+        <v/>
+      </c>
+      <c r="F46" s="48" t="inlineStr">
+        <is>
+          <t>Net hours effect is nil - this is a rate top-up only</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="n"/>
+      <c r="H46" s="24" t="n"/>
+      <c r="I46" s="24" t="n"/>
+      <c r="J46" s="24" t="n"/>
+      <c r="K46" s="24" t="n"/>
+      <c r="L46" s="24" t="n"/>
+      <c r="M46" s="24" t="n"/>
+      <c r="N46" s="24" t="n"/>
+      <c r="O46" s="24" t="n"/>
+      <c r="P46" s="24" t="n"/>
+      <c r="Q46" s="24" t="n"/>
+      <c r="R46" s="24" t="n"/>
+      <c r="S46" s="24" t="n"/>
+      <c r="T46" s="24" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>Total timesheet hours per the screenshots</t>
-        </is>
-      </c>
-      <c r="B47" s="45">
-        <f>H30</f>
-        <v/>
-      </c>
+          <t>AMOUNT STILL OWING</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="inlineStr"/>
       <c r="C47" s="46" t="inlineStr"/>
-      <c r="D47" s="37" t="inlineStr"/>
+      <c r="D47" s="47" t="inlineStr"/>
+      <c r="E47" s="47">
+        <f>E43-E46</f>
+        <v/>
+      </c>
+      <c r="F47" s="54" t="inlineStr">
+        <is>
+          <t>Nil = the underpayment has been fully corrected</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="24" t="n"/>
+      <c r="I47" s="24" t="n"/>
+      <c r="J47" s="24" t="n"/>
+      <c r="K47" s="24" t="n"/>
+      <c r="L47" s="24" t="n"/>
+      <c r="M47" s="24" t="n"/>
+      <c r="N47" s="24" t="n"/>
+      <c r="O47" s="24" t="n"/>
+      <c r="P47" s="24" t="n"/>
+      <c r="Q47" s="24" t="n"/>
+      <c r="R47" s="24" t="n"/>
+      <c r="S47" s="24" t="n"/>
+      <c r="T47" s="24" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="33" t="inlineStr">
-        <is>
-          <t>HOURS VARIANCE (timesheet less paid)</t>
-        </is>
-      </c>
-      <c r="B48" s="35">
-        <f>B47-B45</f>
-        <v/>
-      </c>
-      <c r="C48" s="36" t="inlineStr"/>
-      <c r="D48" s="42">
-        <f>IF(ROUND(B48,2)=0,"FULLY RECONCILED - nil hours variance","VARIANCE - investigate")</f>
-        <v/>
-      </c>
+      <c r="A48" s="24" t="n"/>
+      <c r="B48" s="24" t="n"/>
+      <c r="C48" s="24" t="n"/>
+      <c r="D48" s="24" t="n"/>
+      <c r="E48" s="24" t="n"/>
+      <c r="F48" s="24" t="n"/>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="24" t="n"/>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="24" t="n"/>
+      <c r="K48" s="24" t="n"/>
+      <c r="L48" s="24" t="n"/>
+      <c r="M48" s="24" t="n"/>
+      <c r="N48" s="24" t="n"/>
+      <c r="O48" s="24" t="n"/>
+      <c r="P48" s="24" t="n"/>
+      <c r="Q48" s="24" t="n"/>
+      <c r="R48" s="24" t="n"/>
+      <c r="S48" s="24" t="n"/>
+      <c r="T48" s="24" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="44" t="inlineStr">
-        <is>
-          <t>Gross that should have been paid (timesheet hours x $37.50)</t>
-        </is>
-      </c>
-      <c r="B49" s="45" t="inlineStr"/>
-      <c r="C49" s="46">
-        <f>B47*37.5</f>
-        <v/>
-      </c>
-      <c r="D49" s="37" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="44" t="inlineStr">
-        <is>
-          <t>Gross actually paid across all pay runs (after the rate correction)</t>
-        </is>
-      </c>
-      <c r="B50" s="45" t="inlineStr"/>
-      <c r="C50" s="46">
-        <f>C44</f>
-        <v/>
-      </c>
-      <c r="D50" s="37" t="inlineStr"/>
+      <c r="A49" s="38" t="inlineStr">
+        <is>
+          <t>E.  COMPLETENESS CHECK  -  proves nothing paid sits outside this reconciliation, on hours and on dollars</t>
+        </is>
+      </c>
+      <c r="B49" s="38" t="n"/>
+      <c r="C49" s="38" t="n"/>
+      <c r="D49" s="38" t="n"/>
+      <c r="E49" s="38" t="n"/>
+      <c r="F49" s="38" t="n"/>
+      <c r="G49" s="38" t="n"/>
+      <c r="H49" s="38" t="n"/>
+      <c r="I49" s="38" t="n"/>
+      <c r="J49" s="38" t="n"/>
+      <c r="K49" s="38" t="n"/>
+      <c r="L49" s="38" t="n"/>
+      <c r="M49" s="38" t="n"/>
+      <c r="N49" s="38" t="n"/>
+      <c r="O49" s="38" t="n"/>
+      <c r="P49" s="24" t="n"/>
+      <c r="Q49" s="24" t="n"/>
+      <c r="R49" s="24" t="n"/>
+      <c r="S49" s="24" t="n"/>
+      <c r="T49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1" s="12">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="inlineStr">
+        <is>
+          <t>Gross $</t>
+        </is>
+      </c>
+      <c r="D50" s="27" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="n"/>
+      <c r="F50" s="24" t="n"/>
+      <c r="G50" s="24" t="n"/>
+      <c r="H50" s="24" t="n"/>
+      <c r="I50" s="24" t="n"/>
+      <c r="J50" s="24" t="n"/>
+      <c r="K50" s="24" t="n"/>
+      <c r="L50" s="24" t="n"/>
+      <c r="M50" s="24" t="n"/>
+      <c r="N50" s="24" t="n"/>
+      <c r="O50" s="24" t="n"/>
+      <c r="P50" s="24" t="n"/>
+      <c r="Q50" s="24" t="n"/>
+      <c r="R50" s="24" t="n"/>
+      <c r="S50" s="24" t="n"/>
+      <c r="T50" s="24" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="inlineStr">
-        <is>
-          <t>DOLLAR VARIANCE (should have been paid less actually paid)</t>
-        </is>
-      </c>
-      <c r="B51" s="35" t="inlineStr"/>
-      <c r="C51" s="36">
-        <f>C49-C50</f>
-        <v/>
-      </c>
-      <c r="D51" s="42">
-        <f>IF(ROUND(C51,2)=0,"FULLY RECONCILED - nil dollar variance","VARIANCE - investigate")</f>
-        <v/>
-      </c>
+      <c r="A51" s="43" t="inlineStr">
+        <is>
+          <t>Total on all four pay-run tabs (including the +/-16 hr rate reversal)</t>
+        </is>
+      </c>
+      <c r="B51" s="41">
+        <f>SUM('07 Aug 2026'!$G$3:$G$6)+SUM('21 Aug 2026'!$G$3:$G$7)+SUM('20 Sept 2026 '!$G$3:$G$14)+SUM('22 Sep 2026'!$G$3:$G$11)</f>
+        <v/>
+      </c>
+      <c r="C51" s="42">
+        <f>SUM('07 Aug 2026'!$O$3:$O$6)+SUM('21 Aug 2026'!$O$3:$O$7)+SUM('20 Sept 2026 '!$O$3:$O$14)+SUM('22 Sep 2026'!$O$3:$O$11)</f>
+        <v/>
+      </c>
+      <c r="D51" s="48" t="inlineStr"/>
+      <c r="E51" s="24" t="n"/>
+      <c r="F51" s="24" t="n"/>
+      <c r="G51" s="24" t="n"/>
+      <c r="H51" s="24" t="n"/>
+      <c r="I51" s="24" t="n"/>
+      <c r="J51" s="24" t="n"/>
+      <c r="K51" s="24" t="n"/>
+      <c r="L51" s="24" t="n"/>
+      <c r="M51" s="24" t="n"/>
+      <c r="N51" s="24" t="n"/>
+      <c r="O51" s="24" t="n"/>
+      <c r="P51" s="24" t="n"/>
+      <c r="Q51" s="24" t="n"/>
+      <c r="R51" s="24" t="n"/>
+      <c r="S51" s="24" t="n"/>
+      <c r="T51" s="24" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
+          <t>Total matched to a timesheet line in Section C</t>
+        </is>
+      </c>
+      <c r="B52" s="41">
+        <f>I37</f>
+        <v/>
+      </c>
+      <c r="C52" s="42">
+        <f>M37</f>
+        <v/>
+      </c>
+      <c r="D52" s="48" t="inlineStr"/>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="24" t="n"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="24" t="n"/>
+      <c r="I52" s="24" t="n"/>
+      <c r="J52" s="24" t="n"/>
+      <c r="K52" s="24" t="n"/>
+      <c r="L52" s="24" t="n"/>
+      <c r="M52" s="24" t="n"/>
+      <c r="N52" s="24" t="n"/>
+      <c r="O52" s="24" t="n"/>
+      <c r="P52" s="24" t="n"/>
+      <c r="Q52" s="24" t="n"/>
+      <c r="R52" s="24" t="n"/>
+      <c r="S52" s="24" t="n"/>
+      <c r="T52" s="24" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="43" t="inlineStr">
         <is>
-          <t>E.  FINDINGS</t>
-        </is>
-      </c>
-      <c r="B53" s="43" t="n"/>
-      <c r="C53" s="43" t="n"/>
-      <c r="D53" s="43" t="n"/>
-      <c r="E53" s="43" t="n"/>
-      <c r="F53" s="43" t="n"/>
-      <c r="G53" s="43" t="n"/>
-      <c r="H53" s="43" t="n"/>
-      <c r="I53" s="43" t="n"/>
-      <c r="J53" s="43" t="n"/>
-      <c r="K53" s="43" t="n"/>
-      <c r="L53" s="43" t="n"/>
-      <c r="M53" s="43" t="n"/>
-      <c r="N53" s="43" t="n"/>
-      <c r="O53" s="43" t="n"/>
+          <t>Difference - rate-correction adjustment, no work date attached</t>
+        </is>
+      </c>
+      <c r="B53" s="41">
+        <f>B51-B52</f>
+        <v/>
+      </c>
+      <c r="C53" s="42">
+        <f>C51-C52</f>
+        <v/>
+      </c>
+      <c r="D53" s="48">
+        <f>IF(ROUND(B53,2)=0,"OK - nil unmatched hours; $"&amp;TEXT(C53,"0.00")&amp;" is the rate top-up per Section D","INVESTIGATE - unmatched paid hours")</f>
+        <v/>
+      </c>
+      <c r="E53" s="24" t="n"/>
+      <c r="F53" s="24" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="24" t="n"/>
+      <c r="J53" s="24" t="n"/>
+      <c r="K53" s="24" t="n"/>
+      <c r="L53" s="24" t="n"/>
+      <c r="M53" s="24" t="n"/>
+      <c r="N53" s="24" t="n"/>
+      <c r="O53" s="24" t="n"/>
+      <c r="P53" s="24" t="n"/>
+      <c r="Q53" s="24" t="n"/>
+      <c r="R53" s="24" t="n"/>
+      <c r="S53" s="24" t="n"/>
+      <c r="T53" s="24" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="47" t="inlineStr">
+      <c r="A54" s="43" t="inlineStr">
+        <is>
+          <t>Total timesheet hours per the screenshots</t>
+        </is>
+      </c>
+      <c r="B54" s="41">
+        <f>H37</f>
+        <v/>
+      </c>
+      <c r="C54" s="42" t="inlineStr"/>
+      <c r="D54" s="48" t="inlineStr"/>
+      <c r="E54" s="24" t="n"/>
+      <c r="F54" s="24" t="n"/>
+      <c r="G54" s="24" t="n"/>
+      <c r="H54" s="24" t="n"/>
+      <c r="I54" s="24" t="n"/>
+      <c r="J54" s="24" t="n"/>
+      <c r="K54" s="24" t="n"/>
+      <c r="L54" s="24" t="n"/>
+      <c r="M54" s="24" t="n"/>
+      <c r="N54" s="24" t="n"/>
+      <c r="O54" s="24" t="n"/>
+      <c r="P54" s="24" t="n"/>
+      <c r="Q54" s="24" t="n"/>
+      <c r="R54" s="24" t="n"/>
+      <c r="S54" s="24" t="n"/>
+      <c r="T54" s="24" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>HOURS VARIANCE (timesheet less paid)</t>
+        </is>
+      </c>
+      <c r="B55" s="46">
+        <f>B54-B52</f>
+        <v/>
+      </c>
+      <c r="C55" s="47" t="inlineStr"/>
+      <c r="D55" s="54">
+        <f>IF(ROUND(B55,2)=0,"FULLY RECONCILED - nil hours variance","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="E55" s="24" t="n"/>
+      <c r="F55" s="24" t="n"/>
+      <c r="G55" s="24" t="n"/>
+      <c r="H55" s="24" t="n"/>
+      <c r="I55" s="24" t="n"/>
+      <c r="J55" s="24" t="n"/>
+      <c r="K55" s="24" t="n"/>
+      <c r="L55" s="24" t="n"/>
+      <c r="M55" s="24" t="n"/>
+      <c r="N55" s="24" t="n"/>
+      <c r="O55" s="24" t="n"/>
+      <c r="P55" s="24" t="n"/>
+      <c r="Q55" s="24" t="n"/>
+      <c r="R55" s="24" t="n"/>
+      <c r="S55" s="24" t="n"/>
+      <c r="T55" s="24" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="43" t="inlineStr">
+        <is>
+          <t>Gross that should have been paid (timesheet hours x $37.50)</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr"/>
+      <c r="C56" s="42">
+        <f>B54*37.5</f>
+        <v/>
+      </c>
+      <c r="D56" s="48" t="inlineStr"/>
+      <c r="E56" s="24" t="n"/>
+      <c r="F56" s="24" t="n"/>
+      <c r="G56" s="24" t="n"/>
+      <c r="H56" s="24" t="n"/>
+      <c r="I56" s="24" t="n"/>
+      <c r="J56" s="24" t="n"/>
+      <c r="K56" s="24" t="n"/>
+      <c r="L56" s="24" t="n"/>
+      <c r="M56" s="24" t="n"/>
+      <c r="N56" s="24" t="n"/>
+      <c r="O56" s="24" t="n"/>
+      <c r="P56" s="24" t="n"/>
+      <c r="Q56" s="24" t="n"/>
+      <c r="R56" s="24" t="n"/>
+      <c r="S56" s="24" t="n"/>
+      <c r="T56" s="24" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="43" t="inlineStr">
+        <is>
+          <t>Gross actually paid across all pay runs (after the rate correction)</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr"/>
+      <c r="C57" s="42">
+        <f>C51</f>
+        <v/>
+      </c>
+      <c r="D57" s="48" t="inlineStr"/>
+      <c r="E57" s="24" t="n"/>
+      <c r="F57" s="24" t="n"/>
+      <c r="G57" s="24" t="n"/>
+      <c r="H57" s="24" t="n"/>
+      <c r="I57" s="24" t="n"/>
+      <c r="J57" s="24" t="n"/>
+      <c r="K57" s="24" t="n"/>
+      <c r="L57" s="24" t="n"/>
+      <c r="M57" s="24" t="n"/>
+      <c r="N57" s="24" t="n"/>
+      <c r="O57" s="24" t="n"/>
+      <c r="P57" s="24" t="n"/>
+      <c r="Q57" s="24" t="n"/>
+      <c r="R57" s="24" t="n"/>
+      <c r="S57" s="24" t="n"/>
+      <c r="T57" s="24" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="inlineStr">
+        <is>
+          <t>DOLLAR VARIANCE (should have been paid less actually paid)</t>
+        </is>
+      </c>
+      <c r="B58" s="46" t="inlineStr"/>
+      <c r="C58" s="47">
+        <f>C56-C57</f>
+        <v/>
+      </c>
+      <c r="D58" s="54">
+        <f>IF(ROUND(C58,2)=0,"FULLY RECONCILED - nil dollar variance","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="E58" s="24" t="n"/>
+      <c r="F58" s="24" t="n"/>
+      <c r="G58" s="24" t="n"/>
+      <c r="H58" s="24" t="n"/>
+      <c r="I58" s="24" t="n"/>
+      <c r="J58" s="24" t="n"/>
+      <c r="K58" s="24" t="n"/>
+      <c r="L58" s="24" t="n"/>
+      <c r="M58" s="24" t="n"/>
+      <c r="N58" s="24" t="n"/>
+      <c r="O58" s="24" t="n"/>
+      <c r="P58" s="24" t="n"/>
+      <c r="Q58" s="24" t="n"/>
+      <c r="R58" s="24" t="n"/>
+      <c r="S58" s="24" t="n"/>
+      <c r="T58" s="24" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="n"/>
+      <c r="B59" s="24" t="n"/>
+      <c r="C59" s="24" t="n"/>
+      <c r="D59" s="24" t="n"/>
+      <c r="E59" s="24" t="n"/>
+      <c r="F59" s="24" t="n"/>
+      <c r="G59" s="24" t="n"/>
+      <c r="H59" s="24" t="n"/>
+      <c r="I59" s="24" t="n"/>
+      <c r="J59" s="24" t="n"/>
+      <c r="K59" s="24" t="n"/>
+      <c r="L59" s="24" t="n"/>
+      <c r="M59" s="24" t="n"/>
+      <c r="N59" s="24" t="n"/>
+      <c r="O59" s="24" t="n"/>
+      <c r="P59" s="24" t="n"/>
+      <c r="Q59" s="24" t="n"/>
+      <c r="R59" s="24" t="n"/>
+      <c r="S59" s="24" t="n"/>
+      <c r="T59" s="24" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="38" t="inlineStr">
+        <is>
+          <t>F.  FINDINGS</t>
+        </is>
+      </c>
+      <c r="B60" s="38" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="38" t="n"/>
+      <c r="E60" s="38" t="n"/>
+      <c r="F60" s="38" t="n"/>
+      <c r="G60" s="38" t="n"/>
+      <c r="H60" s="38" t="n"/>
+      <c r="I60" s="38" t="n"/>
+      <c r="J60" s="38" t="n"/>
+      <c r="K60" s="38" t="n"/>
+      <c r="L60" s="38" t="n"/>
+      <c r="M60" s="38" t="n"/>
+      <c r="N60" s="38" t="n"/>
+      <c r="O60" s="38" t="n"/>
+      <c r="P60" s="24" t="n"/>
+      <c r="Q60" s="24" t="n"/>
+      <c r="R60" s="24" t="n"/>
+      <c r="S60" s="24" t="n"/>
+      <c r="T60" s="24" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="55" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B54" s="48" t="inlineStr">
+      <c r="B61" s="56" t="inlineStr">
+        <is>
+          <t>The 16 hours queried (24 Aug and 28 Aug, DTTL) are NOT missing - they were paid in full.</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="n"/>
+      <c r="J61" s="24" t="n"/>
+      <c r="K61" s="24" t="n"/>
+      <c r="L61" s="24" t="n"/>
+      <c r="M61" s="24" t="n"/>
+      <c r="N61" s="24" t="n"/>
+      <c r="O61" s="24" t="n"/>
+      <c r="P61" s="24" t="n"/>
+      <c r="Q61" s="24" t="n"/>
+      <c r="R61" s="24" t="n"/>
+      <c r="S61" s="24" t="n"/>
+      <c r="T61" s="24" t="n"/>
+    </row>
+    <row r="62" ht="34" customHeight="1" s="12">
+      <c r="A62" s="24" t="n"/>
+      <c r="B62" s="57" t="inlineStr">
+        <is>
+          <t>Both days were paid in the 20 Sep 2026 pay run at $37.50/hr: 24/08 as 3.5 + 4.5 hrs ($131.25 + $168.75 = $300.00) and 28/08 as 3.5 + 4.5 hrs ($131.25 + $168.75 = $300.00). $600.00 gross in total. Nothing is owing. See Section A for the exact pay-run lines, and the two highlighted rows in Section C.</t>
+        </is>
+      </c>
+      <c r="P62" s="24" t="n"/>
+      <c r="Q62" s="24" t="n"/>
+      <c r="R62" s="24" t="n"/>
+      <c r="S62" s="24" t="n"/>
+      <c r="T62" s="24" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="n"/>
+      <c r="B63" s="24" t="n"/>
+      <c r="C63" s="24" t="n"/>
+      <c r="D63" s="24" t="n"/>
+      <c r="E63" s="24" t="n"/>
+      <c r="F63" s="24" t="n"/>
+      <c r="G63" s="24" t="n"/>
+      <c r="H63" s="24" t="n"/>
+      <c r="I63" s="24" t="n"/>
+      <c r="J63" s="24" t="n"/>
+      <c r="K63" s="24" t="n"/>
+      <c r="L63" s="24" t="n"/>
+      <c r="M63" s="24" t="n"/>
+      <c r="N63" s="24" t="n"/>
+      <c r="O63" s="24" t="n"/>
+      <c r="P63" s="24" t="n"/>
+      <c r="Q63" s="24" t="n"/>
+      <c r="R63" s="24" t="n"/>
+      <c r="S63" s="24" t="n"/>
+      <c r="T63" s="24" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="55" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B64" s="56" t="inlineStr">
         <is>
           <t>Hours and dollars both reconcile in full.</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="32" customHeight="1" s="12">
-      <c r="B55" s="49" t="inlineStr">
-        <is>
-          <t>All 111.50 timesheet hours across the four fortnights have been paid, and total gross of $4,181.25 equals 111.50 hrs x $37.50 exactly. Nil variance at day level, fortnight level and in total. Every paid line ties back to a timesheet entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="47" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B57" s="48" t="inlineStr">
-        <is>
-          <t>Rate error on fortnight ending 07/08/2026 - now corrected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="32" customHeight="1" s="12">
-      <c r="B58" s="49" t="inlineStr">
-        <is>
-          <t>16 hrs were paid at $35.15/hr instead of $37.50/hr, a shortfall of $37.60 ($18.80 on 29 Jul and $9.40 on each of the two 30 Jul shifts). Payroll reversed and re-paid those 16 hrs in the 21 Aug 2026 run. Nothing further is owing. See Section C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="47" t="inlineStr">
+      <c r="I64" s="24" t="n"/>
+      <c r="J64" s="24" t="n"/>
+      <c r="K64" s="24" t="n"/>
+      <c r="L64" s="24" t="n"/>
+      <c r="M64" s="24" t="n"/>
+      <c r="N64" s="24" t="n"/>
+      <c r="O64" s="24" t="n"/>
+      <c r="P64" s="24" t="n"/>
+      <c r="Q64" s="24" t="n"/>
+      <c r="R64" s="24" t="n"/>
+      <c r="S64" s="24" t="n"/>
+      <c r="T64" s="24" t="n"/>
+    </row>
+    <row r="65" ht="34" customHeight="1" s="12">
+      <c r="A65" s="24" t="n"/>
+      <c r="B65" s="57" t="inlineStr">
+        <is>
+          <t>All 111.50 timesheet hours across the four fortnights have been paid, and total gross of $4,181.25 equals 111.50 hrs x $37.50 exactly. Nil variance at day level, fortnight level and in total.</t>
+        </is>
+      </c>
+      <c r="P65" s="24" t="n"/>
+      <c r="Q65" s="24" t="n"/>
+      <c r="R65" s="24" t="n"/>
+      <c r="S65" s="24" t="n"/>
+      <c r="T65" s="24" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="n"/>
+      <c r="B66" s="24" t="n"/>
+      <c r="C66" s="24" t="n"/>
+      <c r="D66" s="24" t="n"/>
+      <c r="E66" s="24" t="n"/>
+      <c r="F66" s="24" t="n"/>
+      <c r="G66" s="24" t="n"/>
+      <c r="H66" s="24" t="n"/>
+      <c r="I66" s="24" t="n"/>
+      <c r="J66" s="24" t="n"/>
+      <c r="K66" s="24" t="n"/>
+      <c r="L66" s="24" t="n"/>
+      <c r="M66" s="24" t="n"/>
+      <c r="N66" s="24" t="n"/>
+      <c r="O66" s="24" t="n"/>
+      <c r="P66" s="24" t="n"/>
+      <c r="Q66" s="24" t="n"/>
+      <c r="R66" s="24" t="n"/>
+      <c r="S66" s="24" t="n"/>
+      <c r="T66" s="24" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="55" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B60" s="48" t="inlineStr">
+      <c r="B67" s="56" t="inlineStr">
+        <is>
+          <t>Rate error on fortnight ending 07/08/2026 - already corrected.</t>
+        </is>
+      </c>
+      <c r="I67" s="24" t="n"/>
+      <c r="J67" s="24" t="n"/>
+      <c r="K67" s="24" t="n"/>
+      <c r="L67" s="24" t="n"/>
+      <c r="M67" s="24" t="n"/>
+      <c r="N67" s="24" t="n"/>
+      <c r="O67" s="24" t="n"/>
+      <c r="P67" s="24" t="n"/>
+      <c r="Q67" s="24" t="n"/>
+      <c r="R67" s="24" t="n"/>
+      <c r="S67" s="24" t="n"/>
+      <c r="T67" s="24" t="n"/>
+    </row>
+    <row r="68" ht="34" customHeight="1" s="12">
+      <c r="A68" s="24" t="n"/>
+      <c r="B68" s="57" t="inlineStr">
+        <is>
+          <t>16 hrs were paid at $35.15/hr instead of $37.50/hr, a shortfall of $37.60 ($18.80 on 29 Jul and $9.40 on each of the two 30 Jul shifts). Payroll reversed and re-paid those 16 hrs in the 21 Aug 2026 run. Nothing further is owing. See Section D.</t>
+        </is>
+      </c>
+      <c r="P68" s="24" t="n"/>
+      <c r="Q68" s="24" t="n"/>
+      <c r="R68" s="24" t="n"/>
+      <c r="S68" s="24" t="n"/>
+      <c r="T68" s="24" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="n"/>
+      <c r="B69" s="24" t="n"/>
+      <c r="C69" s="24" t="n"/>
+      <c r="D69" s="24" t="n"/>
+      <c r="E69" s="24" t="n"/>
+      <c r="F69" s="24" t="n"/>
+      <c r="G69" s="24" t="n"/>
+      <c r="H69" s="24" t="n"/>
+      <c r="I69" s="24" t="n"/>
+      <c r="J69" s="24" t="n"/>
+      <c r="K69" s="24" t="n"/>
+      <c r="L69" s="24" t="n"/>
+      <c r="M69" s="24" t="n"/>
+      <c r="N69" s="24" t="n"/>
+      <c r="O69" s="24" t="n"/>
+      <c r="P69" s="24" t="n"/>
+      <c r="Q69" s="24" t="n"/>
+      <c r="R69" s="24" t="n"/>
+      <c r="S69" s="24" t="n"/>
+      <c r="T69" s="24" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="55" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B70" s="56" t="inlineStr">
         <is>
           <t>The rate correction was booked to the wrong location.</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="32" customHeight="1" s="12">
-      <c r="B61" s="49" t="inlineStr">
-        <is>
-          <t>The original 16 hrs were split CBA 8 hrs, PwC - MEL Technician 4 hrs and Aware Super 4 hrs. The reversal and re-payment put all 16 hrs against CBA FT Tech MEL. Take-home pay is correct, but job costing for PwC and Aware Super is understated by 4 hrs each and CBA is overstated by 8 hrs. Worth raising with payroll if client recharges are driven off this data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="47" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B63" s="48" t="inlineStr">
-        <is>
-          <t>Fortnight ending 04/09/2026 was paid across two pay runs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1" s="12">
-      <c r="B64" s="49" t="inlineStr">
-        <is>
-          <t>48 hrs of DTTL work went through the 20 Sep 2026 run and 23.50 hrs of PwC National Pool work went through the 22 Sep 2026 run. Total 71.50 hrs, which agrees to the timesheet. A split payment, not a shortfall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="47" t="inlineStr">
+      <c r="I70" s="24" t="n"/>
+      <c r="J70" s="24" t="n"/>
+      <c r="K70" s="24" t="n"/>
+      <c r="L70" s="24" t="n"/>
+      <c r="M70" s="24" t="n"/>
+      <c r="N70" s="24" t="n"/>
+      <c r="O70" s="24" t="n"/>
+      <c r="P70" s="24" t="n"/>
+      <c r="Q70" s="24" t="n"/>
+      <c r="R70" s="24" t="n"/>
+      <c r="S70" s="24" t="n"/>
+      <c r="T70" s="24" t="n"/>
+    </row>
+    <row r="71" ht="34" customHeight="1" s="12">
+      <c r="A71" s="24" t="n"/>
+      <c r="B71" s="57" t="inlineStr">
+        <is>
+          <t>The original 16 hrs were split CBA 8 hrs, PwC - MEL Technician 4 hrs and Aware Super 4 hrs. The reversal and re-payment put all 16 hrs against CBA FT Tech MEL. Take-home pay is correct, but job costing for PwC and Aware Super is understated by 4 hrs each and CBA is overstated by 8 hrs. Worth raising with payroll if client recharges run off this data.</t>
+        </is>
+      </c>
+      <c r="P71" s="24" t="n"/>
+      <c r="Q71" s="24" t="n"/>
+      <c r="R71" s="24" t="n"/>
+      <c r="S71" s="24" t="n"/>
+      <c r="T71" s="24" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="n"/>
+      <c r="B72" s="24" t="n"/>
+      <c r="C72" s="24" t="n"/>
+      <c r="D72" s="24" t="n"/>
+      <c r="E72" s="24" t="n"/>
+      <c r="F72" s="24" t="n"/>
+      <c r="G72" s="24" t="n"/>
+      <c r="H72" s="24" t="n"/>
+      <c r="I72" s="24" t="n"/>
+      <c r="J72" s="24" t="n"/>
+      <c r="K72" s="24" t="n"/>
+      <c r="L72" s="24" t="n"/>
+      <c r="M72" s="24" t="n"/>
+      <c r="N72" s="24" t="n"/>
+      <c r="O72" s="24" t="n"/>
+      <c r="P72" s="24" t="n"/>
+      <c r="Q72" s="24" t="n"/>
+      <c r="R72" s="24" t="n"/>
+      <c r="S72" s="24" t="n"/>
+      <c r="T72" s="24" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="55" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B66" s="48" t="inlineStr">
+      <c r="B73" s="56" t="inlineStr">
+        <is>
+          <t>Fortnight ending 04/09/2026 was paid across two pay runs - this is the likely cause of the query.</t>
+        </is>
+      </c>
+      <c r="I73" s="24" t="n"/>
+      <c r="J73" s="24" t="n"/>
+      <c r="K73" s="24" t="n"/>
+      <c r="L73" s="24" t="n"/>
+      <c r="M73" s="24" t="n"/>
+      <c r="N73" s="24" t="n"/>
+      <c r="O73" s="24" t="n"/>
+      <c r="P73" s="24" t="n"/>
+      <c r="Q73" s="24" t="n"/>
+      <c r="R73" s="24" t="n"/>
+      <c r="S73" s="24" t="n"/>
+      <c r="T73" s="24" t="n"/>
+    </row>
+    <row r="74" ht="34" customHeight="1" s="12">
+      <c r="A74" s="24" t="n"/>
+      <c r="B74" s="57" t="inlineStr">
+        <is>
+          <t>48 hrs of DTTL work (including the two days queried) went through the 20 Sep 2026 run, and 23.50 hrs of PwC National Pool work went through the 22 Sep 2026 run. Total 71.50 hrs, which agrees to the timesheet. Anyone checking a single payslip for that fortnight would only see part of it.</t>
+        </is>
+      </c>
+      <c r="P74" s="24" t="n"/>
+      <c r="Q74" s="24" t="n"/>
+      <c r="R74" s="24" t="n"/>
+      <c r="S74" s="24" t="n"/>
+      <c r="T74" s="24" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="n"/>
+      <c r="B75" s="24" t="n"/>
+      <c r="C75" s="24" t="n"/>
+      <c r="D75" s="24" t="n"/>
+      <c r="E75" s="24" t="n"/>
+      <c r="F75" s="24" t="n"/>
+      <c r="G75" s="24" t="n"/>
+      <c r="H75" s="24" t="n"/>
+      <c r="I75" s="24" t="n"/>
+      <c r="J75" s="24" t="n"/>
+      <c r="K75" s="24" t="n"/>
+      <c r="L75" s="24" t="n"/>
+      <c r="M75" s="24" t="n"/>
+      <c r="N75" s="24" t="n"/>
+      <c r="O75" s="24" t="n"/>
+      <c r="P75" s="24" t="n"/>
+      <c r="Q75" s="24" t="n"/>
+      <c r="R75" s="24" t="n"/>
+      <c r="S75" s="24" t="n"/>
+      <c r="T75" s="24" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="55" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B76" s="56" t="inlineStr">
         <is>
           <t>Payment lag worth checking.</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="32" customHeight="1" s="12">
-      <c r="B67" s="49" t="inlineStr">
+      <c r="I76" s="24" t="n"/>
+      <c r="J76" s="24" t="n"/>
+      <c r="K76" s="24" t="n"/>
+      <c r="L76" s="24" t="n"/>
+      <c r="M76" s="24" t="n"/>
+      <c r="N76" s="24" t="n"/>
+      <c r="O76" s="24" t="n"/>
+      <c r="P76" s="24" t="n"/>
+      <c r="Q76" s="24" t="n"/>
+      <c r="R76" s="24" t="n"/>
+      <c r="S76" s="24" t="n"/>
+      <c r="T76" s="24" t="n"/>
+    </row>
+    <row r="77" ht="34" customHeight="1" s="12">
+      <c r="A77" s="24" t="n"/>
+      <c r="B77" s="57" t="inlineStr">
         <is>
           <t>Work from 25-27 Aug was not paid until the 22 Sep 2026 run, roughly four weeks after it was worked. Check this against the payroll calendar if it was not expected.</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="47" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B69" s="48" t="inlineStr">
+      <c r="P77" s="24" t="n"/>
+      <c r="Q77" s="24" t="n"/>
+      <c r="R77" s="24" t="n"/>
+      <c r="S77" s="24" t="n"/>
+      <c r="T77" s="24" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="n"/>
+      <c r="B78" s="24" t="n"/>
+      <c r="C78" s="24" t="n"/>
+      <c r="D78" s="24" t="n"/>
+      <c r="E78" s="24" t="n"/>
+      <c r="F78" s="24" t="n"/>
+      <c r="G78" s="24" t="n"/>
+      <c r="H78" s="24" t="n"/>
+      <c r="I78" s="24" t="n"/>
+      <c r="J78" s="24" t="n"/>
+      <c r="K78" s="24" t="n"/>
+      <c r="L78" s="24" t="n"/>
+      <c r="M78" s="24" t="n"/>
+      <c r="N78" s="24" t="n"/>
+      <c r="O78" s="24" t="n"/>
+      <c r="P78" s="24" t="n"/>
+      <c r="Q78" s="24" t="n"/>
+      <c r="R78" s="24" t="n"/>
+      <c r="S78" s="24" t="n"/>
+      <c r="T78" s="24" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="55" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B79" s="56" t="inlineStr">
         <is>
           <t>Superannuation.</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="32" customHeight="1" s="12">
-      <c r="B70" s="49" t="inlineStr">
+      <c r="I79" s="24" t="n"/>
+      <c r="J79" s="24" t="n"/>
+      <c r="K79" s="24" t="n"/>
+      <c r="L79" s="24" t="n"/>
+      <c r="M79" s="24" t="n"/>
+      <c r="N79" s="24" t="n"/>
+      <c r="O79" s="24" t="n"/>
+      <c r="P79" s="24" t="n"/>
+      <c r="Q79" s="24" t="n"/>
+      <c r="R79" s="24" t="n"/>
+      <c r="S79" s="24" t="n"/>
+      <c r="T79" s="24" t="n"/>
+    </row>
+    <row r="80" ht="34" customHeight="1" s="12">
+      <c r="A80" s="24" t="n"/>
+      <c r="B80" s="57" t="inlineStr">
         <is>
           <t>SG has been calculated at 12% of gross on every line, which is the correct rate. The reversal also reversed the super, so no over or under contribution arises.</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="42" customHeight="1" s="12">
-      <c r="A73" s="50" t="inlineStr">
+      <c r="P80" s="24" t="n"/>
+      <c r="Q80" s="24" t="n"/>
+      <c r="R80" s="24" t="n"/>
+      <c r="S80" s="24" t="n"/>
+      <c r="T80" s="24" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="n"/>
+      <c r="B81" s="24" t="n"/>
+      <c r="C81" s="24" t="n"/>
+      <c r="D81" s="24" t="n"/>
+      <c r="E81" s="24" t="n"/>
+      <c r="F81" s="24" t="n"/>
+      <c r="G81" s="24" t="n"/>
+      <c r="H81" s="24" t="n"/>
+      <c r="I81" s="24" t="n"/>
+      <c r="J81" s="24" t="n"/>
+      <c r="K81" s="24" t="n"/>
+      <c r="L81" s="24" t="n"/>
+      <c r="M81" s="24" t="n"/>
+      <c r="N81" s="24" t="n"/>
+      <c r="O81" s="24" t="n"/>
+      <c r="P81" s="24" t="n"/>
+      <c r="Q81" s="24" t="n"/>
+      <c r="R81" s="24" t="n"/>
+      <c r="S81" s="24" t="n"/>
+      <c r="T81" s="24" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="n"/>
+      <c r="B82" s="24" t="n"/>
+      <c r="C82" s="24" t="n"/>
+      <c r="D82" s="24" t="n"/>
+      <c r="E82" s="24" t="n"/>
+      <c r="F82" s="24" t="n"/>
+      <c r="G82" s="24" t="n"/>
+      <c r="H82" s="24" t="n"/>
+      <c r="I82" s="24" t="n"/>
+      <c r="J82" s="24" t="n"/>
+      <c r="K82" s="24" t="n"/>
+      <c r="L82" s="24" t="n"/>
+      <c r="M82" s="24" t="n"/>
+      <c r="N82" s="24" t="n"/>
+      <c r="O82" s="24" t="n"/>
+      <c r="P82" s="24" t="n"/>
+      <c r="Q82" s="24" t="n"/>
+      <c r="R82" s="24" t="n"/>
+      <c r="S82" s="24" t="n"/>
+      <c r="T82" s="24" t="n"/>
+    </row>
+    <row r="83" ht="44" customHeight="1" s="12">
+      <c r="A83" s="25" t="inlineStr">
         <is>
           <t>Source of timesheet data: the timesheet screenshots for the fortnights ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026, all showing status PROCESSED. Source of paid data: the Earnings Details tabs in this workbook. Paid figures are live formulas - if a pay-run tab is updated, this reconciliation updates with it. Columns S and T were added to each pay-run tab: S pulls the work date out of the Notes text, T confirms the line was matched here.</t>
         </is>
       </c>
+      <c r="P83" s="24" t="n"/>
+      <c r="Q83" s="24" t="n"/>
+      <c r="R83" s="24" t="n"/>
+      <c r="S83" s="24" t="n"/>
+      <c r="T83" s="24" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="n"/>
+      <c r="B84" s="24" t="n"/>
+      <c r="C84" s="24" t="n"/>
+      <c r="D84" s="24" t="n"/>
+      <c r="E84" s="24" t="n"/>
+      <c r="F84" s="24" t="n"/>
+      <c r="G84" s="24" t="n"/>
+      <c r="H84" s="24" t="n"/>
+      <c r="I84" s="24" t="n"/>
+      <c r="J84" s="24" t="n"/>
+      <c r="K84" s="24" t="n"/>
+      <c r="L84" s="24" t="n"/>
+      <c r="M84" s="24" t="n"/>
+      <c r="N84" s="24" t="n"/>
+      <c r="O84" s="24" t="n"/>
+      <c r="P84" s="24" t="n"/>
+      <c r="Q84" s="24" t="n"/>
+      <c r="R84" s="24" t="n"/>
+      <c r="S84" s="24" t="n"/>
+      <c r="T84" s="24" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="n"/>
+      <c r="B85" s="24" t="n"/>
+      <c r="C85" s="24" t="n"/>
+      <c r="D85" s="24" t="n"/>
+      <c r="E85" s="24" t="n"/>
+      <c r="F85" s="24" t="n"/>
+      <c r="G85" s="24" t="n"/>
+      <c r="H85" s="24" t="n"/>
+      <c r="I85" s="24" t="n"/>
+      <c r="J85" s="24" t="n"/>
+      <c r="K85" s="24" t="n"/>
+      <c r="L85" s="24" t="n"/>
+      <c r="M85" s="24" t="n"/>
+      <c r="N85" s="24" t="n"/>
+      <c r="O85" s="24" t="n"/>
+      <c r="P85" s="24" t="n"/>
+      <c r="Q85" s="24" t="n"/>
+      <c r="R85" s="24" t="n"/>
+      <c r="S85" s="24" t="n"/>
+      <c r="T85" s="24" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="24" t="n"/>
+      <c r="B86" s="24" t="n"/>
+      <c r="C86" s="24" t="n"/>
+      <c r="D86" s="24" t="n"/>
+      <c r="E86" s="24" t="n"/>
+      <c r="F86" s="24" t="n"/>
+      <c r="G86" s="24" t="n"/>
+      <c r="H86" s="24" t="n"/>
+      <c r="I86" s="24" t="n"/>
+      <c r="J86" s="24" t="n"/>
+      <c r="K86" s="24" t="n"/>
+      <c r="L86" s="24" t="n"/>
+      <c r="M86" s="24" t="n"/>
+      <c r="N86" s="24" t="n"/>
+      <c r="O86" s="24" t="n"/>
+      <c r="P86" s="24" t="n"/>
+      <c r="Q86" s="24" t="n"/>
+      <c r="R86" s="24" t="n"/>
+      <c r="S86" s="24" t="n"/>
+      <c r="T86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="n"/>
+      <c r="B87" s="24" t="n"/>
+      <c r="C87" s="24" t="n"/>
+      <c r="D87" s="24" t="n"/>
+      <c r="E87" s="24" t="n"/>
+      <c r="F87" s="24" t="n"/>
+      <c r="G87" s="24" t="n"/>
+      <c r="H87" s="24" t="n"/>
+      <c r="I87" s="24" t="n"/>
+      <c r="J87" s="24" t="n"/>
+      <c r="K87" s="24" t="n"/>
+      <c r="L87" s="24" t="n"/>
+      <c r="M87" s="24" t="n"/>
+      <c r="N87" s="24" t="n"/>
+      <c r="O87" s="24" t="n"/>
+      <c r="P87" s="24" t="n"/>
+      <c r="Q87" s="24" t="n"/>
+      <c r="R87" s="24" t="n"/>
+      <c r="S87" s="24" t="n"/>
+      <c r="T87" s="24" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="24" t="n"/>
+      <c r="B88" s="24" t="n"/>
+      <c r="C88" s="24" t="n"/>
+      <c r="D88" s="24" t="n"/>
+      <c r="E88" s="24" t="n"/>
+      <c r="F88" s="24" t="n"/>
+      <c r="G88" s="24" t="n"/>
+      <c r="H88" s="24" t="n"/>
+      <c r="I88" s="24" t="n"/>
+      <c r="J88" s="24" t="n"/>
+      <c r="K88" s="24" t="n"/>
+      <c r="L88" s="24" t="n"/>
+      <c r="M88" s="24" t="n"/>
+      <c r="N88" s="24" t="n"/>
+      <c r="O88" s="24" t="n"/>
+      <c r="P88" s="24" t="n"/>
+      <c r="Q88" s="24" t="n"/>
+      <c r="R88" s="24" t="n"/>
+      <c r="S88" s="24" t="n"/>
+      <c r="T88" s="24" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="n"/>
+      <c r="B89" s="24" t="n"/>
+      <c r="C89" s="24" t="n"/>
+      <c r="D89" s="24" t="n"/>
+      <c r="E89" s="24" t="n"/>
+      <c r="F89" s="24" t="n"/>
+      <c r="G89" s="24" t="n"/>
+      <c r="H89" s="24" t="n"/>
+      <c r="I89" s="24" t="n"/>
+      <c r="J89" s="24" t="n"/>
+      <c r="K89" s="24" t="n"/>
+      <c r="L89" s="24" t="n"/>
+      <c r="M89" s="24" t="n"/>
+      <c r="N89" s="24" t="n"/>
+      <c r="O89" s="24" t="n"/>
+      <c r="P89" s="24" t="n"/>
+      <c r="Q89" s="24" t="n"/>
+      <c r="R89" s="24" t="n"/>
+      <c r="S89" s="24" t="n"/>
+      <c r="T89" s="24" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="24" t="n"/>
+      <c r="B90" s="24" t="n"/>
+      <c r="C90" s="24" t="n"/>
+      <c r="D90" s="24" t="n"/>
+      <c r="E90" s="24" t="n"/>
+      <c r="F90" s="24" t="n"/>
+      <c r="G90" s="24" t="n"/>
+      <c r="H90" s="24" t="n"/>
+      <c r="I90" s="24" t="n"/>
+      <c r="J90" s="24" t="n"/>
+      <c r="K90" s="24" t="n"/>
+      <c r="L90" s="24" t="n"/>
+      <c r="M90" s="24" t="n"/>
+      <c r="N90" s="24" t="n"/>
+      <c r="O90" s="24" t="n"/>
+      <c r="P90" s="24" t="n"/>
+      <c r="Q90" s="24" t="n"/>
+      <c r="R90" s="24" t="n"/>
+      <c r="S90" s="24" t="n"/>
+      <c r="T90" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B58:O58"/>
-    <mergeCell ref="B69:F69"/>
+  <mergeCells count="17">
+    <mergeCell ref="A83:O83"/>
+    <mergeCell ref="B71:O71"/>
+    <mergeCell ref="B74:O74"/>
+    <mergeCell ref="B65:O65"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A73:O73"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B55:O55"/>
-    <mergeCell ref="B70:O70"/>
-    <mergeCell ref="B64:O64"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B67:O67"/>
-    <mergeCell ref="B61:O61"/>
-    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B77:O77"/>
+    <mergeCell ref="B68:O68"/>
+    <mergeCell ref="B62:O62"/>
+    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B80:O80"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B61:H61"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E10">
+  <conditionalFormatting sqref="E13:E17">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J21:J37">
+    <cfRule type="cellIs" priority="2" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J14:J30">
+  <conditionalFormatting sqref="F6:F8">
     <cfRule type="cellIs" priority="3" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
-      <formula>0</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13:G17">
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>ISNUMBER(SEARCH("Reconciled",G13))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>ISNUMBER(SEARCH("VARIANCE",G13))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G10">
-    <cfRule type="expression" priority="5" dxfId="1">
-      <formula>ISNUMBER(SEARCH("Reconciled",G6))&gt;0</formula>
+  <conditionalFormatting sqref="N21:N37">
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>ISNUMBER(SEARCH("OK",N21))+ISNUMBER(SEARCH("AGREE",N21))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="0">
-      <formula>ISNUMBER(SEARCH("VARIANCE",G6))&gt;0</formula>
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>ISNUMBER(SEARCH("UNDER",N21))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N14:N30">
-    <cfRule type="expression" priority="7" dxfId="1">
-      <formula>ISNUMBER(SEARCH("OK",N14))+ISNUMBER(SEARCH("AGREE",N14))&gt;0</formula>
+  <conditionalFormatting sqref="D51:D58">
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>ISNUMBER(SEARCH("OK",D51))+ISNUMBER(SEARCH("FULLY",D51))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="0">
-      <formula>ISNUMBER(SEARCH("UNDER",N14))&gt;0</formula>
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>ISNUMBER(SEARCH("INVESTIGATE",D51))+ISNUMBER(SEARCH("VARIANCE",D51))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D44:D51">
-    <cfRule type="expression" priority="9" dxfId="1">
-      <formula>ISNUMBER(SEARCH("OK",D44))+ISNUMBER(SEARCH("FULLY",D44))&gt;0</formula>
+  <conditionalFormatting sqref="K6:K8">
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>ISNUMBER(SEARCH("PAID IN FULL",K6))+ISNUMBER(SEARCH("NIL OWING",K6))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="0">
-      <formula>ISNUMBER(SEARCH("INVESTIGATE",D44))+ISNUMBER(SEARCH("VARIANCE",D44))&gt;0</formula>
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>ISNUMBER(SEARCH("SHORTFALL",K6))+ISNUMBER(SEARCH("OWING - ",K6))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3204,12 +4211,12 @@
           <t>SG Super</t>
         </is>
       </c>
-      <c r="S2" s="51" t="inlineStr">
+      <c r="S2" s="58" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="T2" s="51" t="inlineStr">
+      <c r="T2" s="58" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -3280,12 +4287,12 @@
       <c r="Q3" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S3" s="52">
+      <c r="S3" s="59">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="T3">
-        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S3,'Summary '!$D$14:$D$29,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3354,12 +4361,12 @@
       <c r="Q4" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S4" s="52">
+      <c r="S4" s="59">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="T4">
-        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S4,'Summary '!$D$14:$D$29,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3428,12 +4435,12 @@
       <c r="Q5" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="59">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="T5">
-        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S5,'Summary '!$D$14:$D$29,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3502,12 +4509,12 @@
       <c r="Q6" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S6" s="52">
+      <c r="S6" s="59">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="T6">
-        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S6,'Summary '!$D$14:$D$29,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3576,12 +4583,12 @@
       <c r="Q7" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S7" s="52">
+      <c r="S7" s="59">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="T7">
-        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S7,'Summary '!$D$14:$D$29,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3650,12 +4657,12 @@
       <c r="Q8" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S8" s="52">
+      <c r="S8" s="59">
         <f>IFERROR(DATE(VALUE(MID(L8,FIND("/",L8,FIND("/",L8)+1)+1,4)),VALUE(MID(L8,FIND("/",L8)+1,FIND("/",L8,FIND("/",L8)+1)-FIND("/",L8)-1)),VALUE(LEFT(L8,FIND("/",L8)-1))),IF(ISNUMBER(L8),L8,""))</f>
         <v/>
       </c>
       <c r="T8">
-        <f>IF(S8="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S8,'Summary '!$D$14:$D$29,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S8="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S8,'Summary '!$D$21:$D$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3724,12 +4731,12 @@
       <c r="Q9" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S9" s="52">
+      <c r="S9" s="59">
         <f>IFERROR(DATE(VALUE(MID(L9,FIND("/",L9,FIND("/",L9)+1)+1,4)),VALUE(MID(L9,FIND("/",L9)+1,FIND("/",L9,FIND("/",L9)+1)-FIND("/",L9)-1)),VALUE(LEFT(L9,FIND("/",L9)-1))),IF(ISNUMBER(L9),L9,""))</f>
         <v/>
       </c>
       <c r="T9">
-        <f>IF(S9="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S9,'Summary '!$D$14:$D$29,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S9="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S9,'Summary '!$D$21:$D$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3798,12 +4805,12 @@
       <c r="Q10" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S10" s="52">
+      <c r="S10" s="59">
         <f>IFERROR(DATE(VALUE(MID(L10,FIND("/",L10,FIND("/",L10)+1)+1,4)),VALUE(MID(L10,FIND("/",L10)+1,FIND("/",L10,FIND("/",L10)+1)-FIND("/",L10)-1)),VALUE(LEFT(L10,FIND("/",L10)-1))),IF(ISNUMBER(L10),L10,""))</f>
         <v/>
       </c>
       <c r="T10">
-        <f>IF(S10="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S10,'Summary '!$D$14:$D$29,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S10="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S10,'Summary '!$D$21:$D$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3872,12 +4879,12 @@
       <c r="Q11" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S11" s="52">
+      <c r="S11" s="59">
         <f>IFERROR(DATE(VALUE(MID(L11,FIND("/",L11,FIND("/",L11)+1)+1,4)),VALUE(MID(L11,FIND("/",L11)+1,FIND("/",L11,FIND("/",L11)+1)-FIND("/",L11)-1)),VALUE(LEFT(L11,FIND("/",L11)-1))),IF(ISNUMBER(L11),L11,""))</f>
         <v/>
       </c>
       <c r="T11">
-        <f>IF(S11="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S11,'Summary '!$D$14:$D$29,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S11="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S11,'Summary '!$D$21:$D$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4016,12 +5023,12 @@
           <t>SG Super</t>
         </is>
       </c>
-      <c r="S2" s="51" t="inlineStr">
+      <c r="S2" s="58" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="T2" s="51" t="inlineStr">
+      <c r="T2" s="58" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -4092,12 +5099,12 @@
       <c r="Q3" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S3" s="52">
+      <c r="S3" s="59">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="T3">
-        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S3,'Summary '!$D$14:$D$29,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4166,12 +5173,12 @@
       <c r="Q4" s="15" t="n">
         <v>20.25</v>
       </c>
-      <c r="S4" s="52">
+      <c r="S4" s="59">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="T4">
-        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S4,'Summary '!$D$14:$D$29,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4240,12 +5247,12 @@
       <c r="Q5" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="59">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="T5">
-        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S5,'Summary '!$D$14:$D$29,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4314,12 +5321,12 @@
       <c r="Q6" s="15" t="n">
         <v>20.25</v>
       </c>
-      <c r="S6" s="52">
+      <c r="S6" s="59">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="T6">
-        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S6,'Summary '!$D$14:$D$29,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4388,12 +5395,12 @@
       <c r="Q7" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S7" s="52">
+      <c r="S7" s="59">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="T7">
-        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S7,'Summary '!$D$14:$D$29,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4462,12 +5469,12 @@
       <c r="Q8" s="15" t="n">
         <v>20.25</v>
       </c>
-      <c r="S8" s="52">
+      <c r="S8" s="59">
         <f>IFERROR(DATE(VALUE(MID(L8,FIND("/",L8,FIND("/",L8)+1)+1,4)),VALUE(MID(L8,FIND("/",L8)+1,FIND("/",L8,FIND("/",L8)+1)-FIND("/",L8)-1)),VALUE(LEFT(L8,FIND("/",L8)-1))),IF(ISNUMBER(L8),L8,""))</f>
         <v/>
       </c>
       <c r="T8">
-        <f>IF(S8="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S8,'Summary '!$D$14:$D$29,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S8="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S8,'Summary '!$D$21:$D$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4536,12 +5543,12 @@
       <c r="Q9" s="15" t="n">
         <v>13.5</v>
       </c>
-      <c r="S9" s="52">
+      <c r="S9" s="59">
         <f>IFERROR(DATE(VALUE(MID(L9,FIND("/",L9,FIND("/",L9)+1)+1,4)),VALUE(MID(L9,FIND("/",L9)+1,FIND("/",L9,FIND("/",L9)+1)-FIND("/",L9)-1)),VALUE(LEFT(L9,FIND("/",L9)-1))),IF(ISNUMBER(L9),L9,""))</f>
         <v/>
       </c>
       <c r="T9">
-        <f>IF(S9="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S9,'Summary '!$D$14:$D$29,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S9="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S9,'Summary '!$D$21:$D$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4610,12 +5617,12 @@
       <c r="Q10" s="15" t="n">
         <v>22.5</v>
       </c>
-      <c r="S10" s="52">
+      <c r="S10" s="59">
         <f>IFERROR(DATE(VALUE(MID(L10,FIND("/",L10,FIND("/",L10)+1)+1,4)),VALUE(MID(L10,FIND("/",L10)+1,FIND("/",L10,FIND("/",L10)+1)-FIND("/",L10)-1)),VALUE(LEFT(L10,FIND("/",L10)-1))),IF(ISNUMBER(L10),L10,""))</f>
         <v/>
       </c>
       <c r="T10">
-        <f>IF(S10="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S10,'Summary '!$D$14:$D$29,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S10="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S10,'Summary '!$D$21:$D$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4684,12 +5691,12 @@
       <c r="Q11" s="15" t="n">
         <v>13.5</v>
       </c>
-      <c r="S11" s="52">
+      <c r="S11" s="59">
         <f>IFERROR(DATE(VALUE(MID(L11,FIND("/",L11,FIND("/",L11)+1)+1,4)),VALUE(MID(L11,FIND("/",L11)+1,FIND("/",L11,FIND("/",L11)+1)-FIND("/",L11)-1)),VALUE(LEFT(L11,FIND("/",L11)-1))),IF(ISNUMBER(L11),L11,""))</f>
         <v/>
       </c>
       <c r="T11">
-        <f>IF(S11="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S11,'Summary '!$D$14:$D$29,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S11="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S11,'Summary '!$D$21:$D$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4758,12 +5765,12 @@
       <c r="Q12" s="15" t="n">
         <v>22.5</v>
       </c>
-      <c r="S12" s="52">
+      <c r="S12" s="59">
         <f>IFERROR(DATE(VALUE(MID(L12,FIND("/",L12,FIND("/",L12)+1)+1,4)),VALUE(MID(L12,FIND("/",L12)+1,FIND("/",L12,FIND("/",L12)+1)-FIND("/",L12)-1)),VALUE(LEFT(L12,FIND("/",L12)-1))),IF(ISNUMBER(L12),L12,""))</f>
         <v/>
       </c>
       <c r="T12">
-        <f>IF(S12="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S12,'Summary '!$D$14:$D$29,K12)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S12="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S12,'Summary '!$D$21:$D$36,K12)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4832,12 +5839,12 @@
       <c r="Q13" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S13" s="52">
+      <c r="S13" s="59">
         <f>IFERROR(DATE(VALUE(MID(L13,FIND("/",L13,FIND("/",L13)+1)+1,4)),VALUE(MID(L13,FIND("/",L13)+1,FIND("/",L13,FIND("/",L13)+1)-FIND("/",L13)-1)),VALUE(LEFT(L13,FIND("/",L13)-1))),IF(ISNUMBER(L13),L13,""))</f>
         <v/>
       </c>
       <c r="T13">
-        <f>IF(S13="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S13,'Summary '!$D$14:$D$29,K13)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S13="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S13,'Summary '!$D$21:$D$36,K13)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4906,12 +5913,12 @@
       <c r="Q14" s="15" t="n">
         <v>20.25</v>
       </c>
-      <c r="S14" s="52">
+      <c r="S14" s="59">
         <f>IFERROR(DATE(VALUE(MID(L14,FIND("/",L14,FIND("/",L14)+1)+1,4)),VALUE(MID(L14,FIND("/",L14)+1,FIND("/",L14,FIND("/",L14)+1)-FIND("/",L14)-1)),VALUE(LEFT(L14,FIND("/",L14)-1))),IF(ISNUMBER(L14),L14,""))</f>
         <v/>
       </c>
       <c r="T14">
-        <f>IF(S14="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S14,'Summary '!$D$14:$D$29,K14)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S14="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S14,'Summary '!$D$21:$D$36,K14)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5050,12 +6057,12 @@
           <t>SG Super</t>
         </is>
       </c>
-      <c r="S2" s="51" t="inlineStr">
+      <c r="S2" s="58" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="T2" s="51" t="inlineStr">
+      <c r="T2" s="58" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -5126,12 +6133,12 @@
       <c r="Q3" s="15" t="n">
         <v>-67.48569000000001</v>
       </c>
-      <c r="S3" s="52">
+      <c r="S3" s="59">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="T3">
-        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S3,'Summary '!$D$14:$D$29,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5200,12 +6207,12 @@
       <c r="Q4" s="15" t="n">
         <v>71.99754</v>
       </c>
-      <c r="S4" s="52">
+      <c r="S4" s="59">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="T4">
-        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S4,'Summary '!$D$14:$D$29,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5274,12 +6281,12 @@
       <c r="Q5" s="15" t="n">
         <v>22.49923</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="59">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="T5">
-        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S5,'Summary '!$D$14:$D$29,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5348,12 +6355,12 @@
       <c r="Q6" s="15" t="n">
         <v>13.49954</v>
       </c>
-      <c r="S6" s="52">
+      <c r="S6" s="59">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="T6">
-        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S6,'Summary '!$D$14:$D$29,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5422,12 +6429,12 @@
       <c r="Q7" s="15" t="n">
         <v>17.99938</v>
       </c>
-      <c r="S7" s="52">
+      <c r="S7" s="59">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="T7">
-        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S7,'Summary '!$D$14:$D$29,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5565,12 +6572,12 @@
           <t>SG Super</t>
         </is>
       </c>
-      <c r="S2" s="51" t="inlineStr">
+      <c r="S2" s="58" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="T2" s="51" t="inlineStr">
+      <c r="T2" s="58" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -5639,12 +6646,12 @@
       <c r="Q3" s="15" t="n">
         <v>23.19969</v>
       </c>
-      <c r="S3" s="52">
+      <c r="S3" s="59">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="T3">
-        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S3,'Summary '!$D$14:$D$29,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5711,12 +6718,12 @@
       <c r="Q4" s="15" t="n">
         <v>10.54531</v>
       </c>
-      <c r="S4" s="52">
+      <c r="S4" s="59">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="T4">
-        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S4,'Summary '!$D$14:$D$29,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5783,12 +6790,12 @@
       <c r="Q5" s="15" t="n">
         <v>16.8725</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="59">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="T5">
-        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S5,'Summary '!$D$14:$D$29,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5855,12 +6862,12 @@
       <c r="Q6" s="15" t="n">
         <v>16.8725</v>
       </c>
-      <c r="S6" s="52">
+      <c r="S6" s="59">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="T6">
-        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$14:$A$29,S6,'Summary '!$D$14:$D$29,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>

--- a/Timesheet_Reconciliation_Jonathan_Hendratno.xlsx
+++ b/Timesheet_Reconciliation_Jonathan_Hendratno.xlsx
@@ -1389,7 +1389,7 @@
     <row r="19">
       <c r="A19" s="38" t="inlineStr">
         <is>
-          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay run that paid it</t>
+          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay run that paid it.  The Notes column shows how each day was split across pay lines either side of the unpaid break.</t>
         </is>
       </c>
       <c r="B19" s="38" t="n"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="O22" s="48" t="inlineStr">
         <is>
-          <t>Two separate timesheets this day - matched by location</t>
+          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location</t>
         </is>
       </c>
       <c r="P22" s="24" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="O23" s="48" t="inlineStr">
         <is>
-          <t>Two separate timesheets this day - matched by location</t>
+          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location</t>
         </is>
       </c>
       <c r="P23" s="24" t="n"/>
@@ -1841,7 +1841,11 @@
         <f>IF(I25=0,"",IF(ROUND(L25,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L25)*I25,"0.00")))</f>
         <v/>
       </c>
-      <c r="O25" s="48" t="inlineStr"/>
+      <c r="O25" s="48" t="inlineStr">
+        <is>
+          <t>Paid as a single 4 hr line - no break taken</t>
+        </is>
+      </c>
       <c r="P25" s="24" t="n"/>
       <c r="Q25" s="24" t="n"/>
       <c r="R25" s="24" t="n"/>
@@ -2607,7 +2611,11 @@
         <f>IF(I36=0,"",IF(ROUND(L36,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L36)*I36,"0.00")))</f>
         <v/>
       </c>
-      <c r="O36" s="48" t="inlineStr"/>
+      <c r="O36" s="48" t="inlineStr">
+        <is>
+          <t>Paid as a single 4 hr line - no break taken</t>
+        </is>
+      </c>
       <c r="P36" s="24" t="n"/>
       <c r="Q36" s="24" t="n"/>
       <c r="R36" s="24" t="n"/>

--- a/Timesheet_Reconciliation_Jonathan_Hendratno.xlsx
+++ b/Timesheet_Reconciliation_Jonathan_Hendratno.xlsx
@@ -24,12 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="\$#,##0.00###"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="$#,##0.00&quot;/hr&quot;"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -87,7 +88,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -148,6 +149,11 @@
         <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -176,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,43 +220,63 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="9" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -685,24 +711,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T90"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="17" min="1" max="1"/>
-    <col width="11" bestFit="1" customWidth="1" style="17" min="2" max="2"/>
-    <col width="13" customWidth="1" style="17" min="3" max="4"/>
-    <col width="34" customWidth="1" style="12" min="4" max="4"/>
-    <col width="10" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
+    <col width="30" customWidth="1" style="17" min="1" max="1"/>
+    <col width="9" bestFit="1" customWidth="1" style="17" min="2" max="2"/>
+    <col width="26" customWidth="1" style="17" min="3" max="4"/>
+    <col width="12" customWidth="1" style="12" min="4" max="4"/>
+    <col width="34" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
     <col width="10" customWidth="1" style="17" min="6" max="16384"/>
-    <col width="12" customWidth="1" style="12" min="7" max="7"/>
-    <col width="11" customWidth="1" style="12" min="8" max="8"/>
-    <col width="10" customWidth="1" style="12" min="9" max="9"/>
-    <col width="10" customWidth="1" style="12" min="10" max="10"/>
-    <col width="14" customWidth="1" style="12" min="11" max="11"/>
-    <col width="11" customWidth="1" style="12" min="12" max="12"/>
-    <col width="12" customWidth="1" style="12" min="13" max="13"/>
-    <col width="16" customWidth="1" style="12" min="14" max="14"/>
-    <col width="40" customWidth="1" style="12" min="15" max="15"/>
+    <col width="10" customWidth="1" style="12" min="7" max="7"/>
+    <col width="12" customWidth="1" style="12" min="8" max="8"/>
+    <col width="11" customWidth="1" style="12" min="9" max="9"/>
+    <col width="11" customWidth="1" style="12" min="10" max="10"/>
+    <col width="11" customWidth="1" style="12" min="11" max="11"/>
+    <col width="14" customWidth="1" style="12" min="12" max="12"/>
+    <col width="14" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14" customWidth="1" style="12" min="14" max="14"/>
+    <col width="52" customWidth="1" style="12" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="4.5" customHeight="1" s="12">
@@ -730,11 +756,13 @@
       <c r="R1" s="24" t="n"/>
       <c r="S1" s="24" t="n"/>
       <c r="T1" s="24" t="n"/>
-    </row>
-    <row r="2" ht="28" customHeight="1" s="12">
+      <c r="U1" s="24" t="n"/>
+      <c r="V1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="12">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Timesheet hours transcribed from the timesheet screenshots (fortnights ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026). Paid hours are pulled live by formula from the pay-run tabs in this workbook, matched on work date AND location. Prepared 22/09/2026.</t>
+          <t>Includes hourly rate and gross earnings. Timesheet hours transcribed from the timesheet screenshots. Paid hours are pulled live by formula from the pay-run tabs, matched on work date AND location. Pay periods and dates paid are taken from the Employment Hero pay history. Prepared 22/09/2026.</t>
         </is>
       </c>
       <c r="P2" s="24" t="n"/>
@@ -742,6 +770,8 @@
       <c r="R2" s="24" t="n"/>
       <c r="S2" s="24" t="n"/>
       <c r="T2" s="24" t="n"/>
+      <c r="U2" s="24" t="n"/>
+      <c r="V2" s="24" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="24" t="n"/>
@@ -764,6 +794,8 @@
       <c r="R3" s="24" t="n"/>
       <c r="S3" s="24" t="n"/>
       <c r="T3" s="24" t="n"/>
+      <c r="U3" s="24" t="n"/>
+      <c r="V3" s="24" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
@@ -790,8 +822,10 @@
       <c r="R4" s="24" t="n"/>
       <c r="S4" s="24" t="n"/>
       <c r="T4" s="24" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="12">
+      <c r="U4" s="24" t="n"/>
+      <c r="V4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="32" customHeight="1" s="12">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Date</t>
@@ -808,45 +842,42 @@
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Pay Period</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>Date
+Paid</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Hours
 Claimed Missing</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Hours
 Actually Paid</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Shortfall
 (Hrs)</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
-        <is>
-          <t>Paid in
-Pay Run</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="inlineStr">
-        <is>
-          <t>Where to find it
-on that tab</t>
-        </is>
-      </c>
       <c r="I5" s="27" t="inlineStr">
         <is>
-          <t>Rate
-$/hr</t>
+          <t>Rate Paid</t>
         </is>
       </c>
       <c r="J5" s="27" t="inlineStr">
         <is>
-          <t>Gross Paid
-$</t>
+          <t>Where to find it on that tab</t>
         </is>
       </c>
       <c r="K5" s="27" t="inlineStr">
@@ -863,6 +894,8 @@
       <c r="R5" s="24" t="n"/>
       <c r="S5" s="24" t="n"/>
       <c r="T5" s="24" t="n"/>
+      <c r="U5" s="24" t="n"/>
+      <c r="V5" s="24" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="28" t="n">
@@ -878,36 +911,36 @@
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F6" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="31">
+      <c r="G6" s="32">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6)</f>
         <v/>
       </c>
-      <c r="F6" s="31">
-        <f>D6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="32">
+        <f>F6-G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="33">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6),""))))</f>
+        <v/>
+      </c>
+      <c r="J6" s="34" t="inlineStr">
         <is>
           <t>'20 Sept 2026 ' rows 3 and 4  (3.5 hrs 08:30-12:00  +  4.5 hrs 12:30-17:00)</t>
         </is>
       </c>
-      <c r="I6" s="33">
-        <f>IFERROR(J6/E6,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="33">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6)</f>
-        <v/>
-      </c>
       <c r="K6" s="29">
-        <f>IF(ROUND(F6,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
+        <f>IF(ROUND(H6,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
         <v/>
       </c>
       <c r="L6" s="24" t="n"/>
@@ -919,6 +952,8 @@
       <c r="R6" s="24" t="n"/>
       <c r="S6" s="24" t="n"/>
       <c r="T6" s="24" t="n"/>
+      <c r="U6" s="24" t="n"/>
+      <c r="V6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="28" t="n">
@@ -934,36 +969,36 @@
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F7" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="31">
+      <c r="G7" s="32">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7)</f>
         <v/>
       </c>
-      <c r="F7" s="31">
-        <f>D7-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" s="32">
+        <f>F7-G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="33">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7),""))))</f>
+        <v/>
+      </c>
+      <c r="J7" s="34" t="inlineStr">
         <is>
           <t>'20 Sept 2026 ' rows 5 and 6  (3.5 hrs 08:30-12:00  +  4.5 hrs 12:30-17:00)</t>
         </is>
       </c>
-      <c r="I7" s="33">
-        <f>IFERROR(J7/E7,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="33">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7)</f>
-        <v/>
-      </c>
       <c r="K7" s="29">
-        <f>IF(ROUND(F7,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
+        <f>IF(ROUND(H7,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
         <v/>
       </c>
       <c r="L7" s="24" t="n"/>
@@ -975,36 +1010,35 @@
       <c r="R7" s="24" t="n"/>
       <c r="S7" s="24" t="n"/>
       <c r="T7" s="24" t="n"/>
+      <c r="U7" s="24" t="n"/>
+      <c r="V7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>TOTAL CLAIMED</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n"/>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="35">
-        <f>SUM(D6:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="35">
-        <f>SUM(E6:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="35">
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="36">
         <f>SUM(F6:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="34" t="n"/>
-      <c r="H8" s="34" t="n"/>
-      <c r="I8" s="34" t="n"/>
-      <c r="J8" s="36">
-        <f>SUM(J6:J7)</f>
-        <v/>
-      </c>
-      <c r="K8" s="34">
-        <f>IF(ROUND(F8,2)=0,"NIL OWING - all "&amp;TEXT(D8,"0")&amp;" hrs paid ($"&amp;TEXT(J8,"#,##0.00")&amp;" gross)","AMOUNT OWING - investigate")</f>
+      <c r="G8" s="36">
+        <f>SUM(G6:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="36">
+        <f>SUM(H6:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="35" t="n"/>
+      <c r="J8" s="35" t="n"/>
+      <c r="K8" s="35">
+        <f>IF(ROUND(H8,2)=0,"NIL OWING - all "&amp;TEXT(F8,"0")&amp;" hrs paid","HOURS OWING - investigate")</f>
         <v/>
       </c>
       <c r="L8" s="24" t="n"/>
@@ -1016,11 +1050,13 @@
       <c r="R8" s="24" t="n"/>
       <c r="S8" s="24" t="n"/>
       <c r="T8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="46" customHeight="1" s="12">
+      <c r="U8" s="24" t="n"/>
+      <c r="V8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1" s="12">
       <c r="A9" s="37" t="inlineStr">
         <is>
-          <t>WHY IT LOOKED MISSING:  (1) Each day is split across two pay lines, either side of the lunch break - 3.5 hrs + 4.5 hrs - so neither line ever shows as "8 hours" when you scan the payslip.  (2) Both days sit in the fortnight ending 04/09/2026, but that fortnight was paid across TWO pay runs: the 48 hrs of DTTL work went through the 20 Sep 2026 run, while the 23.5 hrs of PwC work went through the 22 Sep 2026 run. Looking at only one of those payslips shows only part of the fortnight.</t>
+          <t>WHY IT LOOKED MISSING:  Each day is split across two pay lines, either side of the unpaid lunch break - 3.5 hrs + 4.5 hrs - so neither line ever shows as "8 hours" when you scan the payslip. Both days fall in the pay period 22/08/2026 - 04/09/2026, paid on 08/09/2026.</t>
         </is>
       </c>
       <c r="P9" s="24" t="n"/>
@@ -1028,6 +1064,8 @@
       <c r="R9" s="24" t="n"/>
       <c r="S9" s="24" t="n"/>
       <c r="T9" s="24" t="n"/>
+      <c r="U9" s="24" t="n"/>
+      <c r="V9" s="24" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="24" t="n"/>
@@ -1050,11 +1088,13 @@
       <c r="R10" s="24" t="n"/>
       <c r="S10" s="24" t="n"/>
       <c r="T10" s="24" t="n"/>
+      <c r="U10" s="24" t="n"/>
+      <c r="V10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="38" t="inlineStr">
         <is>
-          <t>B.  FORTNIGHT SUMMARY  -  timesheet hours vs hours actually paid</t>
+          <t>B.  PAY PERIOD SUMMARY  -  timesheet hours vs hours paid, by pay period and the date each was paid</t>
         </is>
       </c>
       <c r="B11" s="38" t="n"/>
@@ -1076,55 +1116,66 @@
       <c r="R11" s="24" t="n"/>
       <c r="S11" s="24" t="n"/>
       <c r="T11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="12">
+      <c r="U11" s="24" t="n"/>
+      <c r="V11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1" s="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Fortnight Ending</t>
+          <t>Pay Period</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Date
+Paid</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Source Tab in Workbook</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Timesheets
 (count)</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>Timesheet
 Hours</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>Paid
 Hours</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Variance
 (Hrs)</t>
         </is>
       </c>
-      <c r="F12" s="27" t="inlineStr">
-        <is>
-          <t>Variance
-($ @ $37.50)</t>
-        </is>
-      </c>
-      <c r="G12" s="27" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
+        <is>
+          <t>Rate Paid</t>
+        </is>
+      </c>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t>Rate
+Check</t>
+        </is>
+      </c>
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H12" s="27" t="inlineStr">
-        <is>
-          <t>Paid in Pay Run(s)</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="24" t="n"/>
       <c r="K12" s="24" t="n"/>
       <c r="L12" s="24" t="n"/>
       <c r="M12" s="24" t="n"/>
@@ -1135,42 +1186,51 @@
       <c r="R12" s="24" t="n"/>
       <c r="S12" s="24" t="n"/>
       <c r="T12" s="24" t="n"/>
+      <c r="U12" s="24" t="n"/>
+      <c r="V12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B13" s="40">
+      <c r="A13" s="39" t="inlineStr">
+        <is>
+          <t>25/07/2026 - 07/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="41">
         <f>COUNTIFS($C$21:$C$36,$A13)</f>
         <v/>
       </c>
-      <c r="C13" s="41">
-        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A13)</f>
-        <v/>
-      </c>
-      <c r="D13" s="41">
+      <c r="E13" s="42">
         <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A13)</f>
         <v/>
       </c>
-      <c r="E13" s="41">
-        <f>C13-D13</f>
-        <v/>
-      </c>
       <c r="F13" s="42">
-        <f>E13*37.5</f>
-        <v/>
-      </c>
-      <c r="G13" s="43">
-        <f>IF(ROUND(E13,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="H13" s="43" t="inlineStr">
-        <is>
-          <t>07 Aug 2026</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="24" t="n"/>
+        <f>SUMIFS($J$21:$J$36,$C$21:$C$36,$A13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="42">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="43">
+        <f>IFERROR(AVERAGEIFS($L$21:$L$36,$C$21:$C$36,$A13),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="41">
+        <f>IF(H13="","",IF(ROUND(H13,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="J13" s="39">
+        <f>IF(ROUND(G13,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="K13" s="24" t="n"/>
       <c r="L13" s="24" t="n"/>
       <c r="M13" s="24" t="n"/>
@@ -1181,42 +1241,51 @@
       <c r="R13" s="24" t="n"/>
       <c r="S13" s="24" t="n"/>
       <c r="T13" s="24" t="n"/>
+      <c r="U13" s="24" t="n"/>
+      <c r="V13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B14" s="40">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>08/08/2026 - 21/08/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>21 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="41">
         <f>COUNTIFS($C$21:$C$36,$A14)</f>
         <v/>
       </c>
-      <c r="C14" s="41">
-        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A14)</f>
-        <v/>
-      </c>
-      <c r="D14" s="41">
+      <c r="E14" s="42">
         <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A14)</f>
         <v/>
       </c>
-      <c r="E14" s="41">
-        <f>C14-D14</f>
-        <v/>
-      </c>
       <c r="F14" s="42">
-        <f>E14*37.5</f>
-        <v/>
-      </c>
-      <c r="G14" s="43">
-        <f>IF(ROUND(E14,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="H14" s="43" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="24" t="n"/>
+        <f>SUMIFS($J$21:$J$36,$C$21:$C$36,$A14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="42">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="43">
+        <f>IFERROR(AVERAGEIFS($L$21:$L$36,$C$21:$C$36,$A14),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="41">
+        <f>IF(H14="","",IF(ROUND(H14,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="J14" s="39">
+        <f>IF(ROUND(G14,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="K14" s="24" t="n"/>
       <c r="L14" s="24" t="n"/>
       <c r="M14" s="24" t="n"/>
@@ -1227,42 +1296,51 @@
       <c r="R14" s="24" t="n"/>
       <c r="S14" s="24" t="n"/>
       <c r="T14" s="24" t="n"/>
+      <c r="U14" s="24" t="n"/>
+      <c r="V14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B15" s="40">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t>20 Sept 2026 + 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="41">
         <f>COUNTIFS($C$21:$C$36,$A15)</f>
         <v/>
       </c>
-      <c r="C15" s="41">
-        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A15)</f>
-        <v/>
-      </c>
-      <c r="D15" s="41">
+      <c r="E15" s="42">
         <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A15)</f>
         <v/>
       </c>
-      <c r="E15" s="41">
-        <f>C15-D15</f>
-        <v/>
-      </c>
       <c r="F15" s="42">
-        <f>E15*37.5</f>
-        <v/>
-      </c>
-      <c r="G15" s="43">
-        <f>IF(ROUND(E15,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="H15" s="43" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 (DTTL 48 hrs) + 22 Sep 2026 (PwC 23.5 hrs)</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="n"/>
-      <c r="J15" s="24" t="n"/>
+        <f>SUMIFS($J$21:$J$36,$C$21:$C$36,$A15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="42">
+        <f>E15-F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="43">
+        <f>IFERROR(AVERAGEIFS($L$21:$L$36,$C$21:$C$36,$A15),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="41">
+        <f>IF(H15="","",IF(ROUND(H15,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="J15" s="39">
+        <f>IF(ROUND(G15,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="K15" s="24" t="n"/>
       <c r="L15" s="24" t="n"/>
       <c r="M15" s="24" t="n"/>
@@ -1273,42 +1351,51 @@
       <c r="R15" s="24" t="n"/>
       <c r="S15" s="24" t="n"/>
       <c r="T15" s="24" t="n"/>
+      <c r="U15" s="24" t="n"/>
+      <c r="V15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B16" s="40">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>05/09/2026 - 18/09/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="41">
         <f>COUNTIFS($C$21:$C$36,$A16)</f>
         <v/>
       </c>
-      <c r="C16" s="41">
-        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A16)</f>
-        <v/>
-      </c>
-      <c r="D16" s="41">
+      <c r="E16" s="42">
         <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A16)</f>
         <v/>
       </c>
-      <c r="E16" s="41">
-        <f>C16-D16</f>
-        <v/>
-      </c>
       <c r="F16" s="42">
-        <f>E16*37.5</f>
-        <v/>
-      </c>
-      <c r="G16" s="43">
-        <f>IF(ROUND(E16,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="H16" s="43" t="inlineStr">
-        <is>
-          <t>22 Sep 2026</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="n"/>
-      <c r="J16" s="24" t="n"/>
+        <f>SUMIFS($J$21:$J$36,$C$21:$C$36,$A16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="42">
+        <f>E16-F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="43">
+        <f>IFERROR(AVERAGEIFS($L$21:$L$36,$C$21:$C$36,$A16),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="41">
+        <f>IF(H16="","",IF(ROUND(H16,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="J16" s="39">
+        <f>IF(ROUND(G16,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="K16" s="24" t="n"/>
       <c r="L16" s="24" t="n"/>
       <c r="M16" s="24" t="n"/>
@@ -1319,6 +1406,8 @@
       <c r="R16" s="24" t="n"/>
       <c r="S16" s="24" t="n"/>
       <c r="T16" s="24" t="n"/>
+      <c r="U16" s="24" t="n"/>
+      <c r="V16" s="24" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="44" t="inlineStr">
@@ -1326,33 +1415,30 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="45">
-        <f>SUM(B13:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="46">
-        <f>SUM(C13:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="46">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44">
         <f>SUM(D13:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="45">
         <f>SUM(E13:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="45">
         <f>SUM(F13:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="44">
-        <f>IF(ROUND(E17,2)=0,"FULLY RECONCILED","VARIANCE - investigate")</f>
+      <c r="G17" s="45">
+        <f>SUM(G13:G16)</f>
         <v/>
       </c>
       <c r="H17" s="44" t="n"/>
-      <c r="I17" s="24" t="n"/>
-      <c r="J17" s="24" t="n"/>
+      <c r="I17" s="44" t="n"/>
+      <c r="J17" s="44">
+        <f>IF(ROUND(G17,2)=0,"FULLY RECONCILED","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="K17" s="24" t="n"/>
       <c r="L17" s="24" t="n"/>
       <c r="M17" s="24" t="n"/>
@@ -1363,6 +1449,8 @@
       <c r="R17" s="24" t="n"/>
       <c r="S17" s="24" t="n"/>
       <c r="T17" s="24" t="n"/>
+      <c r="U17" s="24" t="n"/>
+      <c r="V17" s="24" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="24" t="n"/>
@@ -1385,11 +1473,13 @@
       <c r="R18" s="24" t="n"/>
       <c r="S18" s="24" t="n"/>
       <c r="T18" s="24" t="n"/>
+      <c r="U18" s="24" t="n"/>
+      <c r="V18" s="24" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="38" t="inlineStr">
         <is>
-          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay run that paid it.  The Notes column shows how each day was split across pay lines either side of the unpaid break.</t>
+          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay period that paid it.  The Notes column shows how each day was split across pay lines either side of the unpaid break.</t>
         </is>
       </c>
       <c r="B19" s="38" t="n"/>
@@ -1411,8 +1501,10 @@
       <c r="R19" s="24" t="n"/>
       <c r="S19" s="24" t="n"/>
       <c r="T19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="12">
+      <c r="U19" s="24" t="n"/>
+      <c r="V19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1" s="12">
       <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Date</t>
@@ -1425,70 +1517,68 @@
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>Fortnight
-Ending</t>
+          <t>Pay Period</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
+          <t>Date
+Paid</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
           <t>Location / Client (per timesheet)</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="G20" s="27" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Break</t>
         </is>
       </c>
-      <c r="H20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Timesheet
 Hours</t>
         </is>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="J20" s="27" t="inlineStr">
         <is>
           <t>Paid
 Hours</t>
         </is>
       </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="K20" s="27" t="inlineStr">
         <is>
           <t>Variance
 (Hrs)</t>
         </is>
       </c>
-      <c r="K20" s="27" t="inlineStr">
-        <is>
-          <t>Paid in
-Pay Run</t>
-        </is>
-      </c>
       <c r="L20" s="27" t="inlineStr">
         <is>
-          <t>Rate Paid
-$/hr</t>
+          <t>Rate Paid</t>
         </is>
       </c>
       <c r="M20" s="27" t="inlineStr">
+        <is>
+          <t>Rate
+Check</t>
+        </is>
+      </c>
+      <c r="N20" s="27" t="inlineStr">
         <is>
           <t>Gross Paid
 $</t>
-        </is>
-      </c>
-      <c r="N20" s="27" t="inlineStr">
-        <is>
-          <t>Rate
-Check</t>
         </is>
       </c>
       <c r="O20" s="27" t="inlineStr">
@@ -1501,69 +1591,72 @@
       <c r="R20" s="24" t="n"/>
       <c r="S20" s="24" t="n"/>
       <c r="T20" s="24" t="n"/>
+      <c r="U20" s="24" t="n"/>
+      <c r="V20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="n">
+      <c r="A21" s="40" t="n">
         <v>46232</v>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C21" s="39" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>25/07/2026 - 07/08/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
         <is>
           <t>CBA FT Tech MEL - 12 months [ONS]</t>
         </is>
       </c>
-      <c r="E21" s="40" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>7:00 AM</t>
         </is>
       </c>
-      <c r="F21" s="40" t="inlineStr">
+      <c r="G21" s="41" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="G21" s="40" t="inlineStr">
+      <c r="H21" s="41" t="inlineStr">
         <is>
           <t>12:30-1:30</t>
         </is>
       </c>
-      <c r="H21" s="41" t="n">
+      <c r="I21" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="I21" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$D21)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$D21)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$D21)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$D21)</f>
-        <v/>
-      </c>
-      <c r="J21" s="41">
-        <f>H21-I21</f>
-        <v/>
-      </c>
-      <c r="K21" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$D21)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$D21)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$D21)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$D21)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L21" s="42">
-        <f>IFERROR(M21/I21,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$D21)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$D21)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$D21)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$D21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="40">
-        <f>IF(I21=0,"",IF(ROUND(L21,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L21)*I21,"0.00")))</f>
+      <c r="J21" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$E21)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$E21)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$E21)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$E21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="42">
+        <f>I21-J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$E21),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$E21),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$E21),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$E21),""))))</f>
+        <v/>
+      </c>
+      <c r="M21" s="41">
+        <f>IF(J21=0,"",IF(ROUND(L21,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N21" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A21,'07 Aug 2026'!$K$3:$K$6,$E21)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A21,'21 Aug 2026'!$K$3:$K$7,$E21)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$E21)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A21,'22 Sep 2026'!$K$3:$K$11,$E21)</f>
         <v/>
       </c>
       <c r="O21" s="48" t="inlineStr">
         <is>
-          <t>Paid as 5.5 + 2.5 hrs either side of break</t>
+          <t>Paid as 5.5 + 2.5 hrs either side of break. Rate later corrected to $37.50/hr - see Section D.</t>
         </is>
       </c>
       <c r="P21" s="24" t="n"/>
@@ -1571,69 +1664,72 @@
       <c r="R21" s="24" t="n"/>
       <c r="S21" s="24" t="n"/>
       <c r="T21" s="24" t="n"/>
+      <c r="U21" s="24" t="n"/>
+      <c r="V21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="n">
+      <c r="A22" s="40" t="n">
         <v>46233</v>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C22" s="39" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D22" s="43" t="inlineStr">
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>25/07/2026 - 07/08/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E22" s="39" t="inlineStr">
         <is>
           <t>PWC – MEL Technician [ONS]</t>
         </is>
       </c>
-      <c r="E22" s="40" t="inlineStr">
+      <c r="F22" s="41" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="G22" s="41" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="G22" s="40" t="inlineStr">
+      <c r="H22" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="41" t="n">
+      <c r="I22" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$D22)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$D22)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$D22)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$D22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="41">
-        <f>H22-I22</f>
-        <v/>
-      </c>
-      <c r="K22" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$D22)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$D22)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$D22)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$D22)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L22" s="42">
-        <f>IFERROR(M22/I22,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$D22)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$D22)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$D22)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$D22)</f>
-        <v/>
-      </c>
-      <c r="N22" s="40">
-        <f>IF(I22=0,"",IF(ROUND(L22,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L22)*I22,"0.00")))</f>
+      <c r="J22" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$E22)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$E22)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$E22)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$E22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="42">
+        <f>I22-J22</f>
+        <v/>
+      </c>
+      <c r="L22" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$E22),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$E22),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$E22),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$E22),""))))</f>
+        <v/>
+      </c>
+      <c r="M22" s="41">
+        <f>IF(J22=0,"",IF(ROUND(L22,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N22" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A22,'07 Aug 2026'!$K$3:$K$6,$E22)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A22,'21 Aug 2026'!$K$3:$K$7,$E22)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$E22)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A22,'22 Sep 2026'!$K$3:$K$11,$E22)</f>
         <v/>
       </c>
       <c r="O22" s="48" t="inlineStr">
         <is>
-          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location</t>
+          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location. Rate later corrected to $37.50/hr - see Section D.</t>
         </is>
       </c>
       <c r="P22" s="24" t="n"/>
@@ -1641,69 +1737,72 @@
       <c r="R22" s="24" t="n"/>
       <c r="S22" s="24" t="n"/>
       <c r="T22" s="24" t="n"/>
+      <c r="U22" s="24" t="n"/>
+      <c r="V22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="n">
+      <c r="A23" s="40" t="n">
         <v>46233</v>
       </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C23" s="39" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>25/07/2026 - 07/08/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E23" s="39" t="inlineStr">
         <is>
           <t>Aware Super AV Maintenance [ONS]</t>
         </is>
       </c>
-      <c r="E23" s="40" t="inlineStr">
+      <c r="F23" s="41" t="inlineStr">
         <is>
           <t>2:25 PM</t>
         </is>
       </c>
-      <c r="F23" s="40" t="inlineStr">
+      <c r="G23" s="41" t="inlineStr">
         <is>
           <t>6:25 PM</t>
         </is>
       </c>
-      <c r="G23" s="40" t="inlineStr">
+      <c r="H23" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="41" t="n">
+      <c r="I23" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="I23" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$D23)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$D23)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$D23)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$D23)</f>
-        <v/>
-      </c>
-      <c r="J23" s="41">
-        <f>H23-I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$D23)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$D23)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$D23)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$D23)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L23" s="42">
-        <f>IFERROR(M23/I23,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$D23)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$D23)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$D23)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$D23)</f>
-        <v/>
-      </c>
-      <c r="N23" s="40">
-        <f>IF(I23=0,"",IF(ROUND(L23,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L23)*I23,"0.00")))</f>
+      <c r="J23" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$E23)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$E23)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$E23)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$E23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="42">
+        <f>I23-J23</f>
+        <v/>
+      </c>
+      <c r="L23" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$E23),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$E23),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$E23),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$E23),""))))</f>
+        <v/>
+      </c>
+      <c r="M23" s="41">
+        <f>IF(J23=0,"",IF(ROUND(L23,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N23" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A23,'07 Aug 2026'!$K$3:$K$6,$E23)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A23,'21 Aug 2026'!$K$3:$K$7,$E23)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$E23)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A23,'22 Sep 2026'!$K$3:$K$11,$E23)</f>
         <v/>
       </c>
       <c r="O23" s="48" t="inlineStr">
         <is>
-          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location</t>
+          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location. Rate later corrected to $37.50/hr - see Section D.</t>
         </is>
       </c>
       <c r="P23" s="24" t="n"/>
@@ -1711,64 +1810,67 @@
       <c r="R23" s="24" t="n"/>
       <c r="S23" s="24" t="n"/>
       <c r="T23" s="24" t="n"/>
+      <c r="U23" s="24" t="n"/>
+      <c r="V23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="n">
+      <c r="A24" s="40" t="n">
         <v>46252</v>
       </c>
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C24" s="39" t="n">
-        <v>46255</v>
-      </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>08/08/2026 - 21/08/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E24" s="39" t="inlineStr">
         <is>
           <t>CBA FT Tech MEL - 12 months [ONS]</t>
         </is>
       </c>
-      <c r="E24" s="40" t="inlineStr">
+      <c r="F24" s="41" t="inlineStr">
         <is>
           <t>7:00 AM</t>
         </is>
       </c>
-      <c r="F24" s="40" t="inlineStr">
+      <c r="G24" s="41" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="G24" s="40" t="inlineStr">
+      <c r="H24" s="41" t="inlineStr">
         <is>
           <t>12:00-1:00</t>
         </is>
       </c>
-      <c r="H24" s="41" t="n">
+      <c r="I24" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="I24" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$D24)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$D24)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$D24)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$D24)</f>
-        <v/>
-      </c>
-      <c r="J24" s="41">
-        <f>H24-I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$D24)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$D24)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$D24)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$D24)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L24" s="42">
-        <f>IFERROR(M24/I24,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$D24)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$D24)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$D24)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$D24)</f>
-        <v/>
-      </c>
-      <c r="N24" s="40">
-        <f>IF(I24=0,"",IF(ROUND(L24,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L24)*I24,"0.00")))</f>
+      <c r="J24" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$E24)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$E24)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$E24)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$E24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="42">
+        <f>I24-J24</f>
+        <v/>
+      </c>
+      <c r="L24" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$E24),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$E24),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$E24),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$E24),""))))</f>
+        <v/>
+      </c>
+      <c r="M24" s="41">
+        <f>IF(J24=0,"",IF(ROUND(L24,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N24" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A24,'07 Aug 2026'!$K$3:$K$6,$E24)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A24,'21 Aug 2026'!$K$3:$K$7,$E24)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$E24)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A24,'22 Sep 2026'!$K$3:$K$11,$E24)</f>
         <v/>
       </c>
       <c r="O24" s="48" t="inlineStr">
@@ -1781,64 +1883,67 @@
       <c r="R24" s="24" t="n"/>
       <c r="S24" s="24" t="n"/>
       <c r="T24" s="24" t="n"/>
+      <c r="U24" s="24" t="n"/>
+      <c r="V24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="n">
+      <c r="A25" s="40" t="n">
         <v>46254</v>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C25" s="39" t="n">
-        <v>46255</v>
-      </c>
-      <c r="D25" s="43" t="inlineStr">
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>08/08/2026 - 21/08/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E25" s="39" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E25" s="40" t="inlineStr">
+      <c r="F25" s="41" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F25" s="40" t="inlineStr">
+      <c r="G25" s="41" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G25" s="40" t="inlineStr">
+      <c r="H25" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H25" s="41" t="n">
+      <c r="I25" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="I25" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)</f>
-        <v/>
-      </c>
-      <c r="J25" s="41">
-        <f>H25-I25</f>
-        <v/>
-      </c>
-      <c r="K25" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L25" s="42">
-        <f>IFERROR(M25/I25,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="40">
-        <f>IF(I25=0,"",IF(ROUND(L25,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L25)*I25,"0.00")))</f>
+      <c r="J25" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$E25)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$E25)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$E25)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$E25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="42">
+        <f>I25-J25</f>
+        <v/>
+      </c>
+      <c r="L25" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$E25),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$E25),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$E25),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$E25),""))))</f>
+        <v/>
+      </c>
+      <c r="M25" s="41">
+        <f>IF(J25=0,"",IF(ROUND(L25,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N25" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A25,'07 Aug 2026'!$K$3:$K$6,$E25)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A25,'21 Aug 2026'!$K$3:$K$7,$E25)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$E25)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A25,'22 Sep 2026'!$K$3:$K$11,$E25)</f>
         <v/>
       </c>
       <c r="O25" s="48" t="inlineStr">
@@ -1851,8 +1956,10 @@
       <c r="R25" s="24" t="n"/>
       <c r="S25" s="24" t="n"/>
       <c r="T25" s="24" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1" s="12">
+      <c r="U25" s="24" t="n"/>
+      <c r="V25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1" s="12">
       <c r="A26" s="28" t="n">
         <v>46258</v>
       </c>
@@ -1861,59 +1968,60 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="C26" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D26" s="30" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="F26" s="29" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="F26" s="29" t="inlineStr">
+      <c r="G26" s="29" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G26" s="29" t="inlineStr">
+      <c r="H26" s="29" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H26" s="31" t="n">
+      <c r="I26" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="I26" s="31">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$D26)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$D26)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$D26)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$D26)</f>
-        <v/>
-      </c>
-      <c r="J26" s="31">
-        <f>H26-I26</f>
-        <v/>
-      </c>
-      <c r="K26" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$D26)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$D26)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$D26)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$D26)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+      <c r="J26" s="32">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$E26)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$E26)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$E26)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$E26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="32">
+        <f>I26-J26</f>
         <v/>
       </c>
       <c r="L26" s="33">
-        <f>IFERROR(M26/I26,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="33">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$D26)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$D26)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$D26)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$D26)</f>
-        <v/>
-      </c>
-      <c r="N26" s="29">
-        <f>IF(I26=0,"",IF(ROUND(L26,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L26)*I26,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O26" s="49" t="inlineStr">
-        <is>
-          <t>QUERY - claimed missing. PAID IN FULL in the 20 Sep 2026 run as 3.5 + 4.5 hrs, $300.00 gross. See Section A.</t>
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$E26),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$E26),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$E26),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$E26),""))))</f>
+        <v/>
+      </c>
+      <c r="M26" s="29">
+        <f>IF(J26=0,"",IF(ROUND(L26,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N26" s="49">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A26,'07 Aug 2026'!$K$3:$K$6,$E26)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A26,'21 Aug 2026'!$K$3:$K$7,$E26)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$E26)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A26,'22 Sep 2026'!$K$3:$K$11,$E26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="50" t="inlineStr">
+        <is>
+          <t>QUERY - claimed missing. PAID IN FULL as 3.5 + 4.5 hrs. See Section A.</t>
         </is>
       </c>
       <c r="P26" s="24" t="n"/>
@@ -1921,69 +2029,72 @@
       <c r="R26" s="24" t="n"/>
       <c r="S26" s="24" t="n"/>
       <c r="T26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="39" t="n">
+      <c r="U26" s="24" t="n"/>
+      <c r="V26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1" s="12">
+      <c r="A27" s="51" t="n">
         <v>46259</v>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="52" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C27" s="39" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E27" s="53" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E27" s="40" t="inlineStr">
+      <c r="F27" s="52" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F27" s="40" t="inlineStr">
+      <c r="G27" s="52" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G27" s="40" t="inlineStr">
+      <c r="H27" s="52" t="inlineStr">
         <is>
           <t>12:00-1:00</t>
         </is>
       </c>
-      <c r="H27" s="41" t="n">
+      <c r="I27" s="55" t="n">
         <v>8</v>
       </c>
-      <c r="I27" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$D27)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$D27)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$D27)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$D27)</f>
-        <v/>
-      </c>
-      <c r="J27" s="41">
-        <f>H27-I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$D27)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$D27)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$D27)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$D27)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L27" s="42">
-        <f>IFERROR(M27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$D27)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$D27)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$D27)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$D27)</f>
-        <v/>
-      </c>
-      <c r="N27" s="40">
-        <f>IF(I27=0,"",IF(ROUND(L27,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L27)*I27,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O27" s="48" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 4 hrs</t>
+      <c r="J27" s="55">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$E27)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$E27)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$E27)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$E27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="55">
+        <f>I27-J27</f>
+        <v/>
+      </c>
+      <c r="L27" s="56">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$E27),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$E27),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$E27),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$E27),""))))</f>
+        <v/>
+      </c>
+      <c r="M27" s="52">
+        <f>IF(J27=0,"",IF(ROUND(L27,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N27" s="57">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A27,'07 Aug 2026'!$K$3:$K$6,$E27)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A27,'21 Aug 2026'!$K$3:$K$7,$E27)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$E27)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A27,'22 Sep 2026'!$K$3:$K$11,$E27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="58" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 4 hrs. Appears on the 22 Sep 2026 tab, not with the rest of this period - confirm the date actually paid.</t>
         </is>
       </c>
       <c r="P27" s="24" t="n"/>
@@ -1991,69 +2102,72 @@
       <c r="R27" s="24" t="n"/>
       <c r="S27" s="24" t="n"/>
       <c r="T27" s="24" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="39" t="n">
+      <c r="U27" s="24" t="n"/>
+      <c r="V27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1" s="12">
+      <c r="A28" s="51" t="n">
         <v>46260</v>
       </c>
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B28" s="52" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C28" s="39" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="C28" s="53" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E28" s="53" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E28" s="40" t="inlineStr">
+      <c r="F28" s="52" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="G28" s="52" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="G28" s="40" t="inlineStr">
+      <c r="H28" s="52" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H28" s="41" t="n">
+      <c r="I28" s="55" t="n">
         <v>7.5</v>
       </c>
-      <c r="I28" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$D28)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$D28)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$D28)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$D28)</f>
-        <v/>
-      </c>
-      <c r="J28" s="41">
-        <f>H28-I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$D28)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$D28)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$D28)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$D28)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L28" s="42">
-        <f>IFERROR(M28/I28,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$D28)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$D28)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$D28)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$D28)</f>
-        <v/>
-      </c>
-      <c r="N28" s="40">
-        <f>IF(I28=0,"",IF(ROUND(L28,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L28)*I28,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O28" s="48" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 3.5 hrs</t>
+      <c r="J28" s="55">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$E28)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$E28)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$E28)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$E28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="55">
+        <f>I28-J28</f>
+        <v/>
+      </c>
+      <c r="L28" s="56">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$E28),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$E28),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$E28),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$E28),""))))</f>
+        <v/>
+      </c>
+      <c r="M28" s="52">
+        <f>IF(J28=0,"",IF(ROUND(L28,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N28" s="57">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A28,'07 Aug 2026'!$K$3:$K$6,$E28)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A28,'21 Aug 2026'!$K$3:$K$7,$E28)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$E28)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A28,'22 Sep 2026'!$K$3:$K$11,$E28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="58" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 3.5 hrs. Appears on the 22 Sep 2026 tab, not with the rest of this period - confirm the date actually paid.</t>
         </is>
       </c>
       <c r="P28" s="24" t="n"/>
@@ -2061,69 +2175,72 @@
       <c r="R28" s="24" t="n"/>
       <c r="S28" s="24" t="n"/>
       <c r="T28" s="24" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="39" t="n">
+      <c r="U28" s="24" t="n"/>
+      <c r="V28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="32" customHeight="1" s="12">
+      <c r="A29" s="51" t="n">
         <v>46261</v>
       </c>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="52" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C29" s="39" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
+      <c r="C29" s="53" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E29" s="53" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E29" s="40" t="inlineStr">
+      <c r="F29" s="52" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F29" s="40" t="inlineStr">
+      <c r="G29" s="52" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G29" s="40" t="inlineStr">
+      <c r="H29" s="52" t="inlineStr">
         <is>
           <t>12:00-1:00</t>
         </is>
       </c>
-      <c r="H29" s="41" t="n">
+      <c r="I29" s="55" t="n">
         <v>8</v>
       </c>
-      <c r="I29" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$D29)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$D29)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$D29)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$D29)</f>
-        <v/>
-      </c>
-      <c r="J29" s="41">
-        <f>H29-I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$D29)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$D29)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$D29)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$D29)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L29" s="42">
-        <f>IFERROR(M29/I29,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$D29)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$D29)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$D29)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$D29)</f>
-        <v/>
-      </c>
-      <c r="N29" s="40">
-        <f>IF(I29=0,"",IF(ROUND(L29,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L29)*I29,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O29" s="48" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 4 hrs</t>
+      <c r="J29" s="55">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$E29)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$E29)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$E29)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$E29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="55">
+        <f>I29-J29</f>
+        <v/>
+      </c>
+      <c r="L29" s="56">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$E29),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$E29),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$E29),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$E29),""))))</f>
+        <v/>
+      </c>
+      <c r="M29" s="52">
+        <f>IF(J29=0,"",IF(ROUND(L29,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N29" s="57">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A29,'07 Aug 2026'!$K$3:$K$6,$E29)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A29,'21 Aug 2026'!$K$3:$K$7,$E29)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$E29)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A29,'22 Sep 2026'!$K$3:$K$11,$E29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="58" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 4 hrs. Appears on the 22 Sep 2026 tab, not with the rest of this period - confirm the date actually paid.</t>
         </is>
       </c>
       <c r="P29" s="24" t="n"/>
@@ -2131,8 +2248,10 @@
       <c r="R29" s="24" t="n"/>
       <c r="S29" s="24" t="n"/>
       <c r="T29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1" s="12">
+      <c r="U29" s="24" t="n"/>
+      <c r="V29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1" s="12">
       <c r="A30" s="28" t="n">
         <v>46262</v>
       </c>
@@ -2141,59 +2260,60 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="C30" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="F30" s="29" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="F30" s="29" t="inlineStr">
+      <c r="G30" s="29" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G30" s="29" t="inlineStr">
+      <c r="H30" s="29" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H30" s="31" t="n">
+      <c r="I30" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="I30" s="31">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$D30)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$D30)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$D30)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$D30)</f>
-        <v/>
-      </c>
-      <c r="J30" s="31">
-        <f>H30-I30</f>
-        <v/>
-      </c>
-      <c r="K30" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$D30)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$D30)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$D30)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$D30)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
+      <c r="J30" s="32">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$E30)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$E30)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$E30)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$E30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="32">
+        <f>I30-J30</f>
         <v/>
       </c>
       <c r="L30" s="33">
-        <f>IFERROR(M30/I30,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="33">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$D30)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$D30)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$D30)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$D30)</f>
-        <v/>
-      </c>
-      <c r="N30" s="29">
-        <f>IF(I30=0,"",IF(ROUND(L30,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L30)*I30,"0.00")))</f>
-        <v/>
-      </c>
-      <c r="O30" s="49" t="inlineStr">
-        <is>
-          <t>QUERY - claimed missing. PAID IN FULL in the 20 Sep 2026 run as 3.5 + 4.5 hrs, $300.00 gross. See Section A.</t>
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$E30),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$E30),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$E30),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$E30),""))))</f>
+        <v/>
+      </c>
+      <c r="M30" s="29">
+        <f>IF(J30=0,"",IF(ROUND(L30,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N30" s="49">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A30,'07 Aug 2026'!$K$3:$K$6,$E30)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A30,'21 Aug 2026'!$K$3:$K$7,$E30)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$E30)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A30,'22 Sep 2026'!$K$3:$K$11,$E30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="50" t="inlineStr">
+        <is>
+          <t>QUERY - claimed missing. PAID IN FULL as 3.5 + 4.5 hrs. See Section A.</t>
         </is>
       </c>
       <c r="P30" s="24" t="n"/>
@@ -2201,64 +2321,67 @@
       <c r="R30" s="24" t="n"/>
       <c r="S30" s="24" t="n"/>
       <c r="T30" s="24" t="n"/>
+      <c r="U30" s="24" t="n"/>
+      <c r="V30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="39" t="n">
+      <c r="A31" s="40" t="n">
         <v>46265</v>
       </c>
-      <c r="B31" s="40" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C31" s="39" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D31" s="43" t="inlineStr">
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E31" s="39" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E31" s="40" t="inlineStr">
+      <c r="F31" s="41" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="F31" s="40" t="inlineStr">
+      <c r="G31" s="41" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G31" s="40" t="inlineStr">
+      <c r="H31" s="41" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H31" s="41" t="n">
+      <c r="I31" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="I31" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$D31)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$D31)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$D31)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$D31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="41">
-        <f>H31-I31</f>
-        <v/>
-      </c>
-      <c r="K31" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$D31)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$D31)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$D31)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$D31)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L31" s="42">
-        <f>IFERROR(M31/I31,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$D31)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$D31)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$D31)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$D31)</f>
-        <v/>
-      </c>
-      <c r="N31" s="40">
-        <f>IF(I31=0,"",IF(ROUND(L31,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L31)*I31,"0.00")))</f>
+      <c r="J31" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$E31)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$E31)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$E31)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$E31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="42">
+        <f>I31-J31</f>
+        <v/>
+      </c>
+      <c r="L31" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$E31),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$E31),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$E31),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$E31),""))))</f>
+        <v/>
+      </c>
+      <c r="M31" s="41">
+        <f>IF(J31=0,"",IF(ROUND(L31,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N31" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A31,'07 Aug 2026'!$K$3:$K$6,$E31)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A31,'21 Aug 2026'!$K$3:$K$7,$E31)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$E31)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A31,'22 Sep 2026'!$K$3:$K$11,$E31)</f>
         <v/>
       </c>
       <c r="O31" s="48" t="inlineStr">
@@ -2271,64 +2394,67 @@
       <c r="R31" s="24" t="n"/>
       <c r="S31" s="24" t="n"/>
       <c r="T31" s="24" t="n"/>
+      <c r="U31" s="24" t="n"/>
+      <c r="V31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="39" t="n">
+      <c r="A32" s="40" t="n">
         <v>46266</v>
       </c>
-      <c r="B32" s="40" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C32" s="39" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D32" s="43" t="inlineStr">
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E32" s="39" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E32" s="40" t="inlineStr">
+      <c r="F32" s="41" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="G32" s="41" t="inlineStr">
         <is>
           <t>5:30 PM</t>
         </is>
       </c>
-      <c r="G32" s="40" t="inlineStr">
+      <c r="H32" s="41" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H32" s="41" t="n">
+      <c r="I32" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="I32" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$D32)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$D32)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$D32)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$D32)</f>
-        <v/>
-      </c>
-      <c r="J32" s="41">
-        <f>H32-I32</f>
-        <v/>
-      </c>
-      <c r="K32" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$D32)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$D32)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$D32)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$D32)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L32" s="42">
-        <f>IFERROR(M32/I32,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$D32)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$D32)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$D32)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$D32)</f>
-        <v/>
-      </c>
-      <c r="N32" s="40">
-        <f>IF(I32=0,"",IF(ROUND(L32,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L32)*I32,"0.00")))</f>
+      <c r="J32" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$E32)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$E32)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$E32)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$E32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="42">
+        <f>I32-J32</f>
+        <v/>
+      </c>
+      <c r="L32" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$E32),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$E32),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$E32),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$E32),""))))</f>
+        <v/>
+      </c>
+      <c r="M32" s="41">
+        <f>IF(J32=0,"",IF(ROUND(L32,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N32" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A32,'07 Aug 2026'!$K$3:$K$6,$E32)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A32,'21 Aug 2026'!$K$3:$K$7,$E32)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$E32)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A32,'22 Sep 2026'!$K$3:$K$11,$E32)</f>
         <v/>
       </c>
       <c r="O32" s="48" t="inlineStr">
@@ -2341,64 +2467,67 @@
       <c r="R32" s="24" t="n"/>
       <c r="S32" s="24" t="n"/>
       <c r="T32" s="24" t="n"/>
+      <c r="U32" s="24" t="n"/>
+      <c r="V32" s="24" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="39" t="n">
+      <c r="A33" s="40" t="n">
         <v>46267</v>
       </c>
-      <c r="B33" s="40" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C33" s="39" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="C33" s="39" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E33" s="39" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E33" s="40" t="inlineStr">
+      <c r="F33" s="41" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="F33" s="40" t="inlineStr">
+      <c r="G33" s="41" t="inlineStr">
         <is>
           <t>5:30 PM</t>
         </is>
       </c>
-      <c r="G33" s="40" t="inlineStr">
+      <c r="H33" s="41" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H33" s="41" t="n">
+      <c r="I33" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="I33" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$D33)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$D33)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$D33)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$D33)</f>
-        <v/>
-      </c>
-      <c r="J33" s="41">
-        <f>H33-I33</f>
-        <v/>
-      </c>
-      <c r="K33" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$D33)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$D33)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$D33)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$D33)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L33" s="42">
-        <f>IFERROR(M33/I33,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$D33)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$D33)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$D33)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$D33)</f>
-        <v/>
-      </c>
-      <c r="N33" s="40">
-        <f>IF(I33=0,"",IF(ROUND(L33,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L33)*I33,"0.00")))</f>
+      <c r="J33" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$E33)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$E33)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$E33)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$E33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="42">
+        <f>I33-J33</f>
+        <v/>
+      </c>
+      <c r="L33" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$E33),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$E33),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$E33),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$E33),""))))</f>
+        <v/>
+      </c>
+      <c r="M33" s="41">
+        <f>IF(J33=0,"",IF(ROUND(L33,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N33" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A33,'07 Aug 2026'!$K$3:$K$6,$E33)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A33,'21 Aug 2026'!$K$3:$K$7,$E33)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$E33)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A33,'22 Sep 2026'!$K$3:$K$11,$E33)</f>
         <v/>
       </c>
       <c r="O33" s="48" t="inlineStr">
@@ -2411,64 +2540,67 @@
       <c r="R33" s="24" t="n"/>
       <c r="S33" s="24" t="n"/>
       <c r="T33" s="24" t="n"/>
+      <c r="U33" s="24" t="n"/>
+      <c r="V33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="39" t="n">
+      <c r="A34" s="40" t="n">
         <v>46269</v>
       </c>
-      <c r="B34" s="40" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C34" s="39" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D34" s="43" t="inlineStr">
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E34" s="39" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E34" s="40" t="inlineStr">
+      <c r="F34" s="41" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="G34" s="41" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G34" s="40" t="inlineStr">
+      <c r="H34" s="41" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H34" s="41" t="n">
+      <c r="I34" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="I34" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$D34)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$D34)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$D34)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$D34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="41">
-        <f>H34-I34</f>
-        <v/>
-      </c>
-      <c r="K34" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$D34)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$D34)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$D34)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$D34)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L34" s="42">
-        <f>IFERROR(M34/I34,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$D34)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$D34)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$D34)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$D34)</f>
-        <v/>
-      </c>
-      <c r="N34" s="40">
-        <f>IF(I34=0,"",IF(ROUND(L34,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L34)*I34,"0.00")))</f>
+      <c r="J34" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$E34)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$E34)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$E34)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$E34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="42">
+        <f>I34-J34</f>
+        <v/>
+      </c>
+      <c r="L34" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$E34),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$E34),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$E34),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$E34),""))))</f>
+        <v/>
+      </c>
+      <c r="M34" s="41">
+        <f>IF(J34=0,"",IF(ROUND(L34,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N34" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A34,'07 Aug 2026'!$K$3:$K$6,$E34)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A34,'21 Aug 2026'!$K$3:$K$7,$E34)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$E34)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A34,'22 Sep 2026'!$K$3:$K$11,$E34)</f>
         <v/>
       </c>
       <c r="O34" s="48" t="inlineStr">
@@ -2481,64 +2613,67 @@
       <c r="R34" s="24" t="n"/>
       <c r="S34" s="24" t="n"/>
       <c r="T34" s="24" t="n"/>
+      <c r="U34" s="24" t="n"/>
+      <c r="V34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="39" t="n">
+      <c r="A35" s="40" t="n">
         <v>46275</v>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C35" s="39" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="C35" s="39" t="inlineStr">
+        <is>
+          <t>05/09/2026 - 18/09/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E35" s="39" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E35" s="40" t="inlineStr">
+      <c r="F35" s="41" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F35" s="40" t="inlineStr">
+      <c r="G35" s="41" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G35" s="40" t="inlineStr">
+      <c r="H35" s="41" t="inlineStr">
         <is>
           <t>12:00-1:00</t>
         </is>
       </c>
-      <c r="H35" s="41" t="n">
+      <c r="I35" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="I35" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$D35)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$D35)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$D35)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$D35)</f>
-        <v/>
-      </c>
-      <c r="J35" s="41">
-        <f>H35-I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$D35)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$D35)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$D35)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$D35)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L35" s="42">
-        <f>IFERROR(M35/I35,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$D35)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$D35)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$D35)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$D35)</f>
-        <v/>
-      </c>
-      <c r="N35" s="40">
-        <f>IF(I35=0,"",IF(ROUND(L35,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L35)*I35,"0.00")))</f>
+      <c r="J35" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$E35)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$E35)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$E35)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$E35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="42">
+        <f>I35-J35</f>
+        <v/>
+      </c>
+      <c r="L35" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$E35),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$E35),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$E35),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$E35),""))))</f>
+        <v/>
+      </c>
+      <c r="M35" s="41">
+        <f>IF(J35=0,"",IF(ROUND(L35,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N35" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A35,'07 Aug 2026'!$K$3:$K$6,$E35)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A35,'21 Aug 2026'!$K$3:$K$7,$E35)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$E35)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A35,'22 Sep 2026'!$K$3:$K$11,$E35)</f>
         <v/>
       </c>
       <c r="O35" s="48" t="inlineStr">
@@ -2551,64 +2686,67 @@
       <c r="R35" s="24" t="n"/>
       <c r="S35" s="24" t="n"/>
       <c r="T35" s="24" t="n"/>
+      <c r="U35" s="24" t="n"/>
+      <c r="V35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="39" t="n">
+      <c r="A36" s="40" t="n">
         <v>46282</v>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C36" s="39" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D36" s="43" t="inlineStr">
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>05/09/2026 - 18/09/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E36" s="39" t="inlineStr">
         <is>
           <t>Aware Super AV Maintenance [ONS]</t>
         </is>
       </c>
-      <c r="E36" s="40" t="inlineStr">
+      <c r="F36" s="41" t="inlineStr">
         <is>
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="G36" s="41" t="inlineStr">
         <is>
           <t>3:30 PM</t>
         </is>
       </c>
-      <c r="G36" s="40" t="inlineStr">
+      <c r="H36" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H36" s="41" t="n">
+      <c r="I36" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="I36" s="41">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)</f>
-        <v/>
-      </c>
-      <c r="J36" s="41">
-        <f>H36-I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="40">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L36" s="42">
-        <f>IFERROR(M36/I36,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="42">
-        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)</f>
-        <v/>
-      </c>
-      <c r="N36" s="40">
-        <f>IF(I36=0,"",IF(ROUND(L36,2)=37.5,"OK","UNDER - $"&amp;TEXT((37.5-L36)*I36,"0.00")))</f>
+      <c r="J36" s="42">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$E36)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$E36)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$E36)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$E36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="42">
+        <f>I36-J36</f>
+        <v/>
+      </c>
+      <c r="L36" s="43">
+        <f>IFERROR(AVERAGEIFS('07 Aug 2026'!$M$3:$M$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$E36),IFERROR(AVERAGEIFS('21 Aug 2026'!$M$3:$M$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$E36),IFERROR(AVERAGEIFS('20 Sept 2026 '!$M$3:$M$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$E36),IFERROR(AVERAGEIFS('22 Sep 2026'!$M$3:$M$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$E36),""))))</f>
+        <v/>
+      </c>
+      <c r="M36" s="41">
+        <f>IF(J36=0,"",IF(ROUND(L36,2)=37.5,"OK","NOT $37.50 - see Section D"))</f>
+        <v/>
+      </c>
+      <c r="N36" s="47">
+        <f>SUMIFS('07 Aug 2026'!$O$3:$O$6,'07 Aug 2026'!$S$3:$S$6,$A36,'07 Aug 2026'!$K$3:$K$6,$E36)+SUMIFS('21 Aug 2026'!$O$3:$O$7,'21 Aug 2026'!$S$3:$S$7,$A36,'21 Aug 2026'!$K$3:$K$7,$E36)+SUMIFS('20 Sept 2026 '!$O$3:$O$14,'20 Sept 2026 '!$S$3:$S$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$E36)+SUMIFS('22 Sep 2026'!$O$3:$O$11,'22 Sep 2026'!$S$3:$S$11,$A36,'22 Sep 2026'!$K$3:$K$11,$E36)</f>
         <v/>
       </c>
       <c r="O36" s="48" t="inlineStr">
@@ -2621,6 +2759,8 @@
       <c r="R36" s="24" t="n"/>
       <c r="S36" s="24" t="n"/>
       <c r="T36" s="24" t="n"/>
+      <c r="U36" s="24" t="n"/>
+      <c r="V36" s="24" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="44" t="inlineStr">
@@ -2634,34 +2774,36 @@
       <c r="E37" s="44" t="n"/>
       <c r="F37" s="44" t="n"/>
       <c r="G37" s="44" t="n"/>
-      <c r="H37" s="46">
-        <f>SUM(H21:H36)</f>
-        <v/>
-      </c>
-      <c r="I37" s="46">
+      <c r="H37" s="44" t="n"/>
+      <c r="I37" s="45">
         <f>SUM(I21:I36)</f>
         <v/>
       </c>
-      <c r="J37" s="46">
+      <c r="J37" s="45">
         <f>SUM(J21:J36)</f>
         <v/>
       </c>
-      <c r="K37" s="44" t="n"/>
+      <c r="K37" s="45">
+        <f>SUM(K21:K36)</f>
+        <v/>
+      </c>
       <c r="L37" s="44" t="n"/>
-      <c r="M37" s="47">
-        <f>SUM(M21:M36)</f>
-        <v/>
-      </c>
-      <c r="N37" s="44">
-        <f>IF(ROUND(J37,2)=0,"HOURS AGREE","VARIANCE")</f>
-        <v/>
-      </c>
-      <c r="O37" s="44" t="n"/>
+      <c r="M37" s="44" t="n"/>
+      <c r="N37" s="59">
+        <f>SUM(N21:N36)</f>
+        <v/>
+      </c>
+      <c r="O37" s="44">
+        <f>IF(ROUND(K37,2)=0,"HOURS AGREE","VARIANCE")</f>
+        <v/>
+      </c>
       <c r="P37" s="24" t="n"/>
       <c r="Q37" s="24" t="n"/>
       <c r="R37" s="24" t="n"/>
       <c r="S37" s="24" t="n"/>
       <c r="T37" s="24" t="n"/>
+      <c r="U37" s="24" t="n"/>
+      <c r="V37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="24" t="n"/>
@@ -2684,11 +2826,13 @@
       <c r="R38" s="24" t="n"/>
       <c r="S38" s="24" t="n"/>
       <c r="T38" s="24" t="n"/>
+      <c r="U38" s="24" t="n"/>
+      <c r="V38" s="24" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="38" t="inlineStr">
         <is>
-          <t>D.  PAY RATE ERROR AND CORRECTION  -  fortnight ending 07/08/2026</t>
+          <t>D.  PAY RATE REVIEW  -  the incorrect rate on the pay period 25/07/2026 - 07/08/2026, and its correction</t>
         </is>
       </c>
       <c r="B39" s="38" t="n"/>
@@ -2710,8 +2854,10 @@
       <c r="R39" s="24" t="n"/>
       <c r="S39" s="24" t="n"/>
       <c r="T39" s="24" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1" s="12">
+      <c r="U39" s="24" t="n"/>
+      <c r="V39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1" s="12">
       <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Item</t>
@@ -2719,7 +2865,7 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Pay Run</t>
+          <t>Paid On</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
@@ -2729,20 +2875,15 @@
       </c>
       <c r="D40" s="27" t="inlineStr">
         <is>
-          <t>Rate
-$/hr</t>
+          <t>Rate Applied</t>
         </is>
       </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
-          <t>Gross $</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="inlineStr">
-        <is>
           <t>Comment</t>
         </is>
       </c>
+      <c r="F40" s="24" t="n"/>
       <c r="G40" s="24" t="n"/>
       <c r="H40" s="24" t="n"/>
       <c r="I40" s="24" t="n"/>
@@ -2757,34 +2898,32 @@
       <c r="R40" s="24" t="n"/>
       <c r="S40" s="24" t="n"/>
       <c r="T40" s="24" t="n"/>
+      <c r="U40" s="24" t="n"/>
+      <c r="V40" s="24" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="43" t="inlineStr">
-        <is>
-          <t>Paid at incorrect rate</t>
-        </is>
-      </c>
-      <c r="B41" s="43" t="inlineStr">
-        <is>
-          <t>07 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C41" s="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>Rate originally applied</t>
+        </is>
+      </c>
+      <c r="B41" s="40" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C41" s="42">
         <f>'07 Aug 2026'!G3+'07 Aug 2026'!G4+'07 Aug 2026'!G5+'07 Aug 2026'!G6</f>
         <v/>
       </c>
-      <c r="D41" s="42" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="E41" s="42">
-        <f>SUM('07 Aug 2026'!O3:O6)</f>
-        <v/>
-      </c>
-      <c r="F41" s="48" t="inlineStr">
-        <is>
-          <t>Original payment - rate used was $35.15/hr</t>
-        </is>
-      </c>
+      <c r="D41" s="43">
+        <f>'07 Aug 2026'!M3</f>
+        <v/>
+      </c>
+      <c r="E41" s="48" t="inlineStr">
+        <is>
+          <t>INCORRECT - the rate used on the first pay period</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="n"/>
       <c r="G41" s="24" t="n"/>
       <c r="H41" s="24" t="n"/>
       <c r="I41" s="24" t="n"/>
@@ -2799,34 +2938,31 @@
       <c r="R41" s="24" t="n"/>
       <c r="S41" s="24" t="n"/>
       <c r="T41" s="24" t="n"/>
+      <c r="U41" s="24" t="n"/>
+      <c r="V41" s="24" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="43" t="inlineStr">
-        <is>
-          <t>Should have been paid</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="inlineStr">
-        <is>
-          <t>07 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C42" s="41">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>Correct rate for the role</t>
+        </is>
+      </c>
+      <c r="B42" s="40" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C42" s="42">
         <f>C41</f>
         <v/>
       </c>
-      <c r="D42" s="42" t="n">
+      <c r="D42" s="43" t="n">
         <v>37.5</v>
       </c>
-      <c r="E42" s="42">
-        <f>C42*D42</f>
-        <v/>
-      </c>
-      <c r="F42" s="48" t="inlineStr">
-        <is>
-          <t>Correct casual ordinary rate is $37.50/hr</t>
-        </is>
-      </c>
+      <c r="E42" s="48" t="inlineStr">
+        <is>
+          <t>Casual Ordinary Hours rate that should have applied</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="n"/>
       <c r="G42" s="24" t="n"/>
       <c r="H42" s="24" t="n"/>
       <c r="I42" s="24" t="n"/>
@@ -2841,25 +2977,32 @@
       <c r="R42" s="24" t="n"/>
       <c r="S42" s="24" t="n"/>
       <c r="T42" s="24" t="n"/>
+      <c r="U42" s="24" t="n"/>
+      <c r="V42" s="24" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="50" t="inlineStr">
-        <is>
-          <t>Underpayment</t>
-        </is>
-      </c>
-      <c r="B43" s="50" t="inlineStr"/>
-      <c r="C43" s="51" t="inlineStr"/>
-      <c r="D43" s="52" t="inlineStr"/>
-      <c r="E43" s="52">
-        <f>E42-E41</f>
-        <v/>
-      </c>
-      <c r="F43" s="53" t="inlineStr">
-        <is>
-          <t>Shortfall on the first fortnight</t>
-        </is>
-      </c>
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>Reversal line</t>
+        </is>
+      </c>
+      <c r="B43" s="40" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C43" s="42">
+        <f>'21 Aug 2026'!G3</f>
+        <v/>
+      </c>
+      <c r="D43" s="43">
+        <f>'21 Aug 2026'!M3</f>
+        <v/>
+      </c>
+      <c r="E43" s="48" t="inlineStr">
+        <is>
+          <t>All 16 hrs paid at the incorrect rate were reversed</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="n"/>
       <c r="G43" s="24" t="n"/>
       <c r="H43" s="24" t="n"/>
       <c r="I43" s="24" t="n"/>
@@ -2874,35 +3017,32 @@
       <c r="R43" s="24" t="n"/>
       <c r="S43" s="24" t="n"/>
       <c r="T43" s="24" t="n"/>
+      <c r="U43" s="24" t="n"/>
+      <c r="V43" s="24" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="43" t="inlineStr">
-        <is>
-          <t>Reversal of incorrect rate</t>
-        </is>
-      </c>
-      <c r="B44" s="43" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C44" s="41">
-        <f>'21 Aug 2026'!G3</f>
-        <v/>
-      </c>
-      <c r="D44" s="42">
-        <f>'21 Aug 2026'!M3</f>
-        <v/>
-      </c>
-      <c r="E44" s="42">
-        <f>'21 Aug 2026'!O3</f>
-        <v/>
-      </c>
-      <c r="F44" s="48" t="inlineStr">
-        <is>
-          <t>Payroll reversed the full 16 hrs at $35.15</t>
-        </is>
-      </c>
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t>Re-payment line</t>
+        </is>
+      </c>
+      <c r="B44" s="40" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C44" s="42">
+        <f>'21 Aug 2026'!G4</f>
+        <v/>
+      </c>
+      <c r="D44" s="43">
+        <f>'21 Aug 2026'!M4</f>
+        <v/>
+      </c>
+      <c r="E44" s="48" t="inlineStr">
+        <is>
+          <t>The same 16 hrs re-paid at the correct rate</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="n"/>
       <c r="G44" s="24" t="n"/>
       <c r="H44" s="24" t="n"/>
       <c r="I44" s="24" t="n"/>
@@ -2917,35 +3057,29 @@
       <c r="R44" s="24" t="n"/>
       <c r="S44" s="24" t="n"/>
       <c r="T44" s="24" t="n"/>
+      <c r="U44" s="24" t="n"/>
+      <c r="V44" s="24" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="43" t="inlineStr">
-        <is>
-          <t>Re-paid at correct rate</t>
-        </is>
-      </c>
-      <c r="B45" s="43" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C45" s="41">
-        <f>'21 Aug 2026'!G4</f>
-        <v/>
-      </c>
-      <c r="D45" s="42">
-        <f>'21 Aug 2026'!M4</f>
-        <v/>
-      </c>
-      <c r="E45" s="42">
-        <f>'21 Aug 2026'!O4</f>
-        <v/>
-      </c>
-      <c r="F45" s="48" t="inlineStr">
-        <is>
-          <t>Re-paid the same 16 hrs at $37.50</t>
-        </is>
-      </c>
+      <c r="A45" s="60" t="inlineStr">
+        <is>
+          <t>NET EFFECT ON HOURS</t>
+        </is>
+      </c>
+      <c r="B45" s="61" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C45" s="62">
+        <f>C43+C44</f>
+        <v/>
+      </c>
+      <c r="D45" s="63" t="inlineStr"/>
+      <c r="E45" s="64" t="inlineStr">
+        <is>
+          <t>Nil - no hours added or removed. These lines correct the rate only</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="n"/>
       <c r="G45" s="24" t="n"/>
       <c r="H45" s="24" t="n"/>
       <c r="I45" s="24" t="n"/>
@@ -2960,32 +3094,29 @@
       <c r="R45" s="24" t="n"/>
       <c r="S45" s="24" t="n"/>
       <c r="T45" s="24" t="n"/>
+      <c r="U45" s="24" t="n"/>
+      <c r="V45" s="24" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="43" t="inlineStr">
-        <is>
-          <t>Net correction received</t>
-        </is>
-      </c>
-      <c r="B46" s="43" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C46" s="41">
-        <f>C44+C45</f>
-        <v/>
-      </c>
-      <c r="D46" s="42" t="inlineStr"/>
-      <c r="E46" s="42">
-        <f>E44+E45</f>
-        <v/>
-      </c>
-      <c r="F46" s="48" t="inlineStr">
-        <is>
-          <t>Net hours effect is nil - this is a rate top-up only</t>
-        </is>
-      </c>
+      <c r="A46" s="44" t="inlineStr">
+        <is>
+          <t>RATE NOW APPLYING</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="inlineStr"/>
+      <c r="C46" s="45">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="D46" s="65">
+        <f>'21 Aug 2026'!M4</f>
+        <v/>
+      </c>
+      <c r="E46" s="66">
+        <f>IF(ROUND(D46,2)=37.5,"CORRECTED - all hours now stand at the correct rate","STILL INCORRECT - investigate")</f>
+        <v/>
+      </c>
+      <c r="F46" s="24" t="n"/>
       <c r="G46" s="24" t="n"/>
       <c r="H46" s="24" t="n"/>
       <c r="I46" s="24" t="n"/>
@@ -3000,25 +3131,16 @@
       <c r="R46" s="24" t="n"/>
       <c r="S46" s="24" t="n"/>
       <c r="T46" s="24" t="n"/>
+      <c r="U46" s="24" t="n"/>
+      <c r="V46" s="24" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="44" t="inlineStr">
-        <is>
-          <t>AMOUNT STILL OWING</t>
-        </is>
-      </c>
-      <c r="B47" s="44" t="inlineStr"/>
-      <c r="C47" s="46" t="inlineStr"/>
-      <c r="D47" s="47" t="inlineStr"/>
-      <c r="E47" s="47">
-        <f>E43-E46</f>
-        <v/>
-      </c>
-      <c r="F47" s="54" t="inlineStr">
-        <is>
-          <t>Nil = the underpayment has been fully corrected</t>
-        </is>
-      </c>
+      <c r="A47" s="24" t="n"/>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="24" t="n"/>
       <c r="G47" s="24" t="n"/>
       <c r="H47" s="24" t="n"/>
       <c r="I47" s="24" t="n"/>
@@ -3033,76 +3155,85 @@
       <c r="R47" s="24" t="n"/>
       <c r="S47" s="24" t="n"/>
       <c r="T47" s="24" t="n"/>
+      <c r="U47" s="24" t="n"/>
+      <c r="V47" s="24" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="n"/>
-      <c r="B48" s="24" t="n"/>
-      <c r="C48" s="24" t="n"/>
-      <c r="D48" s="24" t="n"/>
-      <c r="E48" s="24" t="n"/>
-      <c r="F48" s="24" t="n"/>
-      <c r="G48" s="24" t="n"/>
-      <c r="H48" s="24" t="n"/>
-      <c r="I48" s="24" t="n"/>
-      <c r="J48" s="24" t="n"/>
-      <c r="K48" s="24" t="n"/>
-      <c r="L48" s="24" t="n"/>
-      <c r="M48" s="24" t="n"/>
-      <c r="N48" s="24" t="n"/>
-      <c r="O48" s="24" t="n"/>
+      <c r="A48" s="38" t="inlineStr">
+        <is>
+          <t>E.  COMPLETENESS CHECK  -  proves no paid hours sit outside this reconciliation</t>
+        </is>
+      </c>
+      <c r="B48" s="38" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="38" t="n"/>
+      <c r="E48" s="38" t="n"/>
+      <c r="F48" s="38" t="n"/>
+      <c r="G48" s="38" t="n"/>
+      <c r="H48" s="38" t="n"/>
+      <c r="I48" s="38" t="n"/>
+      <c r="J48" s="38" t="n"/>
+      <c r="K48" s="38" t="n"/>
+      <c r="L48" s="38" t="n"/>
+      <c r="M48" s="38" t="n"/>
+      <c r="N48" s="38" t="n"/>
+      <c r="O48" s="38" t="n"/>
       <c r="P48" s="24" t="n"/>
       <c r="Q48" s="24" t="n"/>
       <c r="R48" s="24" t="n"/>
       <c r="S48" s="24" t="n"/>
       <c r="T48" s="24" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="38" t="inlineStr">
-        <is>
-          <t>E.  COMPLETENESS CHECK  -  proves nothing paid sits outside this reconciliation, on hours and on dollars</t>
-        </is>
-      </c>
-      <c r="B49" s="38" t="n"/>
-      <c r="C49" s="38" t="n"/>
-      <c r="D49" s="38" t="n"/>
-      <c r="E49" s="38" t="n"/>
-      <c r="F49" s="38" t="n"/>
-      <c r="G49" s="38" t="n"/>
-      <c r="H49" s="38" t="n"/>
-      <c r="I49" s="38" t="n"/>
-      <c r="J49" s="38" t="n"/>
-      <c r="K49" s="38" t="n"/>
-      <c r="L49" s="38" t="n"/>
-      <c r="M49" s="38" t="n"/>
-      <c r="N49" s="38" t="n"/>
-      <c r="O49" s="38" t="n"/>
+      <c r="U48" s="24" t="n"/>
+      <c r="V48" s="24" t="n"/>
+    </row>
+    <row r="49" ht="32" customHeight="1" s="12">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="n"/>
+      <c r="E49" s="24" t="n"/>
+      <c r="F49" s="24" t="n"/>
+      <c r="G49" s="24" t="n"/>
+      <c r="H49" s="24" t="n"/>
+      <c r="I49" s="24" t="n"/>
+      <c r="J49" s="24" t="n"/>
+      <c r="K49" s="24" t="n"/>
+      <c r="L49" s="24" t="n"/>
+      <c r="M49" s="24" t="n"/>
+      <c r="N49" s="24" t="n"/>
+      <c r="O49" s="24" t="n"/>
       <c r="P49" s="24" t="n"/>
       <c r="Q49" s="24" t="n"/>
       <c r="R49" s="24" t="n"/>
       <c r="S49" s="24" t="n"/>
       <c r="T49" s="24" t="n"/>
-    </row>
-    <row r="50" ht="30" customHeight="1" s="12">
-      <c r="A50" s="27" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B50" s="27" t="inlineStr">
-        <is>
-          <t>Hours</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="inlineStr">
-        <is>
-          <t>Gross $</t>
-        </is>
-      </c>
-      <c r="D50" s="27" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
+      <c r="U49" s="24" t="n"/>
+      <c r="V49" s="24" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>Total hours on all four pay-run tabs (including the two rate-correction lines)</t>
+        </is>
+      </c>
+      <c r="B50" s="42">
+        <f>SUM('07 Aug 2026'!$G$3:$G$6)+SUM('21 Aug 2026'!$G$3:$G$7)+SUM('20 Sept 2026 '!$G$3:$G$14)+SUM('22 Sep 2026'!$G$3:$G$11)</f>
+        <v/>
+      </c>
+      <c r="C50" s="48" t="inlineStr"/>
+      <c r="D50" s="24" t="n"/>
       <c r="E50" s="24" t="n"/>
       <c r="F50" s="24" t="n"/>
       <c r="G50" s="24" t="n"/>
@@ -3119,22 +3250,21 @@
       <c r="R50" s="24" t="n"/>
       <c r="S50" s="24" t="n"/>
       <c r="T50" s="24" t="n"/>
+      <c r="U50" s="24" t="n"/>
+      <c r="V50" s="24" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="43" t="inlineStr">
-        <is>
-          <t>Total on all four pay-run tabs (including the +/-16 hr rate reversal)</t>
-        </is>
-      </c>
-      <c r="B51" s="41">
-        <f>SUM('07 Aug 2026'!$G$3:$G$6)+SUM('21 Aug 2026'!$G$3:$G$7)+SUM('20 Sept 2026 '!$G$3:$G$14)+SUM('22 Sep 2026'!$G$3:$G$11)</f>
-        <v/>
-      </c>
-      <c r="C51" s="42">
-        <f>SUM('07 Aug 2026'!$O$3:$O$6)+SUM('21 Aug 2026'!$O$3:$O$7)+SUM('20 Sept 2026 '!$O$3:$O$14)+SUM('22 Sep 2026'!$O$3:$O$11)</f>
-        <v/>
-      </c>
-      <c r="D51" s="48" t="inlineStr"/>
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>Total paid hours matched to a timesheet line in Section C</t>
+        </is>
+      </c>
+      <c r="B51" s="42">
+        <f>J37</f>
+        <v/>
+      </c>
+      <c r="C51" s="48" t="inlineStr"/>
+      <c r="D51" s="24" t="n"/>
       <c r="E51" s="24" t="n"/>
       <c r="F51" s="24" t="n"/>
       <c r="G51" s="24" t="n"/>
@@ -3151,22 +3281,24 @@
       <c r="R51" s="24" t="n"/>
       <c r="S51" s="24" t="n"/>
       <c r="T51" s="24" t="n"/>
+      <c r="U51" s="24" t="n"/>
+      <c r="V51" s="24" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="43" t="inlineStr">
-        <is>
-          <t>Total matched to a timesheet line in Section C</t>
-        </is>
-      </c>
-      <c r="B52" s="41">
-        <f>I37</f>
-        <v/>
-      </c>
-      <c r="C52" s="42">
-        <f>M37</f>
-        <v/>
-      </c>
-      <c r="D52" s="48" t="inlineStr"/>
+      <c r="A52" s="39" t="inlineStr">
+        <is>
+          <t>Unmatched paid hours</t>
+        </is>
+      </c>
+      <c r="B52" s="42">
+        <f>B50-B51</f>
+        <v/>
+      </c>
+      <c r="C52" s="48">
+        <f>IF(ROUND(B52,2)=0,"OK - every paid hour ties to a timesheet line","INVESTIGATE - unmatched paid hours")</f>
+        <v/>
+      </c>
+      <c r="D52" s="24" t="n"/>
       <c r="E52" s="24" t="n"/>
       <c r="F52" s="24" t="n"/>
       <c r="G52" s="24" t="n"/>
@@ -3183,25 +3315,21 @@
       <c r="R52" s="24" t="n"/>
       <c r="S52" s="24" t="n"/>
       <c r="T52" s="24" t="n"/>
+      <c r="U52" s="24" t="n"/>
+      <c r="V52" s="24" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="43" t="inlineStr">
-        <is>
-          <t>Difference - rate-correction adjustment, no work date attached</t>
-        </is>
-      </c>
-      <c r="B53" s="41">
-        <f>B51-B52</f>
-        <v/>
-      </c>
-      <c r="C53" s="42">
-        <f>C51-C52</f>
-        <v/>
-      </c>
-      <c r="D53" s="48">
-        <f>IF(ROUND(B53,2)=0,"OK - nil unmatched hours; $"&amp;TEXT(C53,"0.00")&amp;" is the rate top-up per Section D","INVESTIGATE - unmatched paid hours")</f>
-        <v/>
-      </c>
+      <c r="A53" s="39" t="inlineStr">
+        <is>
+          <t>Total timesheet hours per the screenshots</t>
+        </is>
+      </c>
+      <c r="B53" s="42">
+        <f>I37</f>
+        <v/>
+      </c>
+      <c r="C53" s="48" t="inlineStr"/>
+      <c r="D53" s="24" t="n"/>
       <c r="E53" s="24" t="n"/>
       <c r="F53" s="24" t="n"/>
       <c r="G53" s="24" t="n"/>
@@ -3218,19 +3346,24 @@
       <c r="R53" s="24" t="n"/>
       <c r="S53" s="24" t="n"/>
       <c r="T53" s="24" t="n"/>
+      <c r="U53" s="24" t="n"/>
+      <c r="V53" s="24" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="43" t="inlineStr">
-        <is>
-          <t>Total timesheet hours per the screenshots</t>
-        </is>
-      </c>
-      <c r="B54" s="41">
-        <f>H37</f>
-        <v/>
-      </c>
-      <c r="C54" s="42" t="inlineStr"/>
-      <c r="D54" s="48" t="inlineStr"/>
+      <c r="A54" s="44" t="inlineStr">
+        <is>
+          <t>HOURS VARIANCE (timesheet less paid)</t>
+        </is>
+      </c>
+      <c r="B54" s="45">
+        <f>B53-B51</f>
+        <v/>
+      </c>
+      <c r="C54" s="66">
+        <f>IF(ROUND(B54,2)=0,"FULLY RECONCILED - nil hours variance","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="D54" s="24" t="n"/>
       <c r="E54" s="24" t="n"/>
       <c r="F54" s="24" t="n"/>
       <c r="G54" s="24" t="n"/>
@@ -3247,22 +3380,14 @@
       <c r="R54" s="24" t="n"/>
       <c r="S54" s="24" t="n"/>
       <c r="T54" s="24" t="n"/>
+      <c r="U54" s="24" t="n"/>
+      <c r="V54" s="24" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="44" t="inlineStr">
-        <is>
-          <t>HOURS VARIANCE (timesheet less paid)</t>
-        </is>
-      </c>
-      <c r="B55" s="46">
-        <f>B54-B52</f>
-        <v/>
-      </c>
-      <c r="C55" s="47" t="inlineStr"/>
-      <c r="D55" s="54">
-        <f>IF(ROUND(B55,2)=0,"FULLY RECONCILED - nil hours variance","VARIANCE - investigate")</f>
-        <v/>
-      </c>
+      <c r="A55" s="24" t="n"/>
+      <c r="B55" s="24" t="n"/>
+      <c r="C55" s="24" t="n"/>
+      <c r="D55" s="24" t="n"/>
       <c r="E55" s="24" t="n"/>
       <c r="F55" s="24" t="n"/>
       <c r="G55" s="24" t="n"/>
@@ -3279,55 +3404,48 @@
       <c r="R55" s="24" t="n"/>
       <c r="S55" s="24" t="n"/>
       <c r="T55" s="24" t="n"/>
+      <c r="U55" s="24" t="n"/>
+      <c r="V55" s="24" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="43" t="inlineStr">
-        <is>
-          <t>Gross that should have been paid (timesheet hours x $37.50)</t>
-        </is>
-      </c>
-      <c r="B56" s="41" t="inlineStr"/>
-      <c r="C56" s="42">
-        <f>B54*37.5</f>
-        <v/>
-      </c>
-      <c r="D56" s="48" t="inlineStr"/>
-      <c r="E56" s="24" t="n"/>
-      <c r="F56" s="24" t="n"/>
-      <c r="G56" s="24" t="n"/>
-      <c r="H56" s="24" t="n"/>
-      <c r="I56" s="24" t="n"/>
-      <c r="J56" s="24" t="n"/>
-      <c r="K56" s="24" t="n"/>
-      <c r="L56" s="24" t="n"/>
-      <c r="M56" s="24" t="n"/>
-      <c r="N56" s="24" t="n"/>
-      <c r="O56" s="24" t="n"/>
+      <c r="A56" s="38" t="inlineStr">
+        <is>
+          <t>F.  FINDINGS</t>
+        </is>
+      </c>
+      <c r="B56" s="38" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="38" t="n"/>
+      <c r="E56" s="38" t="n"/>
+      <c r="F56" s="38" t="n"/>
+      <c r="G56" s="38" t="n"/>
+      <c r="H56" s="38" t="n"/>
+      <c r="I56" s="38" t="n"/>
+      <c r="J56" s="38" t="n"/>
+      <c r="K56" s="38" t="n"/>
+      <c r="L56" s="38" t="n"/>
+      <c r="M56" s="38" t="n"/>
+      <c r="N56" s="38" t="n"/>
+      <c r="O56" s="38" t="n"/>
       <c r="P56" s="24" t="n"/>
       <c r="Q56" s="24" t="n"/>
       <c r="R56" s="24" t="n"/>
       <c r="S56" s="24" t="n"/>
       <c r="T56" s="24" t="n"/>
+      <c r="U56" s="24" t="n"/>
+      <c r="V56" s="24" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="43" t="inlineStr">
-        <is>
-          <t>Gross actually paid across all pay runs (after the rate correction)</t>
-        </is>
-      </c>
-      <c r="B57" s="41" t="inlineStr"/>
-      <c r="C57" s="42">
-        <f>C51</f>
-        <v/>
-      </c>
-      <c r="D57" s="48" t="inlineStr"/>
-      <c r="E57" s="24" t="n"/>
-      <c r="F57" s="24" t="n"/>
-      <c r="G57" s="24" t="n"/>
-      <c r="H57" s="24" t="n"/>
-      <c r="I57" s="24" t="n"/>
-      <c r="J57" s="24" t="n"/>
-      <c r="K57" s="24" t="n"/>
+      <c r="A57" s="67" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B57" s="68" t="inlineStr">
+        <is>
+          <t>The 16 hours queried (24 Aug and 28 Aug, DTTL) are NOT missing - they were paid in full.</t>
+        </is>
+      </c>
       <c r="L57" s="24" t="n"/>
       <c r="M57" s="24" t="n"/>
       <c r="N57" s="24" t="n"/>
@@ -3337,38 +3455,23 @@
       <c r="R57" s="24" t="n"/>
       <c r="S57" s="24" t="n"/>
       <c r="T57" s="24" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="44" t="inlineStr">
-        <is>
-          <t>DOLLAR VARIANCE (should have been paid less actually paid)</t>
-        </is>
-      </c>
-      <c r="B58" s="46" t="inlineStr"/>
-      <c r="C58" s="47">
-        <f>C56-C57</f>
-        <v/>
-      </c>
-      <c r="D58" s="54">
-        <f>IF(ROUND(C58,2)=0,"FULLY RECONCILED - nil dollar variance","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="E58" s="24" t="n"/>
-      <c r="F58" s="24" t="n"/>
-      <c r="G58" s="24" t="n"/>
-      <c r="H58" s="24" t="n"/>
-      <c r="I58" s="24" t="n"/>
-      <c r="J58" s="24" t="n"/>
-      <c r="K58" s="24" t="n"/>
-      <c r="L58" s="24" t="n"/>
-      <c r="M58" s="24" t="n"/>
-      <c r="N58" s="24" t="n"/>
-      <c r="O58" s="24" t="n"/>
+      <c r="U57" s="24" t="n"/>
+      <c r="V57" s="24" t="n"/>
+    </row>
+    <row r="58" ht="36" customHeight="1" s="12">
+      <c r="A58" s="24" t="n"/>
+      <c r="B58" s="69" t="inlineStr">
+        <is>
+          <t>Both days fall in the pay period 22/08/2026 - 04/09/2026, which was paid on 08/09/2026. Each was paid as 3.5 hrs + 4.5 hrs either side of the unpaid break, which is why neither shows as a single 8 hour entry. 16 hours in total, nil shortfall. See Section A and the two highlighted rows in Section C.</t>
+        </is>
+      </c>
       <c r="P58" s="24" t="n"/>
       <c r="Q58" s="24" t="n"/>
       <c r="R58" s="24" t="n"/>
       <c r="S58" s="24" t="n"/>
       <c r="T58" s="24" t="n"/>
+      <c r="U58" s="24" t="n"/>
+      <c r="V58" s="24" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="24" t="n"/>
@@ -3391,82 +3494,82 @@
       <c r="R59" s="24" t="n"/>
       <c r="S59" s="24" t="n"/>
       <c r="T59" s="24" t="n"/>
+      <c r="U59" s="24" t="n"/>
+      <c r="V59" s="24" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="38" t="inlineStr">
-        <is>
-          <t>F.  FINDINGS</t>
-        </is>
-      </c>
-      <c r="B60" s="38" t="n"/>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="38" t="n"/>
-      <c r="E60" s="38" t="n"/>
-      <c r="F60" s="38" t="n"/>
-      <c r="G60" s="38" t="n"/>
-      <c r="H60" s="38" t="n"/>
-      <c r="I60" s="38" t="n"/>
-      <c r="J60" s="38" t="n"/>
-      <c r="K60" s="38" t="n"/>
-      <c r="L60" s="38" t="n"/>
-      <c r="M60" s="38" t="n"/>
-      <c r="N60" s="38" t="n"/>
-      <c r="O60" s="38" t="n"/>
+      <c r="A60" s="67" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B60" s="68" t="inlineStr">
+        <is>
+          <t>Hours reconcile in full across all four pay periods.</t>
+        </is>
+      </c>
+      <c r="L60" s="24" t="n"/>
+      <c r="M60" s="24" t="n"/>
+      <c r="N60" s="24" t="n"/>
+      <c r="O60" s="24" t="n"/>
       <c r="P60" s="24" t="n"/>
       <c r="Q60" s="24" t="n"/>
       <c r="R60" s="24" t="n"/>
       <c r="S60" s="24" t="n"/>
       <c r="T60" s="24" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="55" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B61" s="56" t="inlineStr">
-        <is>
-          <t>The 16 hours queried (24 Aug and 28 Aug, DTTL) are NOT missing - they were paid in full.</t>
-        </is>
-      </c>
-      <c r="I61" s="24" t="n"/>
-      <c r="J61" s="24" t="n"/>
-      <c r="K61" s="24" t="n"/>
-      <c r="L61" s="24" t="n"/>
-      <c r="M61" s="24" t="n"/>
-      <c r="N61" s="24" t="n"/>
-      <c r="O61" s="24" t="n"/>
+      <c r="U60" s="24" t="n"/>
+      <c r="V60" s="24" t="n"/>
+    </row>
+    <row r="61" ht="36" customHeight="1" s="12">
+      <c r="A61" s="24" t="n"/>
+      <c r="B61" s="69" t="inlineStr">
+        <is>
+          <t>All 111.50 timesheet hours have been paid. Nil variance at day level, at pay period level and in total, and every paid line ties back to a timesheet entry.</t>
+        </is>
+      </c>
       <c r="P61" s="24" t="n"/>
       <c r="Q61" s="24" t="n"/>
       <c r="R61" s="24" t="n"/>
       <c r="S61" s="24" t="n"/>
       <c r="T61" s="24" t="n"/>
-    </row>
-    <row r="62" ht="34" customHeight="1" s="12">
+      <c r="U61" s="24" t="n"/>
+      <c r="V61" s="24" t="n"/>
+    </row>
+    <row r="62">
       <c r="A62" s="24" t="n"/>
-      <c r="B62" s="57" t="inlineStr">
-        <is>
-          <t>Both days were paid in the 20 Sep 2026 pay run at $37.50/hr: 24/08 as 3.5 + 4.5 hrs ($131.25 + $168.75 = $300.00) and 28/08 as 3.5 + 4.5 hrs ($131.25 + $168.75 = $300.00). $600.00 gross in total. Nothing is owing. See Section A for the exact pay-run lines, and the two highlighted rows in Section C.</t>
-        </is>
-      </c>
+      <c r="B62" s="24" t="n"/>
+      <c r="C62" s="24" t="n"/>
+      <c r="D62" s="24" t="n"/>
+      <c r="E62" s="24" t="n"/>
+      <c r="F62" s="24" t="n"/>
+      <c r="G62" s="24" t="n"/>
+      <c r="H62" s="24" t="n"/>
+      <c r="I62" s="24" t="n"/>
+      <c r="J62" s="24" t="n"/>
+      <c r="K62" s="24" t="n"/>
+      <c r="L62" s="24" t="n"/>
+      <c r="M62" s="24" t="n"/>
+      <c r="N62" s="24" t="n"/>
+      <c r="O62" s="24" t="n"/>
       <c r="P62" s="24" t="n"/>
       <c r="Q62" s="24" t="n"/>
       <c r="R62" s="24" t="n"/>
       <c r="S62" s="24" t="n"/>
       <c r="T62" s="24" t="n"/>
+      <c r="U62" s="24" t="n"/>
+      <c r="V62" s="24" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="n"/>
-      <c r="B63" s="24" t="n"/>
-      <c r="C63" s="24" t="n"/>
-      <c r="D63" s="24" t="n"/>
-      <c r="E63" s="24" t="n"/>
-      <c r="F63" s="24" t="n"/>
-      <c r="G63" s="24" t="n"/>
-      <c r="H63" s="24" t="n"/>
-      <c r="I63" s="24" t="n"/>
-      <c r="J63" s="24" t="n"/>
-      <c r="K63" s="24" t="n"/>
+      <c r="A63" s="67" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B63" s="68" t="inlineStr">
+        <is>
+          <t>CHECK THIS - 23.50 hours may have been paid two weeks late.</t>
+        </is>
+      </c>
       <c r="L63" s="24" t="n"/>
       <c r="M63" s="24" t="n"/>
       <c r="N63" s="24" t="n"/>
@@ -3476,56 +3579,59 @@
       <c r="R63" s="24" t="n"/>
       <c r="S63" s="24" t="n"/>
       <c r="T63" s="24" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="55" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B64" s="56" t="inlineStr">
-        <is>
-          <t>Hours and dollars both reconcile in full.</t>
-        </is>
-      </c>
-      <c r="I64" s="24" t="n"/>
-      <c r="J64" s="24" t="n"/>
-      <c r="K64" s="24" t="n"/>
-      <c r="L64" s="24" t="n"/>
-      <c r="M64" s="24" t="n"/>
-      <c r="N64" s="24" t="n"/>
-      <c r="O64" s="24" t="n"/>
+      <c r="U63" s="24" t="n"/>
+      <c r="V63" s="24" t="n"/>
+    </row>
+    <row r="64" ht="36" customHeight="1" s="12">
+      <c r="A64" s="24" t="n"/>
+      <c r="B64" s="69" t="inlineStr">
+        <is>
+          <t>The hours worked on 25, 26 and 27 August fall in the pay period 22/08/2026 - 04/09/2026, which was paid on 08/09/2026. In this workbook they sit on the 22 Sep 2026 tab, apart from the rest of that period. If that tab represents the run paid on 22/09/2026, those 23.50 hours were paid a fortnight after the rest of the period. The hours themselves are correct and fully paid - only the date they reached him is in question. Confirm against the payslips. These rows are shaded in Section C.</t>
+        </is>
+      </c>
       <c r="P64" s="24" t="n"/>
       <c r="Q64" s="24" t="n"/>
       <c r="R64" s="24" t="n"/>
       <c r="S64" s="24" t="n"/>
       <c r="T64" s="24" t="n"/>
-    </row>
-    <row r="65" ht="34" customHeight="1" s="12">
+      <c r="U64" s="24" t="n"/>
+      <c r="V64" s="24" t="n"/>
+    </row>
+    <row r="65">
       <c r="A65" s="24" t="n"/>
-      <c r="B65" s="57" t="inlineStr">
-        <is>
-          <t>All 111.50 timesheet hours across the four fortnights have been paid, and total gross of $4,181.25 equals 111.50 hrs x $37.50 exactly. Nil variance at day level, fortnight level and in total.</t>
-        </is>
-      </c>
+      <c r="B65" s="24" t="n"/>
+      <c r="C65" s="24" t="n"/>
+      <c r="D65" s="24" t="n"/>
+      <c r="E65" s="24" t="n"/>
+      <c r="F65" s="24" t="n"/>
+      <c r="G65" s="24" t="n"/>
+      <c r="H65" s="24" t="n"/>
+      <c r="I65" s="24" t="n"/>
+      <c r="J65" s="24" t="n"/>
+      <c r="K65" s="24" t="n"/>
+      <c r="L65" s="24" t="n"/>
+      <c r="M65" s="24" t="n"/>
+      <c r="N65" s="24" t="n"/>
+      <c r="O65" s="24" t="n"/>
       <c r="P65" s="24" t="n"/>
       <c r="Q65" s="24" t="n"/>
       <c r="R65" s="24" t="n"/>
       <c r="S65" s="24" t="n"/>
       <c r="T65" s="24" t="n"/>
+      <c r="U65" s="24" t="n"/>
+      <c r="V65" s="24" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="n"/>
-      <c r="B66" s="24" t="n"/>
-      <c r="C66" s="24" t="n"/>
-      <c r="D66" s="24" t="n"/>
-      <c r="E66" s="24" t="n"/>
-      <c r="F66" s="24" t="n"/>
-      <c r="G66" s="24" t="n"/>
-      <c r="H66" s="24" t="n"/>
-      <c r="I66" s="24" t="n"/>
-      <c r="J66" s="24" t="n"/>
-      <c r="K66" s="24" t="n"/>
+      <c r="A66" s="67" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B66" s="68" t="inlineStr">
+        <is>
+          <t>The rate on the period 25/07/2026 - 07/08/2026 was wrong, and has been corrected.</t>
+        </is>
+      </c>
       <c r="L66" s="24" t="n"/>
       <c r="M66" s="24" t="n"/>
       <c r="N66" s="24" t="n"/>
@@ -3535,56 +3641,59 @@
       <c r="R66" s="24" t="n"/>
       <c r="S66" s="24" t="n"/>
       <c r="T66" s="24" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="55" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B67" s="56" t="inlineStr">
-        <is>
-          <t>Rate error on fortnight ending 07/08/2026 - already corrected.</t>
-        </is>
-      </c>
-      <c r="I67" s="24" t="n"/>
-      <c r="J67" s="24" t="n"/>
-      <c r="K67" s="24" t="n"/>
-      <c r="L67" s="24" t="n"/>
-      <c r="M67" s="24" t="n"/>
-      <c r="N67" s="24" t="n"/>
-      <c r="O67" s="24" t="n"/>
+      <c r="U66" s="24" t="n"/>
+      <c r="V66" s="24" t="n"/>
+    </row>
+    <row r="67" ht="36" customHeight="1" s="12">
+      <c r="A67" s="24" t="n"/>
+      <c r="B67" s="69" t="inlineStr">
+        <is>
+          <t>16 hrs were first paid at $35.15/hr instead of $37.50/hr on 11/08/2026. Those hours were reversed and re-paid at $37.50/hr on 25/08/2026, so all hours now stand at the correct rate. Every other line across the four periods was paid at $37.50/hr.</t>
+        </is>
+      </c>
       <c r="P67" s="24" t="n"/>
       <c r="Q67" s="24" t="n"/>
       <c r="R67" s="24" t="n"/>
       <c r="S67" s="24" t="n"/>
       <c r="T67" s="24" t="n"/>
-    </row>
-    <row r="68" ht="34" customHeight="1" s="12">
+      <c r="U67" s="24" t="n"/>
+      <c r="V67" s="24" t="n"/>
+    </row>
+    <row r="68">
       <c r="A68" s="24" t="n"/>
-      <c r="B68" s="57" t="inlineStr">
-        <is>
-          <t>16 hrs were paid at $35.15/hr instead of $37.50/hr, a shortfall of $37.60 ($18.80 on 29 Jul and $9.40 on each of the two 30 Jul shifts). Payroll reversed and re-paid those 16 hrs in the 21 Aug 2026 run. Nothing further is owing. See Section D.</t>
-        </is>
-      </c>
+      <c r="B68" s="24" t="n"/>
+      <c r="C68" s="24" t="n"/>
+      <c r="D68" s="24" t="n"/>
+      <c r="E68" s="24" t="n"/>
+      <c r="F68" s="24" t="n"/>
+      <c r="G68" s="24" t="n"/>
+      <c r="H68" s="24" t="n"/>
+      <c r="I68" s="24" t="n"/>
+      <c r="J68" s="24" t="n"/>
+      <c r="K68" s="24" t="n"/>
+      <c r="L68" s="24" t="n"/>
+      <c r="M68" s="24" t="n"/>
+      <c r="N68" s="24" t="n"/>
+      <c r="O68" s="24" t="n"/>
       <c r="P68" s="24" t="n"/>
       <c r="Q68" s="24" t="n"/>
       <c r="R68" s="24" t="n"/>
       <c r="S68" s="24" t="n"/>
       <c r="T68" s="24" t="n"/>
+      <c r="U68" s="24" t="n"/>
+      <c r="V68" s="24" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="24" t="n"/>
-      <c r="B69" s="24" t="n"/>
-      <c r="C69" s="24" t="n"/>
-      <c r="D69" s="24" t="n"/>
-      <c r="E69" s="24" t="n"/>
-      <c r="F69" s="24" t="n"/>
-      <c r="G69" s="24" t="n"/>
-      <c r="H69" s="24" t="n"/>
-      <c r="I69" s="24" t="n"/>
-      <c r="J69" s="24" t="n"/>
-      <c r="K69" s="24" t="n"/>
+      <c r="A69" s="67" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B69" s="68" t="inlineStr">
+        <is>
+          <t>The rate-correction lines were booked to the wrong location.</t>
+        </is>
+      </c>
       <c r="L69" s="24" t="n"/>
       <c r="M69" s="24" t="n"/>
       <c r="N69" s="24" t="n"/>
@@ -3594,56 +3703,59 @@
       <c r="R69" s="24" t="n"/>
       <c r="S69" s="24" t="n"/>
       <c r="T69" s="24" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="55" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B70" s="56" t="inlineStr">
-        <is>
-          <t>The rate correction was booked to the wrong location.</t>
-        </is>
-      </c>
-      <c r="I70" s="24" t="n"/>
-      <c r="J70" s="24" t="n"/>
-      <c r="K70" s="24" t="n"/>
-      <c r="L70" s="24" t="n"/>
-      <c r="M70" s="24" t="n"/>
-      <c r="N70" s="24" t="n"/>
-      <c r="O70" s="24" t="n"/>
+      <c r="U69" s="24" t="n"/>
+      <c r="V69" s="24" t="n"/>
+    </row>
+    <row r="70" ht="36" customHeight="1" s="12">
+      <c r="A70" s="24" t="n"/>
+      <c r="B70" s="69" t="inlineStr">
+        <is>
+          <t>The original 16 hrs were split CBA 8 hrs, PwC - MEL Technician 4 hrs and Aware Super 4 hrs. The reversal and re-payment put all 16 hrs against CBA FT Tech MEL. Hours and rate paid are correct, but job costing for PwC and Aware Super is understated by 4 hrs each and CBA is overstated by 8 hrs. Worth raising with payroll if client recharges run off this data.</t>
+        </is>
+      </c>
       <c r="P70" s="24" t="n"/>
       <c r="Q70" s="24" t="n"/>
       <c r="R70" s="24" t="n"/>
       <c r="S70" s="24" t="n"/>
       <c r="T70" s="24" t="n"/>
-    </row>
-    <row r="71" ht="34" customHeight="1" s="12">
+      <c r="U70" s="24" t="n"/>
+      <c r="V70" s="24" t="n"/>
+    </row>
+    <row r="71">
       <c r="A71" s="24" t="n"/>
-      <c r="B71" s="57" t="inlineStr">
-        <is>
-          <t>The original 16 hrs were split CBA 8 hrs, PwC - MEL Technician 4 hrs and Aware Super 4 hrs. The reversal and re-payment put all 16 hrs against CBA FT Tech MEL. Take-home pay is correct, but job costing for PwC and Aware Super is understated by 4 hrs each and CBA is overstated by 8 hrs. Worth raising with payroll if client recharges run off this data.</t>
-        </is>
-      </c>
+      <c r="B71" s="24" t="n"/>
+      <c r="C71" s="24" t="n"/>
+      <c r="D71" s="24" t="n"/>
+      <c r="E71" s="24" t="n"/>
+      <c r="F71" s="24" t="n"/>
+      <c r="G71" s="24" t="n"/>
+      <c r="H71" s="24" t="n"/>
+      <c r="I71" s="24" t="n"/>
+      <c r="J71" s="24" t="n"/>
+      <c r="K71" s="24" t="n"/>
+      <c r="L71" s="24" t="n"/>
+      <c r="M71" s="24" t="n"/>
+      <c r="N71" s="24" t="n"/>
+      <c r="O71" s="24" t="n"/>
       <c r="P71" s="24" t="n"/>
       <c r="Q71" s="24" t="n"/>
       <c r="R71" s="24" t="n"/>
       <c r="S71" s="24" t="n"/>
       <c r="T71" s="24" t="n"/>
+      <c r="U71" s="24" t="n"/>
+      <c r="V71" s="24" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="n"/>
-      <c r="B72" s="24" t="n"/>
-      <c r="C72" s="24" t="n"/>
-      <c r="D72" s="24" t="n"/>
-      <c r="E72" s="24" t="n"/>
-      <c r="F72" s="24" t="n"/>
-      <c r="G72" s="24" t="n"/>
-      <c r="H72" s="24" t="n"/>
-      <c r="I72" s="24" t="n"/>
-      <c r="J72" s="24" t="n"/>
-      <c r="K72" s="24" t="n"/>
+      <c r="A72" s="67" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B72" s="68" t="inlineStr">
+        <is>
+          <t>The pay period 08/08/2026 - 21/08/2026 carries three separate payment dates.</t>
+        </is>
+      </c>
       <c r="L72" s="24" t="n"/>
       <c r="M72" s="24" t="n"/>
       <c r="N72" s="24" t="n"/>
@@ -3653,43 +3765,47 @@
       <c r="R72" s="24" t="n"/>
       <c r="S72" s="24" t="n"/>
       <c r="T72" s="24" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="55" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B73" s="56" t="inlineStr">
-        <is>
-          <t>Fortnight ending 04/09/2026 was paid across two pay runs - this is the likely cause of the query.</t>
-        </is>
-      </c>
-      <c r="I73" s="24" t="n"/>
-      <c r="J73" s="24" t="n"/>
-      <c r="K73" s="24" t="n"/>
-      <c r="L73" s="24" t="n"/>
-      <c r="M73" s="24" t="n"/>
-      <c r="N73" s="24" t="n"/>
-      <c r="O73" s="24" t="n"/>
+      <c r="U72" s="24" t="n"/>
+      <c r="V72" s="24" t="n"/>
+    </row>
+    <row r="73" ht="36" customHeight="1" s="12">
+      <c r="A73" s="24" t="n"/>
+      <c r="B73" s="69" t="inlineStr">
+        <is>
+          <t>The pay history shows that period paid on 25/08/2026, 26/08/2026 and 28/08/2026. This reconciliation uses 25/08/2026, the first of them. The extra runs are consistent with the rate correction being processed separately. Worth confirming what the 26/08 and 28/08 runs covered.</t>
+        </is>
+      </c>
       <c r="P73" s="24" t="n"/>
       <c r="Q73" s="24" t="n"/>
       <c r="R73" s="24" t="n"/>
       <c r="S73" s="24" t="n"/>
       <c r="T73" s="24" t="n"/>
-    </row>
-    <row r="74" ht="34" customHeight="1" s="12">
+      <c r="U73" s="24" t="n"/>
+      <c r="V73" s="24" t="n"/>
+    </row>
+    <row r="74">
       <c r="A74" s="24" t="n"/>
-      <c r="B74" s="57" t="inlineStr">
-        <is>
-          <t>48 hrs of DTTL work (including the two days queried) went through the 20 Sep 2026 run, and 23.50 hrs of PwC National Pool work went through the 22 Sep 2026 run. Total 71.50 hrs, which agrees to the timesheet. Anyone checking a single payslip for that fortnight would only see part of it.</t>
-        </is>
-      </c>
+      <c r="B74" s="24" t="n"/>
+      <c r="C74" s="24" t="n"/>
+      <c r="D74" s="24" t="n"/>
+      <c r="E74" s="24" t="n"/>
+      <c r="F74" s="24" t="n"/>
+      <c r="G74" s="24" t="n"/>
+      <c r="H74" s="24" t="n"/>
+      <c r="I74" s="24" t="n"/>
+      <c r="J74" s="24" t="n"/>
+      <c r="K74" s="24" t="n"/>
+      <c r="L74" s="24" t="n"/>
+      <c r="M74" s="24" t="n"/>
+      <c r="N74" s="24" t="n"/>
+      <c r="O74" s="24" t="n"/>
       <c r="P74" s="24" t="n"/>
       <c r="Q74" s="24" t="n"/>
       <c r="R74" s="24" t="n"/>
       <c r="S74" s="24" t="n"/>
       <c r="T74" s="24" t="n"/>
+      <c r="U74" s="24" t="n"/>
+      <c r="V74" s="24" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="24" t="n"/>
@@ -3712,43 +3828,46 @@
       <c r="R75" s="24" t="n"/>
       <c r="S75" s="24" t="n"/>
       <c r="T75" s="24" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="55" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B76" s="56" t="inlineStr">
-        <is>
-          <t>Payment lag worth checking.</t>
-        </is>
-      </c>
-      <c r="I76" s="24" t="n"/>
-      <c r="J76" s="24" t="n"/>
-      <c r="K76" s="24" t="n"/>
-      <c r="L76" s="24" t="n"/>
-      <c r="M76" s="24" t="n"/>
-      <c r="N76" s="24" t="n"/>
-      <c r="O76" s="24" t="n"/>
+      <c r="U75" s="24" t="n"/>
+      <c r="V75" s="24" t="n"/>
+    </row>
+    <row r="76" ht="40" customHeight="1" s="12">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>Timesheet hours transcribed from the timesheet screenshots for the periods ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026, all showing status PROCESSED. Paid hours from the Earnings Details tabs in this workbook. Pay periods and dates paid taken from the Employment Hero pay history. NOTE: the tab names in this workbook are NOT payment dates - the Pay Period and Date Paid columns are the authoritative reference.</t>
+        </is>
+      </c>
       <c r="P76" s="24" t="n"/>
       <c r="Q76" s="24" t="n"/>
       <c r="R76" s="24" t="n"/>
       <c r="S76" s="24" t="n"/>
       <c r="T76" s="24" t="n"/>
-    </row>
-    <row r="77" ht="34" customHeight="1" s="12">
+      <c r="U76" s="24" t="n"/>
+      <c r="V76" s="24" t="n"/>
+    </row>
+    <row r="77">
       <c r="A77" s="24" t="n"/>
-      <c r="B77" s="57" t="inlineStr">
-        <is>
-          <t>Work from 25-27 Aug was not paid until the 22 Sep 2026 run, roughly four weeks after it was worked. Check this against the payroll calendar if it was not expected.</t>
-        </is>
-      </c>
+      <c r="B77" s="24" t="n"/>
+      <c r="C77" s="24" t="n"/>
+      <c r="D77" s="24" t="n"/>
+      <c r="E77" s="24" t="n"/>
+      <c r="F77" s="24" t="n"/>
+      <c r="G77" s="24" t="n"/>
+      <c r="H77" s="24" t="n"/>
+      <c r="I77" s="24" t="n"/>
+      <c r="J77" s="24" t="n"/>
+      <c r="K77" s="24" t="n"/>
+      <c r="L77" s="24" t="n"/>
+      <c r="M77" s="24" t="n"/>
+      <c r="N77" s="24" t="n"/>
+      <c r="O77" s="24" t="n"/>
       <c r="P77" s="24" t="n"/>
       <c r="Q77" s="24" t="n"/>
       <c r="R77" s="24" t="n"/>
       <c r="S77" s="24" t="n"/>
       <c r="T77" s="24" t="n"/>
+      <c r="U77" s="24" t="n"/>
+      <c r="V77" s="24" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="24" t="n"/>
@@ -3771,18 +3890,18 @@
       <c r="R78" s="24" t="n"/>
       <c r="S78" s="24" t="n"/>
       <c r="T78" s="24" t="n"/>
+      <c r="U78" s="24" t="n"/>
+      <c r="V78" s="24" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="55" t="inlineStr">
-        <is>
-          <t>7.</t>
-        </is>
-      </c>
-      <c r="B79" s="56" t="inlineStr">
-        <is>
-          <t>Superannuation.</t>
-        </is>
-      </c>
+      <c r="A79" s="24" t="n"/>
+      <c r="B79" s="24" t="n"/>
+      <c r="C79" s="24" t="n"/>
+      <c r="D79" s="24" t="n"/>
+      <c r="E79" s="24" t="n"/>
+      <c r="F79" s="24" t="n"/>
+      <c r="G79" s="24" t="n"/>
+      <c r="H79" s="24" t="n"/>
       <c r="I79" s="24" t="n"/>
       <c r="J79" s="24" t="n"/>
       <c r="K79" s="24" t="n"/>
@@ -3795,19 +3914,32 @@
       <c r="R79" s="24" t="n"/>
       <c r="S79" s="24" t="n"/>
       <c r="T79" s="24" t="n"/>
-    </row>
-    <row r="80" ht="34" customHeight="1" s="12">
+      <c r="U79" s="24" t="n"/>
+      <c r="V79" s="24" t="n"/>
+    </row>
+    <row r="80">
       <c r="A80" s="24" t="n"/>
-      <c r="B80" s="57" t="inlineStr">
-        <is>
-          <t>SG has been calculated at 12% of gross on every line, which is the correct rate. The reversal also reversed the super, so no over or under contribution arises.</t>
-        </is>
-      </c>
+      <c r="B80" s="24" t="n"/>
+      <c r="C80" s="24" t="n"/>
+      <c r="D80" s="24" t="n"/>
+      <c r="E80" s="24" t="n"/>
+      <c r="F80" s="24" t="n"/>
+      <c r="G80" s="24" t="n"/>
+      <c r="H80" s="24" t="n"/>
+      <c r="I80" s="24" t="n"/>
+      <c r="J80" s="24" t="n"/>
+      <c r="K80" s="24" t="n"/>
+      <c r="L80" s="24" t="n"/>
+      <c r="M80" s="24" t="n"/>
+      <c r="N80" s="24" t="n"/>
+      <c r="O80" s="24" t="n"/>
       <c r="P80" s="24" t="n"/>
       <c r="Q80" s="24" t="n"/>
       <c r="R80" s="24" t="n"/>
       <c r="S80" s="24" t="n"/>
       <c r="T80" s="24" t="n"/>
+      <c r="U80" s="24" t="n"/>
+      <c r="V80" s="24" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="24" t="n"/>
@@ -3830,6 +3962,8 @@
       <c r="R81" s="24" t="n"/>
       <c r="S81" s="24" t="n"/>
       <c r="T81" s="24" t="n"/>
+      <c r="U81" s="24" t="n"/>
+      <c r="V81" s="24" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="24" t="n"/>
@@ -3852,18 +3986,32 @@
       <c r="R82" s="24" t="n"/>
       <c r="S82" s="24" t="n"/>
       <c r="T82" s="24" t="n"/>
-    </row>
-    <row r="83" ht="44" customHeight="1" s="12">
-      <c r="A83" s="25" t="inlineStr">
-        <is>
-          <t>Source of timesheet data: the timesheet screenshots for the fortnights ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026, all showing status PROCESSED. Source of paid data: the Earnings Details tabs in this workbook. Paid figures are live formulas - if a pay-run tab is updated, this reconciliation updates with it. Columns S and T were added to each pay-run tab: S pulls the work date out of the Notes text, T confirms the line was matched here.</t>
-        </is>
-      </c>
+      <c r="U82" s="24" t="n"/>
+      <c r="V82" s="24" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="24" t="n"/>
+      <c r="B83" s="24" t="n"/>
+      <c r="C83" s="24" t="n"/>
+      <c r="D83" s="24" t="n"/>
+      <c r="E83" s="24" t="n"/>
+      <c r="F83" s="24" t="n"/>
+      <c r="G83" s="24" t="n"/>
+      <c r="H83" s="24" t="n"/>
+      <c r="I83" s="24" t="n"/>
+      <c r="J83" s="24" t="n"/>
+      <c r="K83" s="24" t="n"/>
+      <c r="L83" s="24" t="n"/>
+      <c r="M83" s="24" t="n"/>
+      <c r="N83" s="24" t="n"/>
+      <c r="O83" s="24" t="n"/>
       <c r="P83" s="24" t="n"/>
       <c r="Q83" s="24" t="n"/>
       <c r="R83" s="24" t="n"/>
       <c r="S83" s="24" t="n"/>
       <c r="T83" s="24" t="n"/>
+      <c r="U83" s="24" t="n"/>
+      <c r="V83" s="24" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="24" t="n"/>
@@ -3886,6 +4034,8 @@
       <c r="R84" s="24" t="n"/>
       <c r="S84" s="24" t="n"/>
       <c r="T84" s="24" t="n"/>
+      <c r="U84" s="24" t="n"/>
+      <c r="V84" s="24" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="24" t="n"/>
@@ -3908,6 +4058,8 @@
       <c r="R85" s="24" t="n"/>
       <c r="S85" s="24" t="n"/>
       <c r="T85" s="24" t="n"/>
+      <c r="U85" s="24" t="n"/>
+      <c r="V85" s="24" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="24" t="n"/>
@@ -3930,6 +4082,8 @@
       <c r="R86" s="24" t="n"/>
       <c r="S86" s="24" t="n"/>
       <c r="T86" s="24" t="n"/>
+      <c r="U86" s="24" t="n"/>
+      <c r="V86" s="24" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="24" t="n"/>
@@ -3952,6 +4106,8 @@
       <c r="R87" s="24" t="n"/>
       <c r="S87" s="24" t="n"/>
       <c r="T87" s="24" t="n"/>
+      <c r="U87" s="24" t="n"/>
+      <c r="V87" s="24" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="24" t="n"/>
@@ -3974,6 +4130,8 @@
       <c r="R88" s="24" t="n"/>
       <c r="S88" s="24" t="n"/>
       <c r="T88" s="24" t="n"/>
+      <c r="U88" s="24" t="n"/>
+      <c r="V88" s="24" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="24" t="n"/>
@@ -3996,6 +4154,8 @@
       <c r="R89" s="24" t="n"/>
       <c r="S89" s="24" t="n"/>
       <c r="T89" s="24" t="n"/>
+      <c r="U89" s="24" t="n"/>
+      <c r="V89" s="24" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="24" t="n"/>
@@ -4018,72 +4178,192 @@
       <c r="R90" s="24" t="n"/>
       <c r="S90" s="24" t="n"/>
       <c r="T90" s="24" t="n"/>
+      <c r="U90" s="24" t="n"/>
+      <c r="V90" s="24" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="n"/>
+      <c r="B91" s="24" t="n"/>
+      <c r="C91" s="24" t="n"/>
+      <c r="D91" s="24" t="n"/>
+      <c r="E91" s="24" t="n"/>
+      <c r="F91" s="24" t="n"/>
+      <c r="G91" s="24" t="n"/>
+      <c r="H91" s="24" t="n"/>
+      <c r="I91" s="24" t="n"/>
+      <c r="J91" s="24" t="n"/>
+      <c r="K91" s="24" t="n"/>
+      <c r="L91" s="24" t="n"/>
+      <c r="M91" s="24" t="n"/>
+      <c r="N91" s="24" t="n"/>
+      <c r="O91" s="24" t="n"/>
+      <c r="P91" s="24" t="n"/>
+      <c r="Q91" s="24" t="n"/>
+      <c r="R91" s="24" t="n"/>
+      <c r="S91" s="24" t="n"/>
+      <c r="T91" s="24" t="n"/>
+      <c r="U91" s="24" t="n"/>
+      <c r="V91" s="24" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="24" t="n"/>
+      <c r="B92" s="24" t="n"/>
+      <c r="C92" s="24" t="n"/>
+      <c r="D92" s="24" t="n"/>
+      <c r="E92" s="24" t="n"/>
+      <c r="F92" s="24" t="n"/>
+      <c r="G92" s="24" t="n"/>
+      <c r="H92" s="24" t="n"/>
+      <c r="I92" s="24" t="n"/>
+      <c r="J92" s="24" t="n"/>
+      <c r="K92" s="24" t="n"/>
+      <c r="L92" s="24" t="n"/>
+      <c r="M92" s="24" t="n"/>
+      <c r="N92" s="24" t="n"/>
+      <c r="O92" s="24" t="n"/>
+      <c r="P92" s="24" t="n"/>
+      <c r="Q92" s="24" t="n"/>
+      <c r="R92" s="24" t="n"/>
+      <c r="S92" s="24" t="n"/>
+      <c r="T92" s="24" t="n"/>
+      <c r="U92" s="24" t="n"/>
+      <c r="V92" s="24" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="24" t="n"/>
+      <c r="B93" s="24" t="n"/>
+      <c r="C93" s="24" t="n"/>
+      <c r="D93" s="24" t="n"/>
+      <c r="E93" s="24" t="n"/>
+      <c r="F93" s="24" t="n"/>
+      <c r="G93" s="24" t="n"/>
+      <c r="H93" s="24" t="n"/>
+      <c r="I93" s="24" t="n"/>
+      <c r="J93" s="24" t="n"/>
+      <c r="K93" s="24" t="n"/>
+      <c r="L93" s="24" t="n"/>
+      <c r="M93" s="24" t="n"/>
+      <c r="N93" s="24" t="n"/>
+      <c r="O93" s="24" t="n"/>
+      <c r="P93" s="24" t="n"/>
+      <c r="Q93" s="24" t="n"/>
+      <c r="R93" s="24" t="n"/>
+      <c r="S93" s="24" t="n"/>
+      <c r="T93" s="24" t="n"/>
+      <c r="U93" s="24" t="n"/>
+      <c r="V93" s="24" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="24" t="n"/>
+      <c r="B94" s="24" t="n"/>
+      <c r="C94" s="24" t="n"/>
+      <c r="D94" s="24" t="n"/>
+      <c r="E94" s="24" t="n"/>
+      <c r="F94" s="24" t="n"/>
+      <c r="G94" s="24" t="n"/>
+      <c r="H94" s="24" t="n"/>
+      <c r="I94" s="24" t="n"/>
+      <c r="J94" s="24" t="n"/>
+      <c r="K94" s="24" t="n"/>
+      <c r="L94" s="24" t="n"/>
+      <c r="M94" s="24" t="n"/>
+      <c r="N94" s="24" t="n"/>
+      <c r="O94" s="24" t="n"/>
+      <c r="P94" s="24" t="n"/>
+      <c r="Q94" s="24" t="n"/>
+      <c r="R94" s="24" t="n"/>
+      <c r="S94" s="24" t="n"/>
+      <c r="T94" s="24" t="n"/>
+      <c r="U94" s="24" t="n"/>
+      <c r="V94" s="24" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="n"/>
+      <c r="B95" s="24" t="n"/>
+      <c r="C95" s="24" t="n"/>
+      <c r="D95" s="24" t="n"/>
+      <c r="E95" s="24" t="n"/>
+      <c r="F95" s="24" t="n"/>
+      <c r="G95" s="24" t="n"/>
+      <c r="H95" s="24" t="n"/>
+      <c r="I95" s="24" t="n"/>
+      <c r="J95" s="24" t="n"/>
+      <c r="K95" s="24" t="n"/>
+      <c r="L95" s="24" t="n"/>
+      <c r="M95" s="24" t="n"/>
+      <c r="N95" s="24" t="n"/>
+      <c r="O95" s="24" t="n"/>
+      <c r="P95" s="24" t="n"/>
+      <c r="Q95" s="24" t="n"/>
+      <c r="R95" s="24" t="n"/>
+      <c r="S95" s="24" t="n"/>
+      <c r="T95" s="24" t="n"/>
+      <c r="U95" s="24" t="n"/>
+      <c r="V95" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A83:O83"/>
-    <mergeCell ref="B71:O71"/>
-    <mergeCell ref="B74:O74"/>
-    <mergeCell ref="B65:O65"/>
+  <mergeCells count="15">
+    <mergeCell ref="B58:O58"/>
+    <mergeCell ref="B63:K63"/>
+    <mergeCell ref="B57:K57"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="B79:H79"/>
-    <mergeCell ref="B77:O77"/>
-    <mergeCell ref="B68:O68"/>
-    <mergeCell ref="B62:O62"/>
-    <mergeCell ref="B73:H73"/>
-    <mergeCell ref="B70:H70"/>
-    <mergeCell ref="B64:H64"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B80:O80"/>
+    <mergeCell ref="B73:O73"/>
+    <mergeCell ref="B70:O70"/>
+    <mergeCell ref="A76:O76"/>
+    <mergeCell ref="B64:O64"/>
+    <mergeCell ref="B69:K69"/>
+    <mergeCell ref="B66:K66"/>
+    <mergeCell ref="B67:O67"/>
+    <mergeCell ref="B61:O61"/>
     <mergeCell ref="A9:O9"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B72:K72"/>
+    <mergeCell ref="B60:K60"/>
   </mergeCells>
-  <conditionalFormatting sqref="E13:E17">
+  <conditionalFormatting sqref="G13:G17">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J21:J37">
+  <conditionalFormatting sqref="K21:K37">
     <cfRule type="cellIs" priority="2" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F8">
+  <conditionalFormatting sqref="H6:H8">
     <cfRule type="cellIs" priority="3" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13:G17">
+  <conditionalFormatting sqref="J13:J17">
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>ISNUMBER(SEARCH("Reconciled",G13))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("Reconciled",J13))+ISNUMBER(SEARCH("FULLY",J13))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="0">
-      <formula>ISNUMBER(SEARCH("VARIANCE",G13))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("VARIANCE",J13))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N21:N37">
+  <conditionalFormatting sqref="C50:C54">
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>ISNUMBER(SEARCH("OK",N21))+ISNUMBER(SEARCH("AGREE",N21))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("OK",C50))+ISNUMBER(SEARCH("FULLY",C50))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="0">
-      <formula>ISNUMBER(SEARCH("UNDER",N21))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D51:D58">
-    <cfRule type="expression" priority="8" dxfId="1">
-      <formula>ISNUMBER(SEARCH("OK",D51))+ISNUMBER(SEARCH("FULLY",D51))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="0">
-      <formula>ISNUMBER(SEARCH("INVESTIGATE",D51))+ISNUMBER(SEARCH("VARIANCE",D51))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("INVESTIGATE",C50))+ISNUMBER(SEARCH("VARIANCE",C50))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K8">
-    <cfRule type="expression" priority="10" dxfId="1">
+    <cfRule type="expression" priority="8" dxfId="1">
       <formula>ISNUMBER(SEARCH("PAID IN FULL",K6))+ISNUMBER(SEARCH("NIL OWING",K6))&gt;0</formula>
     </cfRule>
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>ISNUMBER(SEARCH("SHORTFALL",K6))+ISNUMBER(SEARCH("OWING - ",K6))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21:M36">
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>ISNUMBER(SEARCH("OK",M21))&gt;0</formula>
+    </cfRule>
     <cfRule type="expression" priority="11" dxfId="0">
-      <formula>ISNUMBER(SEARCH("SHORTFALL",K6))+ISNUMBER(SEARCH("OWING - ",K6))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("NOT $",M21))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4219,12 +4499,12 @@
           <t>SG Super</t>
         </is>
       </c>
-      <c r="S2" s="58" t="inlineStr">
+      <c r="S2" s="70" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="T2" s="58" t="inlineStr">
+      <c r="T2" s="70" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -4295,12 +4575,12 @@
       <c r="Q3" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S3" s="59">
+      <c r="S3" s="71">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="T3">
-        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$E$21:$E$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4369,12 +4649,12 @@
       <c r="Q4" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S4" s="59">
+      <c r="S4" s="71">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="T4">
-        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$E$21:$E$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4443,12 +4723,12 @@
       <c r="Q5" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S5" s="59">
+      <c r="S5" s="71">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="T5">
-        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$E$21:$E$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4517,12 +4797,12 @@
       <c r="Q6" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="71">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="T6">
-        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$E$21:$E$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4591,12 +4871,12 @@
       <c r="Q7" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S7" s="59">
+      <c r="S7" s="71">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="T7">
-        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$E$21:$E$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4665,12 +4945,12 @@
       <c r="Q8" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S8" s="59">
+      <c r="S8" s="71">
         <f>IFERROR(DATE(VALUE(MID(L8,FIND("/",L8,FIND("/",L8)+1)+1,4)),VALUE(MID(L8,FIND("/",L8)+1,FIND("/",L8,FIND("/",L8)+1)-FIND("/",L8)-1)),VALUE(LEFT(L8,FIND("/",L8)-1))),IF(ISNUMBER(L8),L8,""))</f>
         <v/>
       </c>
       <c r="T8">
-        <f>IF(S8="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S8,'Summary '!$D$21:$D$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S8="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S8,'Summary '!$E$21:$E$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4739,12 +5019,12 @@
       <c r="Q9" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S9" s="59">
+      <c r="S9" s="71">
         <f>IFERROR(DATE(VALUE(MID(L9,FIND("/",L9,FIND("/",L9)+1)+1,4)),VALUE(MID(L9,FIND("/",L9)+1,FIND("/",L9,FIND("/",L9)+1)-FIND("/",L9)-1)),VALUE(LEFT(L9,FIND("/",L9)-1))),IF(ISNUMBER(L9),L9,""))</f>
         <v/>
       </c>
       <c r="T9">
-        <f>IF(S9="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S9,'Summary '!$D$21:$D$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S9="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S9,'Summary '!$E$21:$E$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4813,12 +5093,12 @@
       <c r="Q10" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S10" s="59">
+      <c r="S10" s="71">
         <f>IFERROR(DATE(VALUE(MID(L10,FIND("/",L10,FIND("/",L10)+1)+1,4)),VALUE(MID(L10,FIND("/",L10)+1,FIND("/",L10,FIND("/",L10)+1)-FIND("/",L10)-1)),VALUE(LEFT(L10,FIND("/",L10)-1))),IF(ISNUMBER(L10),L10,""))</f>
         <v/>
       </c>
       <c r="T10">
-        <f>IF(S10="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S10,'Summary '!$D$21:$D$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S10="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S10,'Summary '!$E$21:$E$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4887,12 +5167,12 @@
       <c r="Q11" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="S11" s="59">
+      <c r="S11" s="71">
         <f>IFERROR(DATE(VALUE(MID(L11,FIND("/",L11,FIND("/",L11)+1)+1,4)),VALUE(MID(L11,FIND("/",L11)+1,FIND("/",L11,FIND("/",L11)+1)-FIND("/",L11)-1)),VALUE(LEFT(L11,FIND("/",L11)-1))),IF(ISNUMBER(L11),L11,""))</f>
         <v/>
       </c>
       <c r="T11">
-        <f>IF(S11="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S11,'Summary '!$D$21:$D$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S11="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S11,'Summary '!$E$21:$E$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5031,12 +5311,12 @@
           <t>SG Super</t>
         </is>
       </c>
-      <c r="S2" s="58" t="inlineStr">
+      <c r="S2" s="70" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="T2" s="58" t="inlineStr">
+      <c r="T2" s="70" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -5107,12 +5387,12 @@
       <c r="Q3" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S3" s="59">
+      <c r="S3" s="71">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="T3">
-        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$E$21:$E$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5181,12 +5461,12 @@
       <c r="Q4" s="15" t="n">
         <v>20.25</v>
       </c>
-      <c r="S4" s="59">
+      <c r="S4" s="71">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="T4">
-        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$E$21:$E$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5255,12 +5535,12 @@
       <c r="Q5" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S5" s="59">
+      <c r="S5" s="71">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="T5">
-        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$E$21:$E$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5329,12 +5609,12 @@
       <c r="Q6" s="15" t="n">
         <v>20.25</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="71">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="T6">
-        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$E$21:$E$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5403,12 +5683,12 @@
       <c r="Q7" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S7" s="59">
+      <c r="S7" s="71">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="T7">
-        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$E$21:$E$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5477,12 +5757,12 @@
       <c r="Q8" s="15" t="n">
         <v>20.25</v>
       </c>
-      <c r="S8" s="59">
+      <c r="S8" s="71">
         <f>IFERROR(DATE(VALUE(MID(L8,FIND("/",L8,FIND("/",L8)+1)+1,4)),VALUE(MID(L8,FIND("/",L8)+1,FIND("/",L8,FIND("/",L8)+1)-FIND("/",L8)-1)),VALUE(LEFT(L8,FIND("/",L8)-1))),IF(ISNUMBER(L8),L8,""))</f>
         <v/>
       </c>
       <c r="T8">
-        <f>IF(S8="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S8,'Summary '!$D$21:$D$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S8="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S8,'Summary '!$E$21:$E$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5551,12 +5831,12 @@
       <c r="Q9" s="15" t="n">
         <v>13.5</v>
       </c>
-      <c r="S9" s="59">
+      <c r="S9" s="71">
         <f>IFERROR(DATE(VALUE(MID(L9,FIND("/",L9,FIND("/",L9)+1)+1,4)),VALUE(MID(L9,FIND("/",L9)+1,FIND("/",L9,FIND("/",L9)+1)-FIND("/",L9)-1)),VALUE(LEFT(L9,FIND("/",L9)-1))),IF(ISNUMBER(L9),L9,""))</f>
         <v/>
       </c>
       <c r="T9">
-        <f>IF(S9="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S9,'Summary '!$D$21:$D$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S9="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S9,'Summary '!$E$21:$E$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5625,12 +5905,12 @@
       <c r="Q10" s="15" t="n">
         <v>22.5</v>
       </c>
-      <c r="S10" s="59">
+      <c r="S10" s="71">
         <f>IFERROR(DATE(VALUE(MID(L10,FIND("/",L10,FIND("/",L10)+1)+1,4)),VALUE(MID(L10,FIND("/",L10)+1,FIND("/",L10,FIND("/",L10)+1)-FIND("/",L10)-1)),VALUE(LEFT(L10,FIND("/",L10)-1))),IF(ISNUMBER(L10),L10,""))</f>
         <v/>
       </c>
       <c r="T10">
-        <f>IF(S10="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S10,'Summary '!$D$21:$D$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S10="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S10,'Summary '!$E$21:$E$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5699,12 +5979,12 @@
       <c r="Q11" s="15" t="n">
         <v>13.5</v>
       </c>
-      <c r="S11" s="59">
+      <c r="S11" s="71">
         <f>IFERROR(DATE(VALUE(MID(L11,FIND("/",L11,FIND("/",L11)+1)+1,4)),VALUE(MID(L11,FIND("/",L11)+1,FIND("/",L11,FIND("/",L11)+1)-FIND("/",L11)-1)),VALUE(LEFT(L11,FIND("/",L11)-1))),IF(ISNUMBER(L11),L11,""))</f>
         <v/>
       </c>
       <c r="T11">
-        <f>IF(S11="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S11,'Summary '!$D$21:$D$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S11="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S11,'Summary '!$E$21:$E$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5773,12 +6053,12 @@
       <c r="Q12" s="15" t="n">
         <v>22.5</v>
       </c>
-      <c r="S12" s="59">
+      <c r="S12" s="71">
         <f>IFERROR(DATE(VALUE(MID(L12,FIND("/",L12,FIND("/",L12)+1)+1,4)),VALUE(MID(L12,FIND("/",L12)+1,FIND("/",L12,FIND("/",L12)+1)-FIND("/",L12)-1)),VALUE(LEFT(L12,FIND("/",L12)-1))),IF(ISNUMBER(L12),L12,""))</f>
         <v/>
       </c>
       <c r="T12">
-        <f>IF(S12="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S12,'Summary '!$D$21:$D$36,K12)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S12="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S12,'Summary '!$E$21:$E$36,K12)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5847,12 +6127,12 @@
       <c r="Q13" s="15" t="n">
         <v>15.75</v>
       </c>
-      <c r="S13" s="59">
+      <c r="S13" s="71">
         <f>IFERROR(DATE(VALUE(MID(L13,FIND("/",L13,FIND("/",L13)+1)+1,4)),VALUE(MID(L13,FIND("/",L13)+1,FIND("/",L13,FIND("/",L13)+1)-FIND("/",L13)-1)),VALUE(LEFT(L13,FIND("/",L13)-1))),IF(ISNUMBER(L13),L13,""))</f>
         <v/>
       </c>
       <c r="T13">
-        <f>IF(S13="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S13,'Summary '!$D$21:$D$36,K13)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S13="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S13,'Summary '!$E$21:$E$36,K13)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5921,12 +6201,12 @@
       <c r="Q14" s="15" t="n">
         <v>20.25</v>
       </c>
-      <c r="S14" s="59">
+      <c r="S14" s="71">
         <f>IFERROR(DATE(VALUE(MID(L14,FIND("/",L14,FIND("/",L14)+1)+1,4)),VALUE(MID(L14,FIND("/",L14)+1,FIND("/",L14,FIND("/",L14)+1)-FIND("/",L14)-1)),VALUE(LEFT(L14,FIND("/",L14)-1))),IF(ISNUMBER(L14),L14,""))</f>
         <v/>
       </c>
       <c r="T14">
-        <f>IF(S14="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S14,'Summary '!$D$21:$D$36,K14)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S14="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S14,'Summary '!$E$21:$E$36,K14)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6065,12 +6345,12 @@
           <t>SG Super</t>
         </is>
       </c>
-      <c r="S2" s="58" t="inlineStr">
+      <c r="S2" s="70" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="T2" s="58" t="inlineStr">
+      <c r="T2" s="70" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -6141,12 +6421,12 @@
       <c r="Q3" s="15" t="n">
         <v>-67.48569000000001</v>
       </c>
-      <c r="S3" s="59">
+      <c r="S3" s="71">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="T3">
-        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$E$21:$E$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6215,12 +6495,12 @@
       <c r="Q4" s="15" t="n">
         <v>71.99754</v>
       </c>
-      <c r="S4" s="59">
+      <c r="S4" s="71">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="T4">
-        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$E$21:$E$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6289,12 +6569,12 @@
       <c r="Q5" s="15" t="n">
         <v>22.49923</v>
       </c>
-      <c r="S5" s="59">
+      <c r="S5" s="71">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="T5">
-        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$E$21:$E$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6363,12 +6643,12 @@
       <c r="Q6" s="15" t="n">
         <v>13.49954</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="71">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="T6">
-        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$E$21:$E$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6437,12 +6717,12 @@
       <c r="Q7" s="15" t="n">
         <v>17.99938</v>
       </c>
-      <c r="S7" s="59">
+      <c r="S7" s="71">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="T7">
-        <f>IF(S7="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S7,'Summary '!$E$21:$E$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6580,12 +6860,12 @@
           <t>SG Super</t>
         </is>
       </c>
-      <c r="S2" s="58" t="inlineStr">
+      <c r="S2" s="70" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="T2" s="58" t="inlineStr">
+      <c r="T2" s="70" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -6654,12 +6934,12 @@
       <c r="Q3" s="15" t="n">
         <v>23.19969</v>
       </c>
-      <c r="S3" s="59">
+      <c r="S3" s="71">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="T3">
-        <f>IF(S3="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S3,'Summary '!$E$21:$E$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6726,12 +7006,12 @@
       <c r="Q4" s="15" t="n">
         <v>10.54531</v>
       </c>
-      <c r="S4" s="59">
+      <c r="S4" s="71">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="T4">
-        <f>IF(S4="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S4,'Summary '!$E$21:$E$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6798,12 +7078,12 @@
       <c r="Q5" s="15" t="n">
         <v>16.8725</v>
       </c>
-      <c r="S5" s="59">
+      <c r="S5" s="71">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="T5">
-        <f>IF(S5="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S5,'Summary '!$E$21:$E$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -6870,12 +7150,12 @@
       <c r="Q6" s="15" t="n">
         <v>16.8725</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="71">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="T6">
-        <f>IF(S6="","No - adjustment/reversal (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(S6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,S6,'Summary '!$E$21:$E$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
